--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -37703,49 +37703,49 @@
         <v>81.759</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>100.202</v>
+        <v>100.274</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>114.806</v>
+        <v>115.312</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>114.978</v>
+        <v>115.478</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>121.882</v>
+        <v>122.382</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>123.332</v>
+        <v>123.837</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>123.829</v>
+        <v>124.334</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>124.716</v>
+        <v>125.21</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>124.427</v>
+        <v>124.927</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>125.009</v>
+        <v>125.515</v>
       </c>
       <c r="AI5" s="26" t="n">
-        <v>134.536</v>
+        <v>135.042</v>
       </c>
       <c r="AJ5" s="26" t="n">
-        <v>185.293</v>
+        <v>185.788</v>
       </c>
       <c r="AK5" s="26" t="n">
-        <v>220.263</v>
+        <v>220.764</v>
       </c>
       <c r="AL5" s="26" t="n">
-        <v>241.711</v>
+        <v>242.216</v>
       </c>
       <c r="AM5" s="26" t="n">
-        <v>284.118</v>
+        <v>284.624</v>
       </c>
       <c r="AN5" s="26" t="n">
-        <v>261.673</v>
+        <v>262.167</v>
       </c>
       <c r="AO5" s="26" t="n">
         <v>237.986</v>
@@ -38030,19 +38030,19 @@
         <v>245.213</v>
       </c>
       <c r="EE5" s="26" t="n">
-        <v>369.854</v>
+        <v>370.432</v>
       </c>
       <c r="EF5" s="26" t="n">
-        <v>484.021</v>
+        <v>486.031</v>
       </c>
       <c r="EG5" s="26" t="n">
-        <v>508.688</v>
+        <v>510.694</v>
       </c>
       <c r="EH5" s="26" t="n">
-        <v>931.385</v>
+        <v>933.3920000000001</v>
       </c>
       <c r="EI5" s="26" t="n">
-        <v>950.894</v>
+        <v>951.388</v>
       </c>
       <c r="EJ5" s="26" t="n">
         <v>715.877</v>
@@ -38186,49 +38186,49 @@
         <v>81.759</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>100.202</v>
+        <v>100.274</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>114.806</v>
+        <v>115.312</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>114.978</v>
+        <v>115.478</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>121.882</v>
+        <v>122.382</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>123.332</v>
+        <v>123.837</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>123.829</v>
+        <v>124.334</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>124.716</v>
+        <v>125.21</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>124.427</v>
+        <v>124.927</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>125.009</v>
+        <v>125.515</v>
       </c>
       <c r="AI6" s="26" t="n">
-        <v>131.854</v>
+        <v>132.36</v>
       </c>
       <c r="AJ6" s="26" t="n">
-        <v>153.802</v>
+        <v>154.297</v>
       </c>
       <c r="AK6" s="26" t="n">
-        <v>159.705</v>
+        <v>160.205</v>
       </c>
       <c r="AL6" s="26" t="n">
-        <v>169.47</v>
+        <v>169.975</v>
       </c>
       <c r="AM6" s="26" t="n">
-        <v>170.727</v>
+        <v>171.233</v>
       </c>
       <c r="AN6" s="26" t="n">
-        <v>150.747</v>
+        <v>151.241</v>
       </c>
       <c r="AO6" s="26" t="n">
         <v>125.827</v>
@@ -38513,19 +38513,19 @@
         <v>245.213</v>
       </c>
       <c r="EE6" s="26" t="n">
-        <v>369.854</v>
+        <v>370.432</v>
       </c>
       <c r="EF6" s="26" t="n">
-        <v>484.021</v>
+        <v>486.031</v>
       </c>
       <c r="EG6" s="26" t="n">
-        <v>506.006</v>
+        <v>508.012</v>
       </c>
       <c r="EH6" s="26" t="n">
-        <v>653.704</v>
+        <v>655.71</v>
       </c>
       <c r="EI6" s="26" t="n">
-        <v>501.027</v>
+        <v>501.521</v>
       </c>
       <c r="EJ6" s="26" t="n">
         <v>332.415</v>
@@ -38813,49 +38813,49 @@
         <v>81.759</v>
       </c>
       <c r="Z9" s="26" t="n">
-        <v>100.202</v>
+        <v>100.274</v>
       </c>
       <c r="AA9" s="26" t="n">
-        <v>114.806</v>
+        <v>115.312</v>
       </c>
       <c r="AB9" s="26" t="n">
-        <v>114.978</v>
+        <v>115.478</v>
       </c>
       <c r="AC9" s="26" t="n">
-        <v>121.882</v>
+        <v>122.382</v>
       </c>
       <c r="AD9" s="26" t="n">
-        <v>123.332</v>
+        <v>123.837</v>
       </c>
       <c r="AE9" s="26" t="n">
-        <v>123.829</v>
+        <v>124.334</v>
       </c>
       <c r="AF9" s="26" t="n">
-        <v>124.716</v>
+        <v>125.21</v>
       </c>
       <c r="AG9" s="26" t="n">
-        <v>124.427</v>
+        <v>124.927</v>
       </c>
       <c r="AH9" s="26" t="n">
-        <v>125.009</v>
+        <v>125.515</v>
       </c>
       <c r="AI9" s="26" t="n">
-        <v>134.141</v>
+        <v>134.646</v>
       </c>
       <c r="AJ9" s="26" t="n">
-        <v>167.521</v>
+        <v>168.016</v>
       </c>
       <c r="AK9" s="26" t="n">
-        <v>173.576</v>
+        <v>174.076</v>
       </c>
       <c r="AL9" s="26" t="n">
-        <v>183.493</v>
+        <v>183.999</v>
       </c>
       <c r="AM9" s="26" t="n">
-        <v>184.751</v>
+        <v>185.257</v>
       </c>
       <c r="AN9" s="26" t="n">
-        <v>164.466</v>
+        <v>164.96</v>
       </c>
       <c r="AO9" s="26" t="n">
         <v>139.698</v>
@@ -39140,19 +39140,19 @@
         <v>245.213</v>
       </c>
       <c r="EE9" s="26" t="n">
-        <v>369.854</v>
+        <v>370.432</v>
       </c>
       <c r="EF9" s="26" t="n">
-        <v>484.021</v>
+        <v>486.031</v>
       </c>
       <c r="EG9" s="26" t="n">
-        <v>508.293</v>
+        <v>510.298</v>
       </c>
       <c r="EH9" s="26" t="n">
-        <v>709.341</v>
+        <v>711.348</v>
       </c>
       <c r="EI9" s="26" t="n">
-        <v>556.665</v>
+        <v>557.159</v>
       </c>
       <c r="EJ9" s="26" t="n">
         <v>388.204</v>
@@ -39812,49 +39812,49 @@
         <v>1183.49</v>
       </c>
       <c r="Z13" s="13" t="n">
-        <v>1206.38</v>
+        <v>1206.46</v>
       </c>
       <c r="AA13" s="13" t="n">
-        <v>1220.03</v>
+        <v>1220.44</v>
       </c>
       <c r="AB13" s="13" t="n">
-        <v>1221.39</v>
+        <v>1221.79</v>
       </c>
       <c r="AC13" s="13" t="n">
-        <v>1227.55</v>
+        <v>1227.91</v>
       </c>
       <c r="AD13" s="13" t="n">
-        <v>1227.64</v>
+        <v>1228</v>
       </c>
       <c r="AE13" s="13" t="n">
-        <v>1228.32</v>
+        <v>1228.67</v>
       </c>
       <c r="AF13" s="13" t="n">
-        <v>1233.51</v>
+        <v>1233.83</v>
       </c>
       <c r="AG13" s="13" t="n">
-        <v>1248.95</v>
+        <v>1249.2</v>
       </c>
       <c r="AH13" s="13" t="n">
-        <v>1253.99</v>
+        <v>1254.23</v>
       </c>
       <c r="AI13" s="13" t="n">
-        <v>1267.81</v>
+        <v>1267.98</v>
       </c>
       <c r="AJ13" s="13" t="n">
-        <v>1322.96</v>
+        <v>1322.94</v>
       </c>
       <c r="AK13" s="13" t="n">
-        <v>1377.84</v>
+        <v>1377.69</v>
       </c>
       <c r="AL13" s="13" t="n">
-        <v>1386.37</v>
+        <v>1386.22</v>
       </c>
       <c r="AM13" s="13" t="n">
-        <v>1391.35</v>
+        <v>1391.21</v>
       </c>
       <c r="AN13" s="13" t="n">
-        <v>1404.49</v>
+        <v>1404.32</v>
       </c>
       <c r="AO13" s="13" t="n">
         <v>1421.93</v>
@@ -40586,49 +40586,49 @@
         <v>1223.15</v>
       </c>
       <c r="Z15" s="13" t="n">
-        <v>1238.56</v>
+        <v>1238.61</v>
       </c>
       <c r="AA15" s="13" t="n">
-        <v>1250.63</v>
+        <v>1250.91</v>
       </c>
       <c r="AB15" s="13" t="n">
-        <v>1254.02</v>
+        <v>1254.3</v>
       </c>
       <c r="AC15" s="13" t="n">
-        <v>1270.67</v>
+        <v>1270.92</v>
       </c>
       <c r="AD15" s="13" t="n">
-        <v>1266.22</v>
+        <v>1266.46</v>
       </c>
       <c r="AE15" s="13" t="n">
-        <v>1278.72</v>
+        <v>1278.96</v>
       </c>
       <c r="AF15" s="13" t="n">
-        <v>1299.14</v>
+        <v>1299.36</v>
       </c>
       <c r="AG15" s="13" t="n">
-        <v>1293.82</v>
+        <v>1294</v>
       </c>
       <c r="AH15" s="13" t="n">
-        <v>1293.88</v>
+        <v>1294.04</v>
       </c>
       <c r="AI15" s="13" t="n">
-        <v>1322.22</v>
+        <v>1322.34</v>
       </c>
       <c r="AJ15" s="13" t="n">
-        <v>1365.91</v>
+        <v>1365.89</v>
       </c>
       <c r="AK15" s="13" t="n">
-        <v>1415.01</v>
+        <v>1414.91</v>
       </c>
       <c r="AL15" s="13" t="n">
-        <v>1396.38</v>
+        <v>1396.27</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1379.95</v>
+        <v>1379.86</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1389.15</v>
+        <v>1389.03</v>
       </c>
       <c r="AO15" s="13" t="n">
         <v>1401.36</v>
@@ -40973,49 +40973,49 @@
         <v>100004.1</v>
       </c>
       <c r="Z16" s="18" t="n">
-        <v>124106.1</v>
+        <v>124200</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>143579.8</v>
+        <v>144245.2</v>
       </c>
       <c r="AB16" s="18" t="n">
-        <v>144184.6</v>
+        <v>144844</v>
       </c>
       <c r="AC16" s="18" t="n">
-        <v>154872.1</v>
+        <v>155537.7</v>
       </c>
       <c r="AD16" s="18" t="n">
-        <v>156164.6</v>
+        <v>156835.1</v>
       </c>
       <c r="AE16" s="18" t="n">
-        <v>158341.9</v>
+        <v>159018.5</v>
       </c>
       <c r="AF16" s="18" t="n">
-        <v>162023.4</v>
+        <v>162693.6</v>
       </c>
       <c r="AG16" s="18" t="n">
-        <v>160985.6</v>
+        <v>161655.2</v>
       </c>
       <c r="AH16" s="18" t="n">
-        <v>161746.7</v>
+        <v>162421.9</v>
       </c>
       <c r="AI16" s="18" t="n">
-        <v>177887</v>
+        <v>178571.6</v>
       </c>
       <c r="AJ16" s="18" t="n">
-        <v>253093.4</v>
+        <v>253765.6</v>
       </c>
       <c r="AK16" s="18" t="n">
-        <v>311675.7</v>
+        <v>312360.8</v>
       </c>
       <c r="AL16" s="18" t="n">
-        <v>337519.5</v>
+        <v>338199.7</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392070</v>
+        <v>392740.1</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363503.2</v>
+        <v>364158.8</v>
       </c>
       <c r="AO16" s="18" t="n">
         <v>333504.1</v>
@@ -41300,19 +41300,19 @@
         <v>289816.6</v>
       </c>
       <c r="EE16" s="18" t="n">
-        <v>455588.7</v>
+        <v>456348</v>
       </c>
       <c r="EF16" s="18" t="n">
-        <v>613563.2</v>
+        <v>616235.3</v>
       </c>
       <c r="EG16" s="18" t="n">
-        <v>662642.7</v>
+        <v>665342.3</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1294358.6</v>
+        <v>1297066.2</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1331848.8</v>
+        <v>1332504.4</v>
       </c>
       <c r="EJ16" s="18" t="n">
         <v>1014731.8</v>
@@ -43382,7 +43382,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260911800204</t>
+          <t>20260918800109</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -43391,27 +43391,27 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>251603.814</v>
+        <v>60071.111</v>
       </c>
       <c r="E63" t="n">
-        <v>191.535</v>
+        <v>45.161</v>
       </c>
       <c r="F63" t="n">
-        <v>1313.62</v>
+        <v>1330.14</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2028-08-09</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -43426,36 +43426,44 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260918800109</t>
+          <t>20260922800008</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>60071.111</v>
+        <v>678967.559</v>
       </c>
       <c r="E64" t="n">
-        <v>45.161</v>
+        <v>478.24</v>
       </c>
       <c r="F64" t="n">
-        <v>1330.14</v>
+        <v>1419.72</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2028-08-09</t>
+          <t>2029-04-30</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -43464,50 +43472,42 @@
         </is>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260922800008</t>
+          <t>20260930800251</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>4</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D65" t="n">
-        <v>678967.559</v>
+        <v>260922.379</v>
       </c>
       <c r="E65" t="n">
-        <v>478.24</v>
+        <v>198.629</v>
       </c>
       <c r="F65" t="n">
-        <v>1419.72</v>
+        <v>1313.62</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -43516,7 +43516,7 @@
         </is>
       </c>
       <c r="L65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -43550,7 +43550,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32277억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.69) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
+          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32297억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
         </is>
       </c>
     </row>

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -22,7 +22,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$94</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$102</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$91</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -770,121 +770,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -896,55 +896,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3247억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3194억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3739억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3618억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4232억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4042억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4728억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4470억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5067억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4759억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5384억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5029억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5701억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5299억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6020억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5571억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6308억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5817억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -2153,61 +2153,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
@@ -2308,61 +2308,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.8% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.7% + 회사 캘리브레이션 +4.3%p(최근 3분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -7.0%p(최근 3분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
@@ -2374,55 +2374,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3247억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3194억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3739억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3618억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4232억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4042억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4728억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4470억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5067억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4759억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5384억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5029억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5701억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5299억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6020억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5571억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6308억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5817억 × 2.56% − 총차입금 4751억 × 7.96% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4474,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4595,14 +4595,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출은 2026Q2 기준 잔고 소진분만 — 이후 신규 수주 매출 미포함(2028 감소는 이 한계). forecast_panel 모듈 참고 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출은 2026Q2 기준 잔고 소진분만 — 신규수주 매출 미포함(forecast_panel 097230 status partial(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) — new_order_revenue 값 없음; 2028 감소는 이 한계). forecast_panel 모듈 참고 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 19.4, "op_wape_pct": 100.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 4962.89, "rev_act": 4522.08, "op_pred": 0.0, "op_act": 57.94}, {"q": "2025Q4", "rev_pred": 4962.89, "rev_act": 6296.54, "op_pred": 0.0, "op_act": 504.87}, {"q": "2026Q1", "rev_pred": 4962.89, "rev_act": 5414.0, "op_pred": 0.0, "op_act": 245.81}, {"q": "2026Q2", "rev_pred": 4962.89, "rev_act": 7299.08, "op_pred": 0.0, "op_act": 648.53}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 19.4, "op_wape_pct": 100.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 4962.89, "rev_act": 4522.08, "op_pred": 0.0, "op_act": 57.94}, {"q": "2025Q4", "rev_pred": 4962.89, "rev_act": 6296.54, "op_pred": 0.0, "op_act": 504.87}, {"q": "2026Q1", "rev_pred": 4962.89, "rev_act": 5414.0, "op_pred": 0.0, "op_act": 245.81}, {"q": "2026Q2", "rev_pred": 4962.89, "rev_act": 7299.08, "op_pred": 0.0, "op_act": 648.53}]}</t>
         </is>
       </c>
     </row>
@@ -8804,42 +8804,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.089652</v>
+        <v>0.080183</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.091152</v>
+        <v>0.080182</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.091151</v>
+        <v>0.080182</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.091151</v>
+        <v>0.080181</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.091151</v>
+        <v>0.080181</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.091152</v>
+        <v>0.080183</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.091151</v>
+        <v>0.080182</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.091151</v>
+        <v>0.080182</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.090452</v>
+        <v>0.080181</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.09055100000000001</v>
+        <v>0.080181</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8932,20 +8932,20 @@
         <v/>
       </c>
       <c r="AC24" s="24" t="n">
-        <v>6.007812</v>
+        <v>5.265625</v>
       </c>
       <c r="AD24" s="24" t="n">
-        <v>0.137157</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="25" t="n"/>
       <c r="AF24" s="24" t="n">
-        <v>1.008811</v>
+        <v>0.76652</v>
       </c>
       <c r="AG24" s="24" t="n">
-        <v>0.025872</v>
+        <v>-0.09786300000000001</v>
       </c>
       <c r="AH24" s="24" t="n">
-        <v>0.016722</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="24" t="n">
         <v>0</v>
@@ -8958,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="AM24" s="24" t="n">
-        <v>-0.007675</v>
+        <v>0</v>
       </c>
       <c r="AN24" s="24" t="n">
-        <v>-0.006579</v>
+        <v>0</v>
       </c>
       <c r="AO24" s="25" t="n"/>
     </row>
@@ -9081,39 +9081,39 @@
         <v>-76.43000000000001</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>-73.66</v>
+        <v>-74</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>-70.51000000000001</v>
+        <v>-71.28</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>-67.34999999999999</v>
+        <v>-68.56</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>-64.17</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>-61.99</v>
+        <v>-63.97</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-59.96</v>
+        <v>-62.24</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>-57.93</v>
+        <v>-60.51</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-55.88</v>
+        <v>-58.76</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-54.03</v>
+        <v>-57.18</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -9388,42 +9388,42 @@
         <v/>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.050001</v>
+        <v>0.049995</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.049995</v>
+        <v>0.05001</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.049999</v>
+        <v>0.049998</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.050003</v>
+        <v>0.050007</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.050007</v>
+        <v>0.049984</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.04999</v>
+        <v>0.050016</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050013</v>
+        <v>0.049995</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.050009</v>
+        <v>0.050005</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.049998</v>
+        <v>0.050015</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.050011</v>
+        <v>0.050019</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -9910,17 +9910,17 @@
         <v>0</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
         <v>-0</v>
@@ -9930,10 +9930,10 @@
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>-0</v>
@@ -10038,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
@@ -10048,7 +10048,7 @@
         <v>0</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
         <v>-0</v>
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
         <v>0</v>
@@ -10291,36 +10291,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>-0.216554</v>
+        <v>-0.189842</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>-0.314592</v>
+        <v>-0.262199</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.458938</v>
+        <v>-0.355312</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.856008</v>
+        <v>-0.556218</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-4.05231</v>
+        <v>-0.845969</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>1.242402</v>
+        <v>-5.127757</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.554767</v>
+        <v>1.243644</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.358988</v>
+        <v>0.557684</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.238747</v>
+        <v>0.325404</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.180111</v>
+        <v>0.228511</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -10419,36 +10419,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.153624</v>
+        <v>0.134675</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.15156</v>
+        <v>0.132807</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.1316</v>
+        <v>0.117215</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.117363</v>
+        <v>0.105885</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.07159799999999999</v>
+        <v>0.064625</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.062526</v>
+        <v>0.056674</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.058922</v>
+        <v>0.053694</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.055982</v>
+        <v>0.051269</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.047915</v>
+        <v>0.044326</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.042729</v>
+        <v>0.039505</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11072,33 +11072,33 @@
       </c>
       <c r="AC41" s="31" t="n"/>
       <c r="AD41" s="24" t="n">
-        <v>-0.825</v>
+        <v>-0.8125</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.796067</v>
+        <v>-0.775135</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.560461</v>
+        <v>-0.492003</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.010959</v>
+        <v>0.11421</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>0.097527</v>
+        <v>0.19359</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>0.390358</v>
+        <v>0.473907</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>0.480349</v>
+        <v>0.5037779999999999</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>0.465374</v>
+        <v>0.479142</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>0.376721</v>
+        <v>0.385607</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -11188,36 +11188,36 @@
         <v/>
       </c>
       <c r="AC42" s="24" t="n">
-        <v>-0.584383</v>
+        <v>-0.581864</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.517134</v>
+        <v>-0.507788</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.544892</v>
+        <v>-0.535604</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.525597</v>
+        <v>-0.511945</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.187879</v>
+        <v>-0.162651</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.16129</v>
+        <v>-0.14557</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.142857</v>
+        <v>-0.126667</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.122302</v>
+        <v>-0.104895</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.11194</v>
+        <v>-0.100719</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.107692</v>
+        <v>-0.09629600000000001</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -11489,42 +11489,42 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>0.08964999999999999</v>
+        <v>0.080181</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.080183</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.091152</v>
+        <v>0.080181</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.080182</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.091153</v>
+        <v>0.080182</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.09114800000000001</v>
+        <v>0.08018</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.091153</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.091153</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.09045</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.090546</v>
+        <v>0.080182</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -11799,42 +11799,42 @@
         <v/>
       </c>
       <c r="AC46" s="24" t="n">
-        <v>0.08964900000000001</v>
+        <v>0.08018</v>
       </c>
       <c r="AD46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AE46" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AG46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AH46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AI46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AJ46" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AL46" s="24" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AM46" s="24" t="n">
-        <v>0.090449</v>
+        <v>0.08018</v>
       </c>
       <c r="AN46" s="24" t="n">
-        <v>0.09055199999999999</v>
+        <v>0.08018</v>
       </c>
       <c r="AO46" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO36,"")</f>
@@ -12329,7 +12329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AO102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19523,78 +19523,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>41500</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>7785</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>70019</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-111398</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>118169</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>84575</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>39948</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>-77319</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>243178</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>-51019</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>154788</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
       <c r="Q78" s="18" t="n">
-        <v>-50504</v>
+        <v>3213</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>19866</v>
+        <v>1237</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>-77385</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>21658</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>-86365</v>
-      </c>
+        <v>2439</v>
+      </c>
+      <c r="U78" s="9" t="n"/>
       <c r="V78" s="18" t="n">
-        <v>-102684</v>
+        <v>839</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>146868</v>
+        <v>1697</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>38921</v>
-      </c>
-      <c r="Y78" s="18" t="n">
-        <v>-76775</v>
-      </c>
-      <c r="Z78" s="34" t="n">
-        <v>6330</v>
-      </c>
+        <v>1520</v>
+      </c>
+      <c r="Z78" s="9" t="n"/>
       <c r="AA78" s="18" t="n">
-        <v>-163853</v>
+        <v>2071</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>21461</v>
+        <v>2227</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -19616,78 +19575,47 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>136</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>277</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>424</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>429</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>761</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>1891</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>873</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>1117</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>1917</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>3064</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>6971</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
       <c r="Q79" s="18" t="n">
-        <v>2569</v>
+        <v>9949</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>2160</v>
+        <v>9576</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>2186</v>
+        <v>12419</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>1595</v>
+        <v>9953</v>
       </c>
       <c r="U79" s="34" t="n">
-        <v>8510</v>
+        <v>41897</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>748</v>
+        <v>9595</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>1033</v>
+        <v>9387</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>1431</v>
+        <v>8151</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>2076</v>
+        <v>8218</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>5288</v>
+        <v>35351</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>1613</v>
+        <v>7859</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>1610</v>
+        <v>8911</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -19709,78 +19637,47 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>0</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>1014</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>1025</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>501</v>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>508</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
       <c r="Q80" s="18" t="n">
-        <v>3</v>
+        <v>6961</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>418</v>
+        <v>6031</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>20</v>
+        <v>3116</v>
       </c>
       <c r="U80" s="34" t="n">
-        <v>441</v>
+        <v>18991</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>60</v>
+        <v>684</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>9</v>
+        <v>1617</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>0</v>
+        <v>5517</v>
       </c>
       <c r="Z80" s="34" t="n">
-        <v>69</v>
+        <v>8257</v>
       </c>
       <c r="AA80" s="18" t="n">
-        <v>709</v>
+        <v>2590</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>1</v>
+        <v>8458</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -19802,78 +19699,47 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>-6939</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-6772</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-7054</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>-5770</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-5149</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-24745</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-6529</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>-4305</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>-11778</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>-7418</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>-30030</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
       <c r="Q81" s="18" t="n">
-        <v>-7739</v>
+        <v>235</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>-7297</v>
+        <v>1154</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>-14500</v>
+        <v>1144</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>-9827</v>
+        <v>1205</v>
       </c>
       <c r="U81" s="34" t="n">
-        <v>-39363</v>
+        <v>3738</v>
       </c>
       <c r="V81" s="18" t="n">
-        <v>-9664</v>
+        <v>1554</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>-9041</v>
+        <v>2235</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>-8510</v>
+        <v>1139</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>-8595</v>
+        <v>1248</v>
       </c>
       <c r="Z81" s="34" t="n">
-        <v>-35810</v>
+        <v>6176</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>-7001</v>
+        <v>459</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>-8181</v>
+        <v>4088</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -19895,78 +19761,47 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>7771</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-5896</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>32203</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>8139</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-71061</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-36615</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>11920</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>60153</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-19725</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>34535</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>86883</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
       <c r="Q82" s="18" t="n">
-        <v>-12273</v>
+        <v>6197</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>4515</v>
+        <v>-239</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>192327</v>
+        <v>-4361</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>2965</v>
+        <v>2363</v>
       </c>
       <c r="U82" s="34" t="n">
-        <v>187534</v>
+        <v>3960</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>-10995</v>
+        <v>722</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-4995</v>
+        <v>7181</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>5853</v>
+        <v>-1813</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>7114</v>
+        <v>-854</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>-3023</v>
+        <v>5236</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>1182</v>
+        <v>11970</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>-3243</v>
+        <v>688</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -19988,78 +19823,47 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>1369</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>5163</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>46236</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>7436</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>5440</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>64275</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>1559</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>2198</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>2727</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>2997</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>9481</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
       <c r="Q83" s="18" t="n">
-        <v>1981</v>
+        <v>4853</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1593</v>
+        <v>2575</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>932</v>
+        <v>-3996</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>888</v>
+        <v>9452</v>
       </c>
       <c r="U83" s="34" t="n">
-        <v>5394</v>
+        <v>12884</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>1204</v>
+        <v>152</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>1766</v>
+        <v>6236</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>4627</v>
+        <v>-4577</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>3064</v>
+        <v>-5</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>10661</v>
+        <v>1806</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>2984</v>
+        <v>6241</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>2589</v>
+        <v>450</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -20081,78 +19885,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>1605</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>5362</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>46436</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>7635</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>5640</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>65073</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>1559</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>2902</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>2727</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>2964</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>10152</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
       <c r="Q84" s="18" t="n">
-        <v>2167</v>
+        <v>-6736</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>1780</v>
+        <v>-8339</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>1119</v>
-      </c>
-      <c r="T84" s="18" t="n">
-        <v>1075</v>
-      </c>
-      <c r="U84" s="34" t="n">
-        <v>6141</v>
-      </c>
+        <v>-9980</v>
+      </c>
+      <c r="U84" s="9" t="n"/>
       <c r="V84" s="18" t="n">
-        <v>1391</v>
+        <v>-8756</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>1952</v>
+        <v>-7690</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>4814</v>
-      </c>
-      <c r="Y84" s="18" t="n">
-        <v>3251</v>
-      </c>
-      <c r="Z84" s="34" t="n">
-        <v>11408</v>
-      </c>
+        <v>-6631</v>
+      </c>
+      <c r="Z84" s="9" t="n"/>
       <c r="AA84" s="18" t="n">
-        <v>3171</v>
+        <v>-5788</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>2775</v>
+        <v>-6684</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -20174,74 +19937,18 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>4</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>160</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>77</v>
-      </c>
       <c r="K85" s="9" t="n"/>
-      <c r="L85" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>181</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>48</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>453</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>704</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>148</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>383</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>281</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>838</v>
-      </c>
-      <c r="V85" s="18" t="n">
-        <v>340</v>
-      </c>
-      <c r="W85" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X85" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y85" s="18" t="n">
-        <v>2141</v>
-      </c>
-      <c r="Z85" s="34" t="n">
-        <v>2514</v>
-      </c>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
+      <c r="Z85" s="9" t="n"/>
       <c r="AA85" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB85" s="19" t="n">
-        <v>2</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="AB85" s="5" t="n"/>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="11" t="n"/>
@@ -20262,73 +19969,78 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>236</v>
+        <v>41500</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>199</v>
+        <v>7785</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>200</v>
+        <v>70019</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>199</v>
+        <v>-111398</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>200</v>
+        <v>118169</v>
       </c>
       <c r="K86" s="34" t="n">
-        <v>798</v>
+        <v>84575</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>0</v>
+        <v>39948</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>704</v>
+        <v>-77319</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="9" t="n"/>
+        <v>243178</v>
+      </c>
+      <c r="O86" s="18" t="n">
+        <v>-51019</v>
+      </c>
+      <c r="P86" s="34" t="n">
+        <v>154788</v>
+      </c>
       <c r="Q86" s="18" t="n">
-        <v>186</v>
+        <v>-50504</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>187</v>
+        <v>19866</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>187</v>
+        <v>-77385</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>187</v>
+        <v>21658</v>
       </c>
       <c r="U86" s="34" t="n">
-        <v>747</v>
+        <v>-86365</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>187</v>
+        <v>-102684</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>186</v>
+        <v>146868</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>187</v>
+        <v>38921</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>187</v>
+        <v>-76775</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>747</v>
+        <v>6330</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>187</v>
+        <v>-163853</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>186</v>
+        <v>21461</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -20350,55 +20062,79 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>52</v>
+        <v>277</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>424</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>13</v>
+        <v>429</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="K87" s="9" t="n"/>
+        <v>761</v>
+      </c>
+      <c r="K87" s="34" t="n">
+        <v>1891</v>
+      </c>
       <c r="L87" s="18" t="n">
-        <v>13</v>
+        <v>873</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>13</v>
+        <v>1117</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>13</v>
+        <v>1917</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>13</v>
+        <v>3064</v>
       </c>
       <c r="P87" s="34" t="n">
-        <v>52</v>
+        <v>6971</v>
       </c>
       <c r="Q87" s="18" t="n">
-        <v>0</v>
+        <v>2569</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>0</v>
+        <v>2186</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>0</v>
+        <v>1595</v>
       </c>
       <c r="U87" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="9" t="n"/>
-      <c r="AB87" s="5" t="n"/>
+        <v>8510</v>
+      </c>
+      <c r="V87" s="18" t="n">
+        <v>748</v>
+      </c>
+      <c r="W87" s="18" t="n">
+        <v>1033</v>
+      </c>
+      <c r="X87" s="18" t="n">
+        <v>1431</v>
+      </c>
+      <c r="Y87" s="18" t="n">
+        <v>2076</v>
+      </c>
+      <c r="Z87" s="34" t="n">
+        <v>5288</v>
+      </c>
+      <c r="AA87" s="18" t="n">
+        <v>1613</v>
+      </c>
+      <c r="AB87" s="19" t="n">
+        <v>1610</v>
+      </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -20419,78 +20155,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>-5966</v>
+        <v>0</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>-3067</v>
+        <v>10</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-83474</v>
+        <v>1014</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>48025</v>
+        <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>-18835</v>
+        <v>1</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>-57351</v>
+        <v>1025</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>-3374</v>
+        <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>-3866</v>
+        <v>501</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>-4223</v>
+        <v>7</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>20657</v>
+        <v>0</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>9194</v>
+        <v>508</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>-4568</v>
+        <v>3</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>-53406</v>
+        <v>418</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>-173571</v>
+        <v>0</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>-13289</v>
+        <v>20</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>-244834</v>
+        <v>441</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>-13314</v>
+        <v>0</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>-48115</v>
+        <v>60</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>-17163</v>
+        <v>9</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>199224</v>
+        <v>0</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>120632</v>
+        <v>69</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>-11116</v>
+        <v>709</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>69489</v>
+        <v>1</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -20512,78 +20248,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>43305</v>
+        <v>-6939</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>-1178</v>
+        <v>-6772</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>18748</v>
+        <v>-7054</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>-55234</v>
+        <v>-5770</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>28273</v>
+        <v>-5149</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>-9391</v>
+        <v>-24745</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>48494</v>
+        <v>-6529</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>-21032</v>
+        <v>-4305</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>219230</v>
+        <v>-11778</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>4173</v>
+        <v>-7418</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>250865</v>
+        <v>-30030</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>-67345</v>
+        <v>-7739</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>-29025</v>
+        <v>-7297</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>-58629</v>
+        <v>-14500</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>11334</v>
+        <v>-9827</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>-143665</v>
+        <v>-39363</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>-126993</v>
+        <v>-9664</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>93758</v>
+        <v>-9041</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>27611</v>
+        <v>-8510</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>129563</v>
+        <v>-8595</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>123939</v>
+        <v>-35810</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>-173787</v>
+        <v>-7001</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>87707</v>
+        <v>-8181</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -20605,78 +20341,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>42932</v>
+        <v>7771</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>117115</v>
+        <v>-5896</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>19045</v>
+        <v>32203</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>-53426</v>
+        <v>8139</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>19499</v>
+        <v>-71061</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>102233</v>
+        <v>-36615</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>151777</v>
+        <v>11920</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>-22214</v>
+        <v>60153</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>224614</v>
+        <v>-19725</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>-3920</v>
+        <v>34535</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>350257</v>
+        <v>86883</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>286569</v>
+        <v>-12273</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>-29563</v>
+        <v>4515</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>-61798</v>
+        <v>192327</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>11920</v>
+        <v>2965</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>207128</v>
+        <v>187534</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>80370</v>
+        <v>-10995</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>89820</v>
+        <v>-4995</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>31957</v>
+        <v>5853</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>130059</v>
+        <v>7114</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>332206</v>
+        <v>-3023</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>163666</v>
+        <v>1182</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>86081</v>
+        <v>-3243</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -20698,45 +20434,78 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>1369</v>
       </c>
       <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>5163</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>46236</v>
+      </c>
       <c r="I91" s="18" t="n">
-        <v>785</v>
-      </c>
-      <c r="K91" s="9" t="n"/>
+        <v>7436</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>5440</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>64275</v>
+      </c>
+      <c r="L91" s="18" t="n">
+        <v>1559</v>
+      </c>
+      <c r="M91" s="18" t="n">
+        <v>2198</v>
+      </c>
       <c r="N91" s="18" t="n">
-        <v>0</v>
+        <v>2727</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>4285</v>
-      </c>
-      <c r="P91" s="9" t="n"/>
+        <v>2997</v>
+      </c>
+      <c r="P91" s="34" t="n">
+        <v>9481</v>
+      </c>
+      <c r="Q91" s="18" t="n">
+        <v>1981</v>
+      </c>
+      <c r="R91" s="18" t="n">
+        <v>1593</v>
+      </c>
       <c r="S91" s="18" t="n">
-        <v>664966</v>
-      </c>
-      <c r="U91" s="9" t="n"/>
+        <v>932</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>888</v>
+      </c>
+      <c r="U91" s="34" t="n">
+        <v>5394</v>
+      </c>
       <c r="V91" s="18" t="n">
-        <v>2002</v>
+        <v>1204</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>0</v>
+        <v>1766</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>3030</v>
+        <v>4627</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>1</v>
+        <v>3064</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>5033</v>
+        <v>10661</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>0</v>
+        <v>2984</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>25000</v>
+        <v>2589</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -20758,27 +20527,79 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>1605</v>
       </c>
       <c r="F92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>5362</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>46436</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>7635</v>
+      </c>
       <c r="J92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9" t="n"/>
+        <v>5640</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>65073</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>1559</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>2902</v>
+      </c>
+      <c r="N92" s="18" t="n">
+        <v>2727</v>
+      </c>
       <c r="O92" s="18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="P92" s="9" t="n"/>
-      <c r="U92" s="9" t="n"/>
+        <v>2964</v>
+      </c>
+      <c r="P92" s="34" t="n">
+        <v>10152</v>
+      </c>
+      <c r="Q92" s="18" t="n">
+        <v>2167</v>
+      </c>
+      <c r="R92" s="18" t="n">
+        <v>1780</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>1119</v>
+      </c>
+      <c r="T92" s="18" t="n">
+        <v>1075</v>
+      </c>
+      <c r="U92" s="34" t="n">
+        <v>6141</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>1391</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>1952</v>
+      </c>
       <c r="X92" s="18" t="n">
-        <v>0</v>
+        <v>4814</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="9" t="n"/>
-      <c r="AB92" s="5" t="n"/>
+        <v>3251</v>
+      </c>
+      <c r="Z92" s="34" t="n">
+        <v>11408</v>
+      </c>
+      <c r="AA92" s="18" t="n">
+        <v>3171</v>
+      </c>
+      <c r="AB92" s="19" t="n">
+        <v>2775</v>
+      </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -20799,33 +20620,73 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="F93" s="9" t="n"/>
+      <c r="G93" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="I93" s="18" t="n">
+        <v>77</v>
+      </c>
       <c r="K93" s="9" t="n"/>
-      <c r="P93" s="9" t="n"/>
-      <c r="U93" s="9" t="n"/>
+      <c r="L93" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="M93" s="18" t="n">
+        <v>181</v>
+      </c>
+      <c r="N93" s="18" t="n">
+        <v>48</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>453</v>
+      </c>
+      <c r="P93" s="34" t="n">
+        <v>704</v>
+      </c>
+      <c r="Q93" s="18" t="n">
+        <v>148</v>
+      </c>
+      <c r="R93" s="18" t="n">
+        <v>383</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>281</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="U93" s="34" t="n">
+        <v>838</v>
+      </c>
       <c r="V93" s="18" t="n">
-        <v>7361</v>
+        <v>340</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>374386</v>
+        <v>17</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>8588</v>
+        <v>16</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>7361</v>
+        <v>2141</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>397696</v>
+        <v>2514</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>7369</v>
+        <v>16</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>269100</v>
+        <v>2</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -20847,21 +20708,74 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>236</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>199</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>199</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>798</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>704</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P94" s="9" t="n"/>
-      <c r="U94" s="9" t="n"/>
+      <c r="Q94" s="18" t="n">
+        <v>186</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>187</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>187</v>
+      </c>
+      <c r="T94" s="18" t="n">
+        <v>187</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>747</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>187</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>186</v>
+      </c>
       <c r="X94" s="18" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+        <v>187</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>747</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>187</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>186</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -20875,6 +20789,538 @@
       <c r="AM94" s="10" t="n"/>
       <c r="AN94" s="10" t="n"/>
       <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="L95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="O95" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="P95" s="34" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="9" t="n"/>
+      <c r="AB95" s="5" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>-5966</v>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>-3067</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>-83474</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>48025</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>-18835</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>-57351</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>-3374</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>-3866</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>-4223</v>
+      </c>
+      <c r="O96" s="18" t="n">
+        <v>20657</v>
+      </c>
+      <c r="P96" s="34" t="n">
+        <v>9194</v>
+      </c>
+      <c r="Q96" s="18" t="n">
+        <v>-4568</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>-53406</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>-173571</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>-13289</v>
+      </c>
+      <c r="U96" s="34" t="n">
+        <v>-244834</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>-13314</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>-48115</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>-17163</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>199224</v>
+      </c>
+      <c r="Z96" s="34" t="n">
+        <v>120632</v>
+      </c>
+      <c r="AA96" s="18" t="n">
+        <v>-11116</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>69489</v>
+      </c>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>43305</v>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>-1178</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>18748</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>-55234</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>28273</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>-9391</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>48494</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>-21032</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>219230</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>4173</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>250865</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>-67345</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>-29025</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>-58629</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>11334</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>-143665</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>-126993</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>93758</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>27611</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>129563</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>123939</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>-173787</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>87707</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>42932</v>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>117115</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>19045</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>-53426</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>19499</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>102233</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>151777</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>-22214</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>224614</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>-3920</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>350257</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>286569</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>-29563</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>-61798</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>11920</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>207128</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>80370</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>89820</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>31957</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>130059</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>332206</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>163666</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>86081</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="I99" s="18" t="n">
+        <v>785</v>
+      </c>
+      <c r="K99" s="9" t="n"/>
+      <c r="N99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>4285</v>
+      </c>
+      <c r="P99" s="9" t="n"/>
+      <c r="S99" s="18" t="n">
+        <v>664966</v>
+      </c>
+      <c r="U99" s="9" t="n"/>
+      <c r="V99" s="18" t="n">
+        <v>2002</v>
+      </c>
+      <c r="W99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" s="18" t="n">
+        <v>3030</v>
+      </c>
+      <c r="Y99" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="34" t="n">
+        <v>5033</v>
+      </c>
+      <c r="AA99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="J100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
+      <c r="O100" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="P100" s="9" t="n"/>
+      <c r="U100" s="9" t="n"/>
+      <c r="X100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="9" t="n"/>
+      <c r="AB100" s="5" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="P101" s="9" t="n"/>
+      <c r="U101" s="9" t="n"/>
+      <c r="V101" s="18" t="n">
+        <v>7361</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>374386</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>8588</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>7361</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>397696</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>7369</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>269100</v>
+      </c>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+      <c r="P102" s="9" t="n"/>
+      <c r="U102" s="9" t="n"/>
+      <c r="X102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z102" s="9" t="n"/>
+      <c r="AB102" s="5" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21135,7 +21581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34084,7 +34530,7 @@
         <v>15.63</v>
       </c>
       <c r="AC32" s="20" t="n">
-        <v>7.3</v>
+        <v>7.53</v>
       </c>
       <c r="AD32" s="20">
         <f>IFERROR(Y32*(1+변수!AD41),"")</f>
@@ -35467,7 +35913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FE71"/>
+  <dimension ref="A1:FE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -39224,2293 +39670,2280 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>cohort:②BEP</t>
+          <t>cohort:⑤초호황</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>코호트 ②BEP</t>
+          <t>코호트 ⑤초호황</t>
         </is>
       </c>
       <c r="AI10" s="26" t="n">
         <v>0.396</v>
       </c>
       <c r="AJ10" s="26" t="n">
-        <v>3.956</v>
+        <v>17.772</v>
       </c>
       <c r="AK10" s="26" t="n">
-        <v>4</v>
+        <v>46.688</v>
       </c>
       <c r="AL10" s="26" t="n">
-        <v>4.044</v>
+        <v>58.218</v>
       </c>
       <c r="AM10" s="26" t="n">
-        <v>4.044</v>
+        <v>99.367</v>
       </c>
       <c r="AN10" s="26" t="n">
-        <v>3.956</v>
+        <v>97.20699999999999</v>
       </c>
       <c r="AO10" s="26" t="n">
-        <v>4</v>
+        <v>98.28700000000001</v>
       </c>
       <c r="AP10" s="26" t="n">
-        <v>4.044</v>
+        <v>99.367</v>
       </c>
       <c r="AQ10" s="26" t="n">
-        <v>4.044</v>
+        <v>99.367</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>4</v>
+        <v>98.28700000000001</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>4</v>
+        <v>98.28700000000001</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>4.044</v>
+        <v>73.946</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>2.989</v>
+        <v>57.154</v>
+      </c>
+      <c r="AV10" s="26" t="n">
+        <v>45.164</v>
+      </c>
+      <c r="AW10" s="26" t="n">
+        <v>15.055</v>
       </c>
       <c r="EG10" s="26" t="n">
         <v>0.396</v>
       </c>
       <c r="EH10" s="26" t="n">
-        <v>16.044</v>
+        <v>222.045</v>
       </c>
       <c r="EI10" s="26" t="n">
-        <v>16.044</v>
+        <v>394.228</v>
       </c>
       <c r="EJ10" s="26" t="n">
-        <v>15.033</v>
+        <v>327.674</v>
+      </c>
+      <c r="EK10" s="26" t="n">
+        <v>60.219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>cohort:③중마진</t>
+          <t>hedge_ratio</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>코호트 ③중마진</t>
-        </is>
-      </c>
-      <c r="AJ11" s="26" t="n">
-        <v>13.816</v>
-      </c>
-      <c r="AK11" s="26" t="n">
-        <v>42.688</v>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>54.174</v>
-      </c>
-      <c r="AM11" s="26" t="n">
-        <v>95.324</v>
-      </c>
-      <c r="AN11" s="26" t="n">
-        <v>93.251</v>
-      </c>
-      <c r="AO11" s="26" t="n">
-        <v>94.28700000000001</v>
-      </c>
-      <c r="AP11" s="26" t="n">
-        <v>95.324</v>
-      </c>
-      <c r="AQ11" s="26" t="n">
-        <v>95.324</v>
-      </c>
-      <c r="AR11" s="26" t="n">
-        <v>94.28700000000001</v>
-      </c>
-      <c r="AS11" s="26" t="n">
-        <v>94.28700000000001</v>
-      </c>
-      <c r="AT11" s="26" t="n">
-        <v>69.902</v>
-      </c>
-      <c r="AU11" s="26" t="n">
-        <v>54.165</v>
-      </c>
-      <c r="AV11" s="26" t="n">
-        <v>45.164</v>
-      </c>
-      <c r="AW11" s="26" t="n">
-        <v>15.055</v>
-      </c>
-      <c r="EH11" s="26" t="n">
-        <v>206.002</v>
-      </c>
-      <c r="EI11" s="26" t="n">
-        <v>378.186</v>
-      </c>
-      <c r="EJ11" s="26" t="n">
-        <v>312.641</v>
-      </c>
-      <c r="EK11" s="26" t="n">
-        <v>60.219</v>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AA11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AF11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AK11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AM11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AO11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AS11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AU11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AV11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AW11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AX11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AY11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AZ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BA11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BB11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BC11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BE11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BG11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BH11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BI11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BJ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BN11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BO11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BP11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BQ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BR11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BT11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BU11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BV11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BW11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BX11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BY11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BZ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CA11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CC11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CD11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CE11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CF11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CG11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CH11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CI11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CJ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CK11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CL11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CM11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CN11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CO11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CP11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CQ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CR11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CS11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CT11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CU11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CV11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CW11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CX11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CY11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CZ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DA11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DB11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DC11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DD11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DE11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DG11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DH11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DI11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DJ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DK11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DL11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DM11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DN11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DO11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DP11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DQ11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DR11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DS11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DT11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DU11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DV11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DW11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DX11" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DY11" s="21" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>hedge_ratio</t>
+          <t>hedge_rate</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="W12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="X12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Z12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AA12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AB12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AD12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AF12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AG12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AH12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AI12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AJ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AK12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AL12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AM12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AN12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AO12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AQ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AS12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AT12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AU12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AV12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AW12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AX12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AY12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AZ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BA12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BB12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BC12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BD12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BE12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BF12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BG12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BH12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BI12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BJ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BM12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BN12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BO12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BP12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BQ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BR12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BS12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BT12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BU12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BV12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BW12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BX12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BY12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BZ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CA12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CB12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CC12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CD12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CE12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CF12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CG12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CH12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CI12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CJ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CK12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CL12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CM12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CN12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CO12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CP12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CQ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CR12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CS12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CT12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CU12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CV12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CW12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CX12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CY12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CZ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DA12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DB12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DC12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DD12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DE12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DF12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DG12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DH12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DI12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DJ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DK12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DL12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DM12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DN12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DO12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DP12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DQ12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DR12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DS12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DT12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DU12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DV12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DW12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DX12" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DY12" s="21" t="n">
-        <v>0.7</v>
+          <t>헤지환율</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1080.48</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>1080.48</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1080.48</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1085.22</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>1106.95</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>1115.14</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>1116.26</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>1130.69</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>1130.69</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>1130.69</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>1125.98</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>1123.3</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>1122.51</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>1124.2</v>
+      </c>
+      <c r="S12" s="13" t="n">
+        <v>1126.74</v>
+      </c>
+      <c r="T12" s="13" t="n">
+        <v>1127.57</v>
+      </c>
+      <c r="U12" s="13" t="n">
+        <v>1127.57</v>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>1131.77</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>1145.89</v>
+      </c>
+      <c r="X12" s="13" t="n">
+        <v>1170.82</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>1183.49</v>
+      </c>
+      <c r="Z12" s="13" t="n">
+        <v>1206.46</v>
+      </c>
+      <c r="AA12" s="13" t="n">
+        <v>1220.44</v>
+      </c>
+      <c r="AB12" s="13" t="n">
+        <v>1221.79</v>
+      </c>
+      <c r="AC12" s="13" t="n">
+        <v>1227.91</v>
+      </c>
+      <c r="AD12" s="13" t="n">
+        <v>1228</v>
+      </c>
+      <c r="AE12" s="13" t="n">
+        <v>1228.67</v>
+      </c>
+      <c r="AF12" s="13" t="n">
+        <v>1233.83</v>
+      </c>
+      <c r="AG12" s="13" t="n">
+        <v>1249.2</v>
+      </c>
+      <c r="AH12" s="13" t="n">
+        <v>1254.23</v>
+      </c>
+      <c r="AI12" s="13" t="n">
+        <v>1267.98</v>
+      </c>
+      <c r="AJ12" s="13" t="n">
+        <v>1322.94</v>
+      </c>
+      <c r="AK12" s="13" t="n">
+        <v>1377.69</v>
+      </c>
+      <c r="AL12" s="13" t="n">
+        <v>1386.22</v>
+      </c>
+      <c r="AM12" s="13" t="n">
+        <v>1391.21</v>
+      </c>
+      <c r="AN12" s="13" t="n">
+        <v>1404.32</v>
+      </c>
+      <c r="AO12" s="13" t="n">
+        <v>1421.93</v>
+      </c>
+      <c r="AP12" s="13" t="n">
+        <v>1427.26</v>
+      </c>
+      <c r="AQ12" s="13" t="n">
+        <v>1432.54</v>
+      </c>
+      <c r="AR12" s="13" t="n">
+        <v>1439.9</v>
+      </c>
+      <c r="AS12" s="13" t="n">
+        <v>1446.89</v>
+      </c>
+      <c r="AT12" s="13" t="n">
+        <v>1448.2</v>
+      </c>
+      <c r="AU12" s="13" t="n">
+        <v>1445.63</v>
+      </c>
+      <c r="AV12" s="13" t="n">
+        <v>1442.16</v>
+      </c>
+      <c r="AW12" s="13" t="n">
+        <v>1446.33</v>
+      </c>
+      <c r="AX12" s="13" t="n">
+        <v>1450.09</v>
+      </c>
+      <c r="AY12" s="13" t="n">
+        <v>1455.1</v>
+      </c>
+      <c r="AZ12" s="13" t="n">
+        <v>1461.49</v>
+      </c>
+      <c r="BA12" s="13" t="n">
+        <v>1462.34</v>
+      </c>
+      <c r="BB12" s="13" t="n">
+        <v>1461.64</v>
+      </c>
+      <c r="BC12" s="13" t="n">
+        <v>1427.72</v>
+      </c>
+      <c r="BD12" s="13" t="n">
+        <v>1461.27</v>
+      </c>
+      <c r="BE12" s="13" t="n">
+        <v>1466.54</v>
+      </c>
+      <c r="BF12" s="13" t="n">
+        <v>1463.38</v>
+      </c>
+      <c r="BG12" s="13" t="n">
+        <v>1463.38</v>
+      </c>
+      <c r="BH12" s="13" t="n">
+        <v>1463.38</v>
+      </c>
+      <c r="BI12" s="13" t="n">
+        <v>1446.27</v>
+      </c>
+      <c r="BJ12" s="13" t="n">
+        <v>1439.41</v>
+      </c>
+      <c r="BK12" s="13" t="n">
+        <v>1439.41</v>
+      </c>
+      <c r="BL12" s="13" t="n">
+        <v>1439.41</v>
+      </c>
+      <c r="BM12" s="13" t="n">
+        <v>1439.41</v>
+      </c>
+      <c r="BN12" s="13" t="n">
+        <v>1442.43</v>
+      </c>
+      <c r="BO12" s="13" t="n">
+        <v>1451.59</v>
+      </c>
+      <c r="BP12" s="13" t="n">
+        <v>1451.59</v>
+      </c>
+      <c r="BQ12" s="13" t="n">
+        <v>1454.84</v>
+      </c>
+      <c r="BR12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BS12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BT12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BU12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BV12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BW12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BX12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BY12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="BZ12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CA12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CB12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CC12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CD12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CE12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CF12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CG12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CH12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CI12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CJ12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CK12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CL12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CM12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CN12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CO12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CP12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CQ12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CR12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CS12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CT12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CU12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CV12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CW12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CX12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CY12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="CZ12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DA12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DB12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DC12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DD12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DE12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DF12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DG12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DH12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DI12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DJ12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DK12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DL12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DM12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DN12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DO12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DP12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DQ12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DR12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DS12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DT12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DU12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DV12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DW12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DX12" s="13" t="n">
+        <v>1466.12</v>
+      </c>
+      <c r="DY12" s="13" t="n">
+        <v>1466.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>hedge_rate</t>
+          <t>spot_assumed</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>헤지환율</t>
+          <t>건조시점 환율(가정)</t>
         </is>
       </c>
       <c r="E13" s="13" t="n">
         <v>1080.48</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1080.48</v>
+        <v>1121.86</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1080.48</v>
+        <v>1127.53</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>1085.22</v>
+        <v>1125.78</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>1106.95</v>
+        <v>1167.69</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1115.14</v>
+        <v>1193.96</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1116.26</v>
+        <v>1176.23</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1130.69</v>
+        <v>1193.92</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1130.69</v>
+        <v>1219.69</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1130.69</v>
+        <v>1187.81</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1125.98</v>
+        <v>1117.97</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1123.3</v>
+        <v>1114.99</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1122.51</v>
+        <v>1121.13</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1124.2</v>
+        <v>1159.91</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1126.74</v>
+        <v>1183.5</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1127.57</v>
+        <v>1205.78</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1127.57</v>
+        <v>1262.09</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1131.77</v>
+        <v>1341.93</v>
       </c>
       <c r="W13" s="13" t="n">
-        <v>1145.89</v>
+        <v>1360.12</v>
       </c>
       <c r="X13" s="13" t="n">
-        <v>1170.82</v>
+        <v>1276.95</v>
       </c>
       <c r="Y13" s="13" t="n">
-        <v>1183.49</v>
+        <v>1315.69</v>
       </c>
       <c r="Z13" s="13" t="n">
-        <v>1206.46</v>
+        <v>1313.62</v>
       </c>
       <c r="AA13" s="13" t="n">
-        <v>1220.44</v>
+        <v>1322.01</v>
       </c>
       <c r="AB13" s="13" t="n">
-        <v>1221.79</v>
+        <v>1330.14</v>
       </c>
       <c r="AC13" s="13" t="n">
-        <v>1227.91</v>
+        <v>1371.28</v>
       </c>
       <c r="AD13" s="13" t="n">
-        <v>1228</v>
+        <v>1356.22</v>
       </c>
       <c r="AE13" s="13" t="n">
-        <v>1228.67</v>
+        <v>1396.3</v>
       </c>
       <c r="AF13" s="13" t="n">
-        <v>1233.83</v>
+        <v>1452.28</v>
       </c>
       <c r="AG13" s="13" t="n">
-        <v>1249.2</v>
+        <v>1398.52</v>
       </c>
       <c r="AH13" s="13" t="n">
-        <v>1254.23</v>
+        <v>1386.95</v>
       </c>
       <c r="AI13" s="13" t="n">
-        <v>1267.98</v>
+        <v>1449.19</v>
       </c>
       <c r="AJ13" s="13" t="n">
-        <v>1322.94</v>
+        <v>1466.12</v>
       </c>
       <c r="AK13" s="13" t="n">
-        <v>1377.69</v>
+        <v>1501.75</v>
       </c>
       <c r="AL13" s="13" t="n">
-        <v>1386.22</v>
+        <v>1419.72</v>
       </c>
       <c r="AM13" s="13" t="n">
-        <v>1391.21</v>
+        <v>1353.36</v>
       </c>
       <c r="AN13" s="13" t="n">
-        <v>1404.32</v>
+        <v>1353.36</v>
       </c>
       <c r="AO13" s="13" t="n">
-        <v>1421.93</v>
+        <v>1353.36</v>
       </c>
       <c r="AP13" s="13" t="n">
-        <v>1427.26</v>
+        <v>1353.36</v>
       </c>
       <c r="AQ13" s="13" t="n">
-        <v>1432.54</v>
+        <v>1353.36</v>
       </c>
       <c r="AR13" s="13" t="n">
-        <v>1439.9</v>
+        <v>1353.36</v>
       </c>
       <c r="AS13" s="13" t="n">
-        <v>1446.89</v>
+        <v>1353.36</v>
       </c>
       <c r="AT13" s="13" t="n">
-        <v>1448.2</v>
+        <v>1353.36</v>
       </c>
       <c r="AU13" s="13" t="n">
-        <v>1445.63</v>
+        <v>1353.36</v>
       </c>
       <c r="AV13" s="13" t="n">
-        <v>1442.16</v>
+        <v>1353.36</v>
       </c>
       <c r="AW13" s="13" t="n">
-        <v>1446.33</v>
+        <v>1353.36</v>
       </c>
       <c r="AX13" s="13" t="n">
-        <v>1450.09</v>
+        <v>1353.36</v>
       </c>
       <c r="AY13" s="13" t="n">
-        <v>1455.1</v>
+        <v>1353.36</v>
       </c>
       <c r="AZ13" s="13" t="n">
-        <v>1461.49</v>
+        <v>1353.36</v>
       </c>
       <c r="BA13" s="13" t="n">
-        <v>1462.34</v>
+        <v>1353.36</v>
       </c>
       <c r="BB13" s="13" t="n">
-        <v>1461.64</v>
+        <v>1353.36</v>
       </c>
       <c r="BC13" s="13" t="n">
-        <v>1427.72</v>
+        <v>1353.36</v>
       </c>
       <c r="BD13" s="13" t="n">
-        <v>1461.27</v>
+        <v>1353.36</v>
       </c>
       <c r="BE13" s="13" t="n">
-        <v>1466.54</v>
+        <v>1353.36</v>
       </c>
       <c r="BF13" s="13" t="n">
-        <v>1463.38</v>
+        <v>1353.36</v>
       </c>
       <c r="BG13" s="13" t="n">
-        <v>1463.38</v>
+        <v>1353.36</v>
       </c>
       <c r="BH13" s="13" t="n">
-        <v>1463.38</v>
+        <v>1353.36</v>
       </c>
       <c r="BI13" s="13" t="n">
-        <v>1446.27</v>
+        <v>1353.36</v>
       </c>
       <c r="BJ13" s="13" t="n">
-        <v>1439.41</v>
+        <v>1353.36</v>
       </c>
       <c r="BK13" s="13" t="n">
-        <v>1439.41</v>
+        <v>1353.36</v>
       </c>
       <c r="BL13" s="13" t="n">
-        <v>1439.41</v>
+        <v>1353.36</v>
       </c>
       <c r="BM13" s="13" t="n">
-        <v>1439.41</v>
+        <v>1353.36</v>
       </c>
       <c r="BN13" s="13" t="n">
-        <v>1442.43</v>
+        <v>1353.36</v>
       </c>
       <c r="BO13" s="13" t="n">
-        <v>1451.59</v>
+        <v>1353.36</v>
       </c>
       <c r="BP13" s="13" t="n">
-        <v>1451.59</v>
+        <v>1353.36</v>
       </c>
       <c r="BQ13" s="13" t="n">
-        <v>1454.84</v>
+        <v>1353.36</v>
       </c>
       <c r="BR13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BS13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BT13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BU13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BV13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BW13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BX13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BY13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="BZ13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CA13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CB13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CC13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CD13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CE13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CF13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CG13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CH13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CI13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CJ13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CK13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CL13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CM13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CN13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CO13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CP13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CQ13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CR13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CS13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CT13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CU13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CV13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CW13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CX13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CY13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="CZ13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DA13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DB13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DC13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DD13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DE13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DF13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DG13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DH13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DI13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DJ13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DK13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DL13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DM13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DN13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DO13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DP13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DQ13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DR13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DS13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DT13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DU13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DV13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DW13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DX13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
       <c r="DY13" s="13" t="n">
-        <v>1466.12</v>
+        <v>1353.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>spot_assumed</t>
+          <t>applied_rate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>건조시점 환율(가정)</t>
+          <t>적용환율</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
         <v>1080.48</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1121.86</v>
+        <v>1092.89</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>1127.53</v>
+        <v>1094.6</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>1125.78</v>
+        <v>1097.39</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>1167.69</v>
+        <v>1125.17</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>1193.96</v>
+        <v>1138.79</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>1176.23</v>
+        <v>1134.25</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>1193.92</v>
+        <v>1149.66</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>1219.69</v>
+        <v>1157.39</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>1187.81</v>
+        <v>1147.83</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1117.97</v>
+        <v>1123.57</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>1114.99</v>
+        <v>1120.81</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>1121.13</v>
+        <v>1122.1</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>1159.91</v>
+        <v>1134.91</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>1183.5</v>
+        <v>1143.77</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>1205.78</v>
+        <v>1151.03</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>1262.09</v>
+        <v>1167.92</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>1341.93</v>
+        <v>1194.81</v>
       </c>
       <c r="W14" s="13" t="n">
-        <v>1360.12</v>
+        <v>1210.16</v>
       </c>
       <c r="X14" s="13" t="n">
-        <v>1276.95</v>
+        <v>1202.66</v>
       </c>
       <c r="Y14" s="13" t="n">
-        <v>1315.69</v>
+        <v>1223.15</v>
       </c>
       <c r="Z14" s="13" t="n">
-        <v>1313.62</v>
+        <v>1238.61</v>
       </c>
       <c r="AA14" s="13" t="n">
-        <v>1322.01</v>
+        <v>1250.91</v>
       </c>
       <c r="AB14" s="13" t="n">
-        <v>1330.14</v>
+        <v>1254.3</v>
       </c>
       <c r="AC14" s="13" t="n">
-        <v>1371.28</v>
+        <v>1270.92</v>
       </c>
       <c r="AD14" s="13" t="n">
-        <v>1356.22</v>
+        <v>1266.46</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>1396.3</v>
+        <v>1278.96</v>
       </c>
       <c r="AF14" s="13" t="n">
-        <v>1452.28</v>
+        <v>1299.36</v>
       </c>
       <c r="AG14" s="13" t="n">
-        <v>1398.52</v>
+        <v>1294</v>
       </c>
       <c r="AH14" s="13" t="n">
-        <v>1386.95</v>
+        <v>1294.04</v>
       </c>
       <c r="AI14" s="13" t="n">
-        <v>1449.19</v>
+        <v>1322.34</v>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>1466.12</v>
+        <v>1365.89</v>
       </c>
       <c r="AK14" s="13" t="n">
-        <v>1501.75</v>
+        <v>1414.91</v>
       </c>
       <c r="AL14" s="13" t="n">
-        <v>1419.72</v>
+        <v>1396.27</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1379.86</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1389.03</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1401.36</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1405.09</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1408.79</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.94</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1418.83</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1419.75</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1417.95</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1415.52</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1418.44</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1421.07</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1424.58</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1429.05</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1429.64</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1429.16</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1405.41</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1428.89</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.58</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1430.38</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1430.38</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1430.38</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1418.39</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.59</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.59</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.59</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.59</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1415.71</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.12</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.12</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1424.4</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1353.36</v>
+        <v>1432.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>applied_rate</t>
+          <t>hedged_krw_m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>적용환율</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>1080.48</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>1092.89</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>1094.6</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>1097.39</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>1125.17</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>1138.79</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>1134.25</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>1149.66</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>1157.39</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>1147.83</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>1123.57</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>1120.81</v>
-      </c>
-      <c r="Q15" s="13" t="n">
-        <v>1122.1</v>
-      </c>
-      <c r="R15" s="13" t="n">
-        <v>1134.91</v>
-      </c>
-      <c r="S15" s="13" t="n">
-        <v>1143.77</v>
-      </c>
-      <c r="T15" s="13" t="n">
-        <v>1151.03</v>
-      </c>
-      <c r="U15" s="13" t="n">
-        <v>1167.92</v>
-      </c>
-      <c r="V15" s="13" t="n">
-        <v>1194.81</v>
-      </c>
-      <c r="W15" s="13" t="n">
-        <v>1210.16</v>
-      </c>
-      <c r="X15" s="13" t="n">
-        <v>1202.66</v>
-      </c>
-      <c r="Y15" s="13" t="n">
-        <v>1223.15</v>
-      </c>
-      <c r="Z15" s="13" t="n">
-        <v>1238.61</v>
-      </c>
-      <c r="AA15" s="13" t="n">
-        <v>1250.91</v>
-      </c>
-      <c r="AB15" s="13" t="n">
-        <v>1254.3</v>
-      </c>
-      <c r="AC15" s="13" t="n">
-        <v>1270.92</v>
-      </c>
-      <c r="AD15" s="13" t="n">
-        <v>1266.46</v>
-      </c>
-      <c r="AE15" s="13" t="n">
-        <v>1278.96</v>
-      </c>
-      <c r="AF15" s="13" t="n">
-        <v>1299.36</v>
-      </c>
-      <c r="AG15" s="13" t="n">
-        <v>1294</v>
-      </c>
-      <c r="AH15" s="13" t="n">
-        <v>1294.04</v>
-      </c>
-      <c r="AI15" s="13" t="n">
-        <v>1322.34</v>
-      </c>
-      <c r="AJ15" s="13" t="n">
-        <v>1365.89</v>
-      </c>
-      <c r="AK15" s="13" t="n">
-        <v>1414.91</v>
-      </c>
-      <c r="AL15" s="13" t="n">
-        <v>1396.27</v>
-      </c>
-      <c r="AM15" s="13" t="n">
-        <v>1379.86</v>
-      </c>
-      <c r="AN15" s="13" t="n">
-        <v>1389.03</v>
-      </c>
-      <c r="AO15" s="13" t="n">
-        <v>1401.36</v>
-      </c>
-      <c r="AP15" s="13" t="n">
-        <v>1405.09</v>
-      </c>
-      <c r="AQ15" s="13" t="n">
-        <v>1408.79</v>
-      </c>
-      <c r="AR15" s="13" t="n">
-        <v>1413.94</v>
-      </c>
-      <c r="AS15" s="13" t="n">
-        <v>1418.83</v>
-      </c>
-      <c r="AT15" s="13" t="n">
-        <v>1419.75</v>
-      </c>
-      <c r="AU15" s="13" t="n">
-        <v>1417.95</v>
-      </c>
-      <c r="AV15" s="13" t="n">
-        <v>1415.52</v>
-      </c>
-      <c r="AW15" s="13" t="n">
-        <v>1418.44</v>
-      </c>
-      <c r="AX15" s="13" t="n">
-        <v>1421.07</v>
-      </c>
-      <c r="AY15" s="13" t="n">
-        <v>1424.58</v>
-      </c>
-      <c r="AZ15" s="13" t="n">
-        <v>1429.05</v>
-      </c>
-      <c r="BA15" s="13" t="n">
-        <v>1429.64</v>
-      </c>
-      <c r="BB15" s="13" t="n">
-        <v>1429.16</v>
-      </c>
-      <c r="BC15" s="13" t="n">
-        <v>1405.41</v>
-      </c>
-      <c r="BD15" s="13" t="n">
-        <v>1428.89</v>
-      </c>
-      <c r="BE15" s="13" t="n">
-        <v>1432.58</v>
-      </c>
-      <c r="BF15" s="13" t="n">
-        <v>1430.38</v>
-      </c>
-      <c r="BG15" s="13" t="n">
-        <v>1430.38</v>
-      </c>
-      <c r="BH15" s="13" t="n">
-        <v>1430.38</v>
-      </c>
-      <c r="BI15" s="13" t="n">
-        <v>1418.39</v>
-      </c>
-      <c r="BJ15" s="13" t="n">
-        <v>1413.59</v>
-      </c>
-      <c r="BK15" s="13" t="n">
-        <v>1413.59</v>
-      </c>
-      <c r="BL15" s="13" t="n">
-        <v>1413.59</v>
-      </c>
-      <c r="BM15" s="13" t="n">
-        <v>1413.59</v>
-      </c>
-      <c r="BN15" s="13" t="n">
-        <v>1415.71</v>
-      </c>
-      <c r="BO15" s="13" t="n">
-        <v>1422.12</v>
-      </c>
-      <c r="BP15" s="13" t="n">
-        <v>1422.12</v>
-      </c>
-      <c r="BQ15" s="13" t="n">
-        <v>1424.4</v>
-      </c>
-      <c r="BR15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BS15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BT15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BU15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BV15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BW15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BX15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BY15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="BZ15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CA15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CB15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CC15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CD15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CE15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CF15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CG15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CH15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CI15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CJ15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CK15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CL15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CM15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CN15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CO15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CP15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CQ15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CR15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CS15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CT15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CU15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CV15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CW15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CX15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CY15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="CZ15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DA15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DB15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DC15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DD15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DE15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DF15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DG15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DH15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DI15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DJ15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DK15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DL15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DM15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DN15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DO15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DP15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DQ15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DR15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DS15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DT15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DU15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DV15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DW15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DX15" s="13" t="n">
-        <v>1432.29</v>
-      </c>
-      <c r="DY15" s="13" t="n">
-        <v>1432.29</v>
+          <t>헤지적용 원화매출(백만원)</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>3169.1</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>6702.4</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>6712.8</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>7352.3</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>13923.4</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>16467.9</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>16706.7</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>22060</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>22208.4</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>22266.9</v>
+      </c>
+      <c r="O15" s="18" t="n">
+        <v>34636.6</v>
+      </c>
+      <c r="P15" s="18" t="n">
+        <v>50759</v>
+      </c>
+      <c r="Q15" s="18" t="n">
+        <v>56847.1</v>
+      </c>
+      <c r="R15" s="18" t="n">
+        <v>64025.8</v>
+      </c>
+      <c r="S15" s="18" t="n">
+        <v>67761.2</v>
+      </c>
+      <c r="T15" s="18" t="n">
+        <v>67692.2</v>
+      </c>
+      <c r="U15" s="18" t="n">
+        <v>69448.89999999999</v>
+      </c>
+      <c r="V15" s="18" t="n">
+        <v>73263.5</v>
+      </c>
+      <c r="W15" s="18" t="n">
+        <v>79412</v>
+      </c>
+      <c r="X15" s="18" t="n">
+        <v>87898.7</v>
+      </c>
+      <c r="Y15" s="18" t="n">
+        <v>100004.1</v>
+      </c>
+      <c r="Z15" s="18" t="n">
+        <v>124200</v>
+      </c>
+      <c r="AA15" s="18" t="n">
+        <v>144245.2</v>
+      </c>
+      <c r="AB15" s="18" t="n">
+        <v>144844</v>
+      </c>
+      <c r="AC15" s="18" t="n">
+        <v>155537.7</v>
+      </c>
+      <c r="AD15" s="18" t="n">
+        <v>156835.1</v>
+      </c>
+      <c r="AE15" s="18" t="n">
+        <v>159018.5</v>
+      </c>
+      <c r="AF15" s="18" t="n">
+        <v>162693.6</v>
+      </c>
+      <c r="AG15" s="18" t="n">
+        <v>161655.2</v>
+      </c>
+      <c r="AH15" s="18" t="n">
+        <v>162421.9</v>
+      </c>
+      <c r="AI15" s="18" t="n">
+        <v>178571.6</v>
+      </c>
+      <c r="AJ15" s="18" t="n">
+        <v>253765.6</v>
+      </c>
+      <c r="AK15" s="18" t="n">
+        <v>312360.8</v>
+      </c>
+      <c r="AL15" s="18" t="n">
+        <v>338199.7</v>
+      </c>
+      <c r="AM15" s="18" t="n">
+        <v>392740.1</v>
+      </c>
+      <c r="AN15" s="18" t="n">
+        <v>364158.8</v>
+      </c>
+      <c r="AO15" s="18" t="n">
+        <v>333504.1</v>
+      </c>
+      <c r="AP15" s="18" t="n">
+        <v>323753.6</v>
+      </c>
+      <c r="AQ15" s="18" t="n">
+        <v>311087.9</v>
+      </c>
+      <c r="AR15" s="18" t="n">
+        <v>290283.1</v>
+      </c>
+      <c r="AS15" s="18" t="n">
+        <v>282303.2</v>
+      </c>
+      <c r="AT15" s="18" t="n">
+        <v>238468.2</v>
+      </c>
+      <c r="AU15" s="18" t="n">
+        <v>203677.3</v>
+      </c>
+      <c r="AV15" s="18" t="n">
+        <v>183695.6</v>
+      </c>
+      <c r="AW15" s="18" t="n">
+        <v>129879.5</v>
+      </c>
+      <c r="AX15" s="18" t="n">
+        <v>103761.7</v>
+      </c>
+      <c r="AY15" s="18" t="n">
+        <v>84488.8</v>
+      </c>
+      <c r="AZ15" s="18" t="n">
+        <v>53307.4</v>
+      </c>
+      <c r="BA15" s="18" t="n">
+        <v>50425.1</v>
+      </c>
+      <c r="BB15" s="18" t="n">
+        <v>43041</v>
+      </c>
+      <c r="BC15" s="18" t="n">
+        <v>21434.6</v>
+      </c>
+      <c r="BD15" s="18" t="n">
+        <v>18569.4</v>
+      </c>
+      <c r="BE15" s="18" t="n">
+        <v>17259.3</v>
+      </c>
+      <c r="BF15" s="18" t="n">
+        <v>15990.8</v>
+      </c>
+      <c r="BG15" s="18" t="n">
+        <v>15990.8</v>
+      </c>
+      <c r="BH15" s="18" t="n">
+        <v>15816.9</v>
+      </c>
+      <c r="BI15" s="18" t="n">
+        <v>10845.4</v>
+      </c>
+      <c r="BJ15" s="18" t="n">
+        <v>9725.200000000001</v>
+      </c>
+      <c r="BK15" s="18" t="n">
+        <v>9725.200000000001</v>
+      </c>
+      <c r="BL15" s="18" t="n">
+        <v>9513.799999999999</v>
+      </c>
+      <c r="BM15" s="18" t="n">
+        <v>9619.5</v>
+      </c>
+      <c r="BN15" s="18" t="n">
+        <v>8444.799999999999</v>
+      </c>
+      <c r="BO15" s="18" t="n">
+        <v>6044</v>
+      </c>
+      <c r="BP15" s="18" t="n">
+        <v>5912.6</v>
+      </c>
+      <c r="BQ15" s="18" t="n">
+        <v>2543</v>
+      </c>
+      <c r="BR15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="BS15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="BT15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="BU15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="BV15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="BW15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="BX15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="BY15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="BZ15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CA15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CB15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="CC15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CD15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CE15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CF15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="CG15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CH15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CI15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CJ15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="CK15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CL15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CM15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CN15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CO15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CP15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CQ15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CR15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="CS15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CT15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CU15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CV15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="CW15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="CX15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CY15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="CZ15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="DA15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DB15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DC15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DD15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DE15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DF15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DG15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DH15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="DI15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DJ15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DK15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DL15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="DM15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DN15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DO15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DP15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="DQ15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DR15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DS15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DT15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DU15" s="18" t="n">
+        <v>853.5</v>
+      </c>
+      <c r="DV15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DW15" s="18" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="DX15" s="18" t="n">
+        <v>844.2</v>
+      </c>
+      <c r="DY15" s="18" t="n">
+        <v>572.1</v>
+      </c>
+      <c r="DZ15" s="18" t="n">
+        <v>16584.3</v>
+      </c>
+      <c r="EA15" s="18" t="n">
+        <v>54450.3</v>
+      </c>
+      <c r="EB15" s="18" t="n">
+        <v>101171.9</v>
+      </c>
+      <c r="EC15" s="18" t="n">
+        <v>239393.1</v>
+      </c>
+      <c r="ED15" s="18" t="n">
+        <v>289816.6</v>
+      </c>
+      <c r="EE15" s="18" t="n">
+        <v>456348</v>
+      </c>
+      <c r="EF15" s="18" t="n">
+        <v>616235.3</v>
+      </c>
+      <c r="EG15" s="18" t="n">
+        <v>665342.3</v>
+      </c>
+      <c r="EH15" s="18" t="n">
+        <v>1297066.2</v>
+      </c>
+      <c r="EI15" s="18" t="n">
+        <v>1332504.4</v>
+      </c>
+      <c r="EJ15" s="18" t="n">
+        <v>1014731.8</v>
+      </c>
+      <c r="EK15" s="18" t="n">
+        <v>501825.6</v>
+      </c>
+      <c r="EL15" s="18" t="n">
+        <v>168208.1</v>
+      </c>
+      <c r="EM15" s="18" t="n">
+        <v>67810.3</v>
+      </c>
+      <c r="EN15" s="18" t="n">
+        <v>46112.7</v>
+      </c>
+      <c r="EO15" s="18" t="n">
+        <v>33622.1</v>
+      </c>
+      <c r="EP15" s="18" t="n">
+        <v>10181.4</v>
+      </c>
+      <c r="EQ15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="ER15" s="18" t="n">
+        <v>3432.8</v>
+      </c>
+      <c r="ES15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="ET15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="EU15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="EV15" s="18" t="n">
+        <v>3432.8</v>
+      </c>
+      <c r="EW15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="EX15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="EY15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="EZ15" s="18" t="n">
+        <v>3432.8</v>
+      </c>
+      <c r="FA15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="FB15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="FC15" s="18" t="n">
+        <v>3423.5</v>
+      </c>
+      <c r="FD15" s="18" t="n">
+        <v>3432.8</v>
+      </c>
+      <c r="FE15" s="18" t="n">
+        <v>1416.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>hedged_krw_m</t>
+          <t>target_opm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>헤지적용 원화매출(백만원)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>3169.1</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>6702.4</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>6712.8</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>7352.3</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>13923.4</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>16467.9</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>16706.7</v>
-      </c>
-      <c r="L16" s="18" t="n">
-        <v>22060</v>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>22208.4</v>
-      </c>
-      <c r="N16" s="18" t="n">
-        <v>22266.9</v>
-      </c>
-      <c r="O16" s="18" t="n">
-        <v>34636.6</v>
-      </c>
-      <c r="P16" s="18" t="n">
-        <v>50759</v>
-      </c>
-      <c r="Q16" s="18" t="n">
-        <v>56847.1</v>
-      </c>
-      <c r="R16" s="18" t="n">
-        <v>64025.8</v>
-      </c>
-      <c r="S16" s="18" t="n">
-        <v>67761.2</v>
-      </c>
-      <c r="T16" s="18" t="n">
-        <v>67692.2</v>
-      </c>
-      <c r="U16" s="18" t="n">
-        <v>69448.89999999999</v>
-      </c>
-      <c r="V16" s="18" t="n">
-        <v>73263.5</v>
-      </c>
-      <c r="W16" s="18" t="n">
-        <v>79412</v>
-      </c>
-      <c r="X16" s="18" t="n">
-        <v>87898.7</v>
-      </c>
-      <c r="Y16" s="18" t="n">
-        <v>100004.1</v>
-      </c>
-      <c r="Z16" s="18" t="n">
-        <v>124200</v>
-      </c>
-      <c r="AA16" s="18" t="n">
-        <v>144245.2</v>
-      </c>
-      <c r="AB16" s="18" t="n">
-        <v>144844</v>
-      </c>
-      <c r="AC16" s="18" t="n">
-        <v>155537.7</v>
-      </c>
-      <c r="AD16" s="18" t="n">
-        <v>156835.1</v>
-      </c>
-      <c r="AE16" s="18" t="n">
-        <v>159018.5</v>
-      </c>
-      <c r="AF16" s="18" t="n">
-        <v>162693.6</v>
-      </c>
-      <c r="AG16" s="18" t="n">
-        <v>161655.2</v>
-      </c>
-      <c r="AH16" s="18" t="n">
-        <v>162421.9</v>
-      </c>
-      <c r="AI16" s="18" t="n">
-        <v>178571.6</v>
-      </c>
-      <c r="AJ16" s="18" t="n">
-        <v>253765.6</v>
-      </c>
-      <c r="AK16" s="18" t="n">
-        <v>312360.8</v>
-      </c>
-      <c r="AL16" s="18" t="n">
-        <v>338199.7</v>
-      </c>
-      <c r="AM16" s="18" t="n">
-        <v>392740.1</v>
-      </c>
-      <c r="AN16" s="18" t="n">
-        <v>364158.8</v>
-      </c>
-      <c r="AO16" s="18" t="n">
-        <v>333504.1</v>
-      </c>
-      <c r="AP16" s="18" t="n">
-        <v>323753.6</v>
-      </c>
-      <c r="AQ16" s="18" t="n">
-        <v>311087.9</v>
-      </c>
-      <c r="AR16" s="18" t="n">
-        <v>290283.1</v>
-      </c>
-      <c r="AS16" s="18" t="n">
-        <v>282303.2</v>
-      </c>
-      <c r="AT16" s="18" t="n">
-        <v>238468.2</v>
-      </c>
-      <c r="AU16" s="18" t="n">
-        <v>203677.3</v>
-      </c>
-      <c r="AV16" s="18" t="n">
-        <v>183695.6</v>
-      </c>
-      <c r="AW16" s="18" t="n">
-        <v>129879.5</v>
-      </c>
-      <c r="AX16" s="18" t="n">
-        <v>103761.7</v>
-      </c>
-      <c r="AY16" s="18" t="n">
-        <v>84488.8</v>
-      </c>
-      <c r="AZ16" s="18" t="n">
-        <v>53307.4</v>
-      </c>
-      <c r="BA16" s="18" t="n">
-        <v>50425.1</v>
-      </c>
-      <c r="BB16" s="18" t="n">
-        <v>43041</v>
-      </c>
-      <c r="BC16" s="18" t="n">
-        <v>21434.6</v>
-      </c>
-      <c r="BD16" s="18" t="n">
-        <v>18569.4</v>
-      </c>
-      <c r="BE16" s="18" t="n">
-        <v>17259.3</v>
-      </c>
-      <c r="BF16" s="18" t="n">
-        <v>15990.8</v>
-      </c>
-      <c r="BG16" s="18" t="n">
-        <v>15990.8</v>
-      </c>
-      <c r="BH16" s="18" t="n">
-        <v>15816.9</v>
-      </c>
-      <c r="BI16" s="18" t="n">
-        <v>10845.4</v>
-      </c>
-      <c r="BJ16" s="18" t="n">
-        <v>9725.200000000001</v>
-      </c>
-      <c r="BK16" s="18" t="n">
-        <v>9725.200000000001</v>
-      </c>
-      <c r="BL16" s="18" t="n">
-        <v>9513.799999999999</v>
-      </c>
-      <c r="BM16" s="18" t="n">
-        <v>9619.5</v>
-      </c>
-      <c r="BN16" s="18" t="n">
-        <v>8444.799999999999</v>
-      </c>
-      <c r="BO16" s="18" t="n">
-        <v>6044</v>
-      </c>
-      <c r="BP16" s="18" t="n">
-        <v>5912.6</v>
-      </c>
-      <c r="BQ16" s="18" t="n">
-        <v>2543</v>
-      </c>
-      <c r="BR16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="BS16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="BT16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="BU16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="BV16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="BW16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="BX16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="BY16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="BZ16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CA16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CB16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="CC16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CD16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CE16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CF16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="CG16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CH16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CI16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CJ16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="CK16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CL16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CM16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CN16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CO16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CP16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CQ16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CR16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="CS16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CT16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CU16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CV16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="CW16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="CX16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CY16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="CZ16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="DA16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DB16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DC16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DD16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DE16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DF16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DG16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DH16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="DI16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DJ16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DK16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DL16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="DM16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DN16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DO16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DP16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="DQ16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DR16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DS16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DT16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DU16" s="18" t="n">
-        <v>853.5</v>
-      </c>
-      <c r="DV16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DW16" s="18" t="n">
-        <v>862.9</v>
-      </c>
-      <c r="DX16" s="18" t="n">
-        <v>844.2</v>
-      </c>
-      <c r="DY16" s="18" t="n">
-        <v>572.1</v>
-      </c>
-      <c r="DZ16" s="18" t="n">
-        <v>16584.3</v>
-      </c>
-      <c r="EA16" s="18" t="n">
-        <v>54450.3</v>
-      </c>
-      <c r="EB16" s="18" t="n">
-        <v>101171.9</v>
-      </c>
-      <c r="EC16" s="18" t="n">
-        <v>239393.1</v>
-      </c>
-      <c r="ED16" s="18" t="n">
-        <v>289816.6</v>
-      </c>
-      <c r="EE16" s="18" t="n">
-        <v>456348</v>
-      </c>
-      <c r="EF16" s="18" t="n">
-        <v>616235.3</v>
-      </c>
-      <c r="EG16" s="18" t="n">
-        <v>665342.3</v>
-      </c>
-      <c r="EH16" s="18" t="n">
-        <v>1297066.2</v>
-      </c>
-      <c r="EI16" s="18" t="n">
-        <v>1332504.4</v>
-      </c>
-      <c r="EJ16" s="18" t="n">
-        <v>1014731.8</v>
-      </c>
-      <c r="EK16" s="18" t="n">
-        <v>501825.6</v>
-      </c>
-      <c r="EL16" s="18" t="n">
-        <v>168208.1</v>
-      </c>
-      <c r="EM16" s="18" t="n">
-        <v>67810.3</v>
-      </c>
-      <c r="EN16" s="18" t="n">
-        <v>46112.7</v>
-      </c>
-      <c r="EO16" s="18" t="n">
-        <v>33622.1</v>
-      </c>
-      <c r="EP16" s="18" t="n">
-        <v>10181.4</v>
-      </c>
-      <c r="EQ16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="ER16" s="18" t="n">
-        <v>3432.8</v>
-      </c>
-      <c r="ES16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="ET16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="EU16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="EV16" s="18" t="n">
-        <v>3432.8</v>
-      </c>
-      <c r="EW16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="EX16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="EY16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="EZ16" s="18" t="n">
-        <v>3432.8</v>
-      </c>
-      <c r="FA16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="FB16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="FC16" s="18" t="n">
-        <v>3423.5</v>
-      </c>
-      <c r="FD16" s="18" t="n">
-        <v>3432.8</v>
-      </c>
-      <c r="FE16" s="18" t="n">
-        <v>1416.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>target_opm</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
           <t>타겟 OPM(코호트)</t>
         </is>
       </c>
-      <c r="AI17" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="21" t="n">
-        <v>0.0389</v>
-      </c>
-      <c r="AK17" s="21" t="n">
-        <v>0.0457</v>
-      </c>
-      <c r="AL17" s="21" t="n">
-        <v>0.0465</v>
-      </c>
-      <c r="AM17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AN17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AO17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AP17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AQ17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AR17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AS17" s="21" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AT17" s="21" t="n">
-        <v>0.0473</v>
-      </c>
-      <c r="AU17" s="21" t="n">
-        <v>0.0474</v>
-      </c>
-      <c r="AV17" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AW17" s="21" t="n">
-        <v>0.05</v>
+      <c r="AI16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AL16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AM16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AN16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AP16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AQ16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AS16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AU16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AV16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW16" s="21" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>계약 원장(contracts.json 기반)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>계약 원장(contracts.json 기반)</t>
+          <t>rcp</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>ships</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>amt_krw_m</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>amt_usd_m</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>fx_at_sign</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>signed</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>curve</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>estimated_series</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>rcp</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>ships</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>amt_krw_m</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>amt_usd_m</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>fx_at_sign</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>signed</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>curve</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>estimated_series</t>
-        </is>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20250930800101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>96678.522</v>
+      </c>
+      <c r="E20" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1159.91</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2027-03-13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20250930800101</t>
+          <t>20251103800145</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -41519,27 +41952,27 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>96678.522</v>
+        <v>72796.84699999999</v>
       </c>
       <c r="E21" t="n">
-        <v>83.34999999999999</v>
+        <v>55.33</v>
       </c>
       <c r="F21" t="n">
-        <v>1159.91</v>
+        <v>1315.69</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2027-03-13</t>
+          <t>2027-10-21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -41554,7 +41987,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20251103800145</t>
+          <t>20251110800052</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -41563,27 +41996,27 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>72796.84699999999</v>
+        <v>74855</v>
       </c>
       <c r="E22" t="n">
-        <v>55.33</v>
+        <v>51.653</v>
       </c>
       <c r="F22" t="n">
-        <v>1315.69</v>
+        <v>1449.19</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2027-10-21</t>
+          <t>2029-11-17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -41598,7 +42031,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20251110800052</t>
+          <t>20251126800540</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -41607,27 +42040,27 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>74855</v>
+        <v>164168.4</v>
       </c>
       <c r="E23" t="n">
-        <v>51.653</v>
+        <v>120.701</v>
       </c>
       <c r="F23" t="n">
-        <v>1449.19</v>
+        <v>1360.12</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2029-11-17</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -41642,7 +42075,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20251126800540</t>
+          <t>20251127800440</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -41651,27 +42084,27 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>164168.4</v>
+        <v>176849.588</v>
       </c>
       <c r="E24" t="n">
-        <v>120.701</v>
+        <v>122.033</v>
       </c>
       <c r="F24" t="n">
-        <v>1360.12</v>
+        <v>1449.19</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2034-04-30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -41686,7 +42119,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20251127800440</t>
+          <t>20251127800601</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -41695,27 +42128,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>176849.588</v>
+        <v>168916.01</v>
       </c>
       <c r="E25" t="n">
-        <v>122.033</v>
+        <v>116.559</v>
       </c>
       <c r="F25" t="n">
         <v>1449.19</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2034-04-30</t>
+          <t>2029-12-25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -41730,7 +42163,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20251127800601</t>
+          <t>20251205800202</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -41739,27 +42172,27 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>168916.01</v>
+        <v>92057.856</v>
       </c>
       <c r="E26" t="n">
-        <v>116.559</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1449.19</v>
+        <v>1396.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2029-12-25</t>
+          <t>2030-01-16</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -41774,36 +42207,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20251205800202</t>
+          <t>20251217800479</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>92057.856</v>
+        <v>312576</v>
       </c>
       <c r="E27" t="n">
-        <v>65.93000000000001</v>
+        <v>215.69</v>
       </c>
       <c r="F27" t="n">
-        <v>1396.3</v>
+        <v>1449.19</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2030-01-16</t>
+          <t>2029-10-31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -41818,36 +42251,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20251217800479</t>
+          <t>20251222800631</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAVAL</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>312576</v>
+        <v>161753.283</v>
       </c>
       <c r="E28" t="n">
-        <v>215.69</v>
+        <v>137.518</v>
       </c>
       <c r="F28" t="n">
-        <v>1449.19</v>
+        <v>1176.23</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2019-12-27</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2019-12-27</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2029-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -41862,36 +42295,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20251222800631</t>
+          <t>20251224800003</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>NAVAL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>161753.283</v>
+        <v>68858</v>
       </c>
       <c r="E29" t="n">
-        <v>137.518</v>
+        <v>47.515</v>
       </c>
       <c r="F29" t="n">
-        <v>1176.23</v>
+        <v>1449.19</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2019-12-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2019-12-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2028-12-07</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -41906,44 +42347,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20251224800003</t>
+          <t>20251224800596</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NAVAL</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>68858</v>
+        <v>181818.331</v>
       </c>
       <c r="E30" t="n">
-        <v>47.515</v>
+        <v>163.067</v>
       </c>
       <c r="F30" t="n">
-        <v>1449.19</v>
+        <v>1114.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2028-12-07</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>②BEP</t>
+          <t>2027-04-03</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -41958,7 +42391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20251224800596</t>
+          <t>20251231800507</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -41967,27 +42400,27 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>181818.331</v>
+        <v>382299.462</v>
       </c>
       <c r="E31" t="n">
-        <v>163.067</v>
+        <v>341.959</v>
       </c>
       <c r="F31" t="n">
-        <v>1114.99</v>
+        <v>1117.97</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2027-04-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -42002,7 +42435,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20251231800507</t>
+          <t>20251231800547</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -42011,27 +42444,27 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>382299.462</v>
+        <v>55930.484</v>
       </c>
       <c r="E32" t="n">
-        <v>341.959</v>
+        <v>38.594</v>
       </c>
       <c r="F32" t="n">
-        <v>1117.97</v>
+        <v>1449.19</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2028-09-11</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -42046,7 +42479,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20251231800547</t>
+          <t>20260107800221</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -42055,27 +42488,27 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>55930.484</v>
+        <v>117781.019</v>
       </c>
       <c r="E33" t="n">
-        <v>38.594</v>
+        <v>80.33499999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>1449.19</v>
+        <v>1466.12</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2028-09-11</t>
+          <t>2030-07-02</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -42090,7 +42523,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260107800221</t>
+          <t>20260116800164</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -42099,27 +42532,27 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>117781.019</v>
+        <v>185327.231</v>
       </c>
       <c r="E34" t="n">
-        <v>80.33499999999999</v>
+        <v>126.407</v>
       </c>
       <c r="F34" t="n">
         <v>1466.12</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2030-07-02</t>
+          <t>2029-04-29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -42134,7 +42567,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260116800164</t>
+          <t>20260120800250</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -42143,27 +42576,27 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>185327.231</v>
+        <v>84068.62699999999</v>
       </c>
       <c r="E35" t="n">
-        <v>126.407</v>
+        <v>65.83499999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>1466.12</v>
+        <v>1276.95</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2029-04-29</t>
+          <t>2027-08-30</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -42178,36 +42611,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260120800250</t>
+          <t>20260211800125</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>84068.62699999999</v>
+        <v>353265.889</v>
       </c>
       <c r="E36" t="n">
-        <v>65.83499999999999</v>
+        <v>240.953</v>
       </c>
       <c r="F36" t="n">
-        <v>1276.95</v>
+        <v>1466.12</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2027-08-30</t>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -42216,50 +42657,42 @@
         </is>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260211800125</t>
+          <t>20260227801603</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D37" t="n">
-        <v>353265.889</v>
+        <v>218819.48</v>
       </c>
       <c r="E37" t="n">
-        <v>240.953</v>
+        <v>194.371</v>
       </c>
       <c r="F37" t="n">
-        <v>1466.12</v>
+        <v>1125.78</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2019-03-20</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2019-03-20</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-04-30</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -42268,13 +42701,13 @@
         </is>
       </c>
       <c r="L37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260227801603</t>
+          <t>20260227801809</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -42283,27 +42716,27 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>218819.48</v>
+        <v>81559.656</v>
       </c>
       <c r="E38" t="n">
-        <v>194.371</v>
+        <v>55.63</v>
       </c>
       <c r="F38" t="n">
-        <v>1125.78</v>
+        <v>1466.12</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2019-03-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2019-03-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2028-04-30</t>
+          <t>2049-05-31</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -42318,7 +42751,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260227801809</t>
+          <t>20260304800353</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -42327,27 +42760,27 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>81559.656</v>
+        <v>92241.75599999999</v>
       </c>
       <c r="E39" t="n">
-        <v>55.63</v>
+        <v>62.916</v>
       </c>
       <c r="F39" t="n">
         <v>1466.12</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2049-05-31</t>
+          <t>2030-02-10</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -42362,7 +42795,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260304800353</t>
+          <t>20260306800575</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -42371,27 +42804,27 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>92241.75599999999</v>
+        <v>84679.82000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>62.916</v>
+        <v>57.758</v>
       </c>
       <c r="F40" t="n">
         <v>1466.12</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2030-02-10</t>
+          <t>2030-08-29</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -42406,7 +42839,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260306800575</t>
+          <t>20260313800208</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -42415,27 +42848,27 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>84679.82000000001</v>
+        <v>89392.5</v>
       </c>
       <c r="E41" t="n">
-        <v>57.758</v>
+        <v>60.972</v>
       </c>
       <c r="F41" t="n">
         <v>1466.12</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2030-08-29</t>
+          <t>2028-07-22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -42450,7 +42883,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260313800208</t>
+          <t>20260401800508</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -42459,27 +42892,27 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>89392.5</v>
+        <v>181103.297</v>
       </c>
       <c r="E42" t="n">
-        <v>60.972</v>
+        <v>161.993</v>
       </c>
       <c r="F42" t="n">
-        <v>1466.12</v>
+        <v>1117.97</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2028-07-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -42494,7 +42927,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260401800508</t>
+          <t>20260410800253</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -42503,27 +42936,27 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>181103.297</v>
+        <v>349662.915</v>
       </c>
       <c r="E43" t="n">
-        <v>161.993</v>
+        <v>232.837</v>
       </c>
       <c r="F43" t="n">
-        <v>1117.97</v>
+        <v>1501.75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2030-10-03</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -42538,7 +42971,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260410800253</t>
+          <t>20260422800059</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -42547,27 +42980,27 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>349662.915</v>
+        <v>68249.882</v>
       </c>
       <c r="E44" t="n">
-        <v>232.837</v>
+        <v>45.447</v>
       </c>
       <c r="F44" t="n">
         <v>1501.75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2030-10-03</t>
+          <t>2029-04-30</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -42582,7 +43015,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260422800059</t>
+          <t>20260423800218</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -42591,27 +43024,27 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>68249.882</v>
+        <v>101348.33</v>
       </c>
       <c r="E45" t="n">
-        <v>45.447</v>
+        <v>77.03100000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1501.75</v>
+        <v>1315.69</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
+          <t>2027-10-20</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -42626,7 +43059,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260423800218</t>
+          <t>20260423800721</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -42635,27 +43068,27 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>101348.33</v>
+        <v>82529.905</v>
       </c>
       <c r="E46" t="n">
-        <v>77.03100000000001</v>
+        <v>62.046</v>
       </c>
       <c r="F46" t="n">
-        <v>1315.69</v>
+        <v>1330.14</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2027-10-20</t>
+          <t>2028-09-20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -42670,36 +43103,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260423800721</t>
+          <t>20260427800078</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>82529.905</v>
+        <v>357198.303</v>
       </c>
       <c r="E47" t="n">
-        <v>62.046</v>
+        <v>237.855</v>
       </c>
       <c r="F47" t="n">
-        <v>1330.14</v>
+        <v>1501.75</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2028-09-20</t>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -42708,50 +43149,42 @@
         </is>
       </c>
       <c r="L47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260427800078</t>
+          <t>20260506800906</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D48" t="n">
-        <v>357198.303</v>
+        <v>80559.458</v>
       </c>
       <c r="E48" t="n">
-        <v>237.855</v>
+        <v>61.23</v>
       </c>
       <c r="F48" t="n">
-        <v>1501.75</v>
+        <v>1315.69</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2027-11-30</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -42760,13 +43193,13 @@
         </is>
       </c>
       <c r="L48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260506800906</t>
+          <t>20260518800840</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -42775,27 +43208,27 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>80559.458</v>
+        <v>73371.98299999999</v>
       </c>
       <c r="E49" t="n">
-        <v>61.23</v>
+        <v>50.63</v>
       </c>
       <c r="F49" t="n">
-        <v>1315.69</v>
+        <v>1449.19</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2027-11-30</t>
+          <t>2030-01-02</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -42810,7 +43243,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260518800840</t>
+          <t>20260520800639</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -42819,27 +43252,27 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>73371.98299999999</v>
+        <v>54315.409</v>
       </c>
       <c r="E50" t="n">
-        <v>50.63</v>
+        <v>36.168</v>
       </c>
       <c r="F50" t="n">
-        <v>1449.19</v>
+        <v>1501.75</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2030-01-02</t>
+          <t>2031-05-20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -42854,7 +43287,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260520800639</t>
+          <t>20260529800492</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -42863,27 +43296,27 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>54315.409</v>
+        <v>62695.656</v>
       </c>
       <c r="E51" t="n">
-        <v>36.168</v>
+        <v>52.975</v>
       </c>
       <c r="F51" t="n">
-        <v>1501.75</v>
+        <v>1183.5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2031-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -42898,7 +43331,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260529800492</t>
+          <t>20260601800841</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -42907,27 +43340,27 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>62695.656</v>
+        <v>59851.831</v>
       </c>
       <c r="E52" t="n">
-        <v>52.975</v>
+        <v>44.005</v>
       </c>
       <c r="F52" t="n">
-        <v>1183.5</v>
+        <v>1360.12</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2022-12-13</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2022-12-13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -42942,7 +43375,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260601800841</t>
+          <t>20260618800458</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -42951,27 +43384,27 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>59851.831</v>
+        <v>226877.219</v>
       </c>
       <c r="E53" t="n">
-        <v>44.005</v>
+        <v>209.978</v>
       </c>
       <c r="F53" t="n">
-        <v>1360.12</v>
+        <v>1080.48</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2022-12-13</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2022-12-13</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -42986,7 +43419,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260618800458</t>
+          <t>20260629801171</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -42995,27 +43428,27 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>226877.219</v>
+        <v>81052.209</v>
       </c>
       <c r="E54" t="n">
-        <v>209.978</v>
+        <v>72.499</v>
       </c>
       <c r="F54" t="n">
-        <v>1080.48</v>
+        <v>1117.97</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2031-01-14</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -43030,7 +43463,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260629801171</t>
+          <t>20260630800457</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -43039,27 +43472,27 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>81052.209</v>
+        <v>124213.19</v>
       </c>
       <c r="E55" t="n">
-        <v>72.499</v>
+        <v>92.563</v>
       </c>
       <c r="F55" t="n">
-        <v>1117.97</v>
+        <v>1341.93</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2022-09-05</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2022-09-05</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2031-01-14</t>
+          <t>2028-02-29</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -43074,7 +43507,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260630800457</t>
+          <t>20260630800913</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -43083,27 +43516,27 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>124213.19</v>
+        <v>148791.105</v>
       </c>
       <c r="E56" t="n">
-        <v>92.563</v>
+        <v>99.078</v>
       </c>
       <c r="F56" t="n">
-        <v>1341.93</v>
+        <v>1501.75</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2028-02-29</t>
+          <t>2032-04-18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -43118,7 +43551,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260630800913</t>
+          <t>20260721800175</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -43127,27 +43560,27 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>148791.105</v>
+        <v>187291.109</v>
       </c>
       <c r="E57" t="n">
-        <v>99.078</v>
+        <v>142.576</v>
       </c>
       <c r="F57" t="n">
-        <v>1501.75</v>
+        <v>1313.62</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2032-04-18</t>
+          <t>2027-12-29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -43162,7 +43595,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260721800175</t>
+          <t>20260805800532</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -43171,27 +43604,27 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>187291.109</v>
+        <v>110087.34</v>
       </c>
       <c r="E58" t="n">
-        <v>142.576</v>
+        <v>94.27800000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1313.62</v>
+        <v>1167.69</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2027-12-29</t>
+          <t>2027-06-09</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -43206,7 +43639,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260805800532</t>
+          <t>20260811800408</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -43215,27 +43648,27 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>110087.34</v>
+        <v>72728</v>
       </c>
       <c r="E59" t="n">
-        <v>94.27800000000001</v>
+        <v>54.677</v>
       </c>
       <c r="F59" t="n">
-        <v>1167.69</v>
+        <v>1330.14</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2019-05-31</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2019-05-31</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2027-06-09</t>
+          <t>2029-10-04</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -43250,7 +43683,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260811800408</t>
+          <t>20260818800047</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -43259,27 +43692,27 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>72728</v>
+        <v>104419.289</v>
       </c>
       <c r="E60" t="n">
-        <v>54.677</v>
+        <v>73.54900000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>1330.14</v>
+        <v>1419.72</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2029-10-04</t>
+          <t>2033-08-29</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -43294,7 +43727,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260818800047</t>
+          <t>20260820800160</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -43303,27 +43736,27 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>104419.289</v>
+        <v>85419.25999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>73.54900000000001</v>
+        <v>65.026</v>
       </c>
       <c r="F61" t="n">
-        <v>1419.72</v>
+        <v>1313.62</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2033-08-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -43338,7 +43771,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260820800160</t>
+          <t>20260918800109</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -43347,27 +43780,27 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>85419.25999999999</v>
+        <v>60071.111</v>
       </c>
       <c r="E62" t="n">
-        <v>65.026</v>
+        <v>45.161</v>
       </c>
       <c r="F62" t="n">
-        <v>1313.62</v>
+        <v>1330.14</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2028-08-09</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -43382,36 +43815,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260918800109</t>
+          <t>20260922800008</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>60071.111</v>
+        <v>678967.559</v>
       </c>
       <c r="E63" t="n">
-        <v>45.161</v>
+        <v>478.24</v>
       </c>
       <c r="F63" t="n">
-        <v>1330.14</v>
+        <v>1419.72</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2028-08-09</t>
+          <t>2029-04-30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -43420,50 +43861,42 @@
         </is>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260922800008</t>
+          <t>20260930800251</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>4</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D64" t="n">
-        <v>678967.559</v>
+        <v>260922.379</v>
       </c>
       <c r="E64" t="n">
-        <v>478.24</v>
+        <v>198.629</v>
       </c>
       <c r="F64" t="n">
-        <v>1419.72</v>
+        <v>1313.62</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -43472,90 +43905,46 @@
         </is>
       </c>
       <c r="L64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260930800251</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>260922.379</v>
-      </c>
-      <c r="E65" t="n">
-        <v>198.629</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1313.62</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2027-03-31</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="L65" t="b">
-        <v>0</v>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
+          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 5%, ③중마진 95%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 5%, ③중마진 95% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
+          <t>⚠ 종료일 '-' 12건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 '-' 12건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32297억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32297억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>⚠ 정기보고서 부문 매출 3개월분 &gt; 연결 매출(fin) 1분기(2023Q2; 최대 +34.9%) — 부문표가 내부거래 제거 전이거나 파서 문제(yards 레인). reconcile[q].exceeds_consolidated_pct 에 표시, ratio 는 그대로</t>
         </is>
@@ -51035,7 +51424,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2119</v>
+        <v>1833.4</v>
       </c>
     </row>
     <row r="30">
@@ -51055,7 +51444,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.87</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="32">
@@ -51075,7 +51464,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2541</v>
+        <v>0.2198</v>
       </c>
     </row>
     <row r="34">
@@ -51085,7 +51474,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="35">
@@ -51095,7 +51484,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>23500</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="분기" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="연간예상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="외화" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1465,55 +1465,55 @@
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1613억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)</t>
+SLS 해양 원화 1612억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1576억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)</t>
+SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1594억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)</t>
+SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1594억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1594억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1248억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1004억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1003억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2086,7 +2086,7 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4108억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4107억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2098,31 +2098,31 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4943억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4942억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5272억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5271억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5610억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5609억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5955억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5954억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6257억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6256억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2146,7 +2146,7 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4108억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4107억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2158,31 +2158,31 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4943억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4942억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5272억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5271억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5610억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5609억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5955억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5954억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6257억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6256억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3617,55 +3617,55 @@
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1613억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)
+        <t>추정: SLS 해양 원화 1612억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1576억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)
+        <t>추정: SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1594억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)
+        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1594억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1594억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1248억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1004억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1003억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
@@ -4443,7 +4443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.23% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 3.24% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 0 — 계약 45건 중 포함 5건(marine_hedged_krw_m), 재구성 최대차 2.1 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 0 — 계약 45건 중 포함 5건(marine_hedged_krw_m), 재구성 최대차 2.0 백만원</t>
         </is>
       </c>
     </row>
@@ -7181,35 +7181,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -7300,35 +7300,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -7419,35 +7419,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -7538,35 +7538,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -7657,35 +7657,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -7776,35 +7776,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -7895,35 +7895,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8014,35 +8014,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8149,7 +8149,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>15330</v>
+        <v>15350</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -8240,7 +8240,7 @@
         <v>20500</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>15400</v>
+        <v>15630</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -8422,7 +8422,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15165</v>
+        <v>15226.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9651,36 +9651,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.003355198</v>
+        <v>-0.003381036</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>0.014251169</v>
+        <v>0.003573479</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>-0.006586245</v>
+        <v>0.007173291</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>-0.002721684</v>
+        <v>-0.009123622</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.004144344</v>
+        <v>0.009403346</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>-0.004310738</v>
+        <v>0.000511404</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.003526321</v>
+        <v>0.000919133</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.002692765</v>
+        <v>0.006763517</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.002536297</v>
+        <v>-0.000516962</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.013120394</v>
+        <v>-0.005319491</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -9779,36 +9779,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.003355198</v>
+        <v>-0.003381036</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.014251169</v>
+        <v>0.003573479</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>-0.006586245</v>
+        <v>0.007173291</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>-0.002721684</v>
+        <v>-0.009123622</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.004144344</v>
+        <v>0.009403346</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>-0.004310738</v>
+        <v>0.000511404</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.003526321</v>
+        <v>0.000919133</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.002692765</v>
+        <v>0.006763517</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.002536297</v>
+        <v>-0.000516962</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.013120394</v>
+        <v>-0.005319491</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10038,33 +10038,33 @@
         <v>-0.184017988</v>
       </c>
       <c r="AD31" s="32" t="n">
-        <v>-0.281021965</v>
+        <v>-0.28096673</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="32" t="n">
-        <v>-0.398972267</v>
+        <v>-0.398830659</v>
       </c>
       <c r="AG31" s="32" t="n">
-        <v>-0.696368465</v>
+        <v>-0.695994775</v>
       </c>
       <c r="AH31" s="32" t="n">
-        <v>-1.612142757</v>
+        <v>-1.609050999</v>
       </c>
       <c r="AI31" s="32" t="n">
-        <v>2.515702606</v>
+        <v>2.52357948</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="32" t="n">
-        <v>0.735144534</v>
+        <v>0.735805532</v>
       </c>
       <c r="AL31" s="32" t="n">
-        <v>0.431971341</v>
+        <v>0.43219829</v>
       </c>
       <c r="AM31" s="32" t="n">
-        <v>0.264039538</v>
+        <v>0.264148466</v>
       </c>
       <c r="AN31" s="32" t="n">
-        <v>0.188450227</v>
+        <v>0.188518801</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10166,33 +10166,33 @@
         <v>0.130542904</v>
       </c>
       <c r="AD32" s="32" t="n">
-        <v>0.143888735</v>
+        <v>0.143860454</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="32" t="n">
-        <v>0.128398833</v>
+        <v>0.128366295</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.119368393</v>
+        <v>0.119348006</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>0.074959656</v>
+        <v>0.074936761</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>0.066610691</v>
+        <v>0.06659058599999999</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>0.064159884</v>
+        <v>0.064142403</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>0.061471604</v>
+        <v>0.061456318</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>0.050689093</v>
+        <v>0.050679534</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>0.043523985</v>
+        <v>0.043517807</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -10892,33 +10892,33 @@
         <v>2152.980811</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2152.975135</v>
+        <v>2152.980115</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2152.992823</v>
+        <v>2152.994168</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2153.0111</v>
+        <v>2153.008338</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>274.806903</v>
+        <v>274.810073</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>-0.023097</v>
+        <v>-0.019927</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>0.0111</v>
+        <v>0.008338</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>0.0111</v>
+        <v>0.008338</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>-0.013256</v>
+        <v>-0.01803</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>0.019622</v>
+        <v>0.018206</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -11038,39 +11038,39 @@
         <v>0.091372143</v>
       </c>
       <c r="AD39" s="32" t="n">
-        <v>0.100860751</v>
+        <v>0.100858905</v>
       </c>
       <c r="AE39" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF39" s="32" t="n">
-        <v>0.10275284</v>
+        <v>0.102752018</v>
       </c>
       <c r="AG39" s="32" t="n">
-        <v>0.106430623</v>
+        <v>0.106431777</v>
       </c>
       <c r="AH39" s="32" t="n">
-        <v>0.108021844</v>
+        <v>0.10802063</v>
       </c>
       <c r="AI39" s="32" t="n">
-        <v>0.109658841</v>
+        <v>0.109658904</v>
       </c>
       <c r="AJ39" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK39" s="32" t="n">
-        <v>0.112162433</v>
+        <v>0.112164089</v>
       </c>
       <c r="AL39" s="32" t="n">
-        <v>0.113492621</v>
+        <v>0.113495488</v>
       </c>
       <c r="AM39" s="32" t="n">
-        <v>0.108805258</v>
+        <v>0.108800475</v>
       </c>
       <c r="AN39" s="32" t="n">
-        <v>0.105112108</v>
+        <v>0.105118794</v>
       </c>
       <c r="AO39" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO36,"")</f>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>15330</v>
+        <v>15350</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -11690,7 +11690,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2200010920148514</v>
+        <v>0.2199986135997462</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05359745275052863</v>
+        <v>0.05359746242032782</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03234584155494299</v>
+        <v>0.03235228149894262</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0787017926451721</v>
+        <v>0.07870689658964482</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41264,277 +41264,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
     </row>
     <row r="15">
@@ -41651,277 +41651,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1380.17</v>
+        <v>1379.09</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1387.39</v>
+        <v>1386.1</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1399.7</v>
+        <v>1398.41</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1403.42</v>
+        <v>1402.13</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1407.11</v>
+        <v>1405.82</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1412.25</v>
+        <v>1410.96</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1417.14</v>
+        <v>1415.85</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1418.02</v>
+        <v>1416.73</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1416.19</v>
+        <v>1414.9</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1413.74</v>
+        <v>1412.45</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1416.78</v>
+        <v>1415.49</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1419.52</v>
+        <v>1418.23</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1423.03</v>
+        <v>1421.74</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1427.48</v>
+        <v>1426.19</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1428.07</v>
+        <v>1426.78</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1427.57</v>
+        <v>1426.28</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1403.77</v>
+        <v>1402.48</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1427.23</v>
+        <v>1425.94</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1430.91</v>
+        <v>1429.62</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1428.69</v>
+        <v>1427.4</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1428.69</v>
+        <v>1427.4</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1428.69</v>
+        <v>1427.4</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1416.64</v>
+        <v>1415.35</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1411.81</v>
+        <v>1410.52</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1411.81</v>
+        <v>1410.52</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1411.81</v>
+        <v>1410.52</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1411.81</v>
+        <v>1410.52</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1413.98</v>
+        <v>1412.69</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1420.6</v>
+        <v>1419.31</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1420.6</v>
+        <v>1419.31</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1422.87</v>
+        <v>1421.58</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1430.77</v>
+        <v>1429.48</v>
       </c>
     </row>
     <row r="16">
@@ -42038,277 +42038,277 @@
         <v>338131.1</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392874.9</v>
+        <v>392567.5</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363772.4</v>
+        <v>363434.2</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>333154.8</v>
+        <v>332847.7</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>323416</v>
+        <v>323118.7</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310764.9</v>
+        <v>310480</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289983.6</v>
+        <v>289718.7</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>282013.3</v>
+        <v>281756.6</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>238225.7</v>
+        <v>238009</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203471.8</v>
+        <v>203286.5</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183511</v>
+        <v>183343.6</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129744.8</v>
+        <v>129626.7</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103651.1</v>
+        <v>103557</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84399.2</v>
+        <v>84322.60000000001</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53251.2</v>
+        <v>53203.1</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50372.1</v>
+        <v>50326.6</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42995.8</v>
+        <v>42956.9</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21412.1</v>
+        <v>21392.4</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18550.3</v>
+        <v>18533.6</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17241.7</v>
+        <v>17226.1</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15974.4</v>
+        <v>15960</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15974.4</v>
+        <v>15960</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15800.8</v>
+        <v>15786.5</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10834.4</v>
+        <v>10824.6</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9715.5</v>
+        <v>9706.6</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9715.5</v>
+        <v>9706.6</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9504.200000000001</v>
+        <v>9495.6</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9609.9</v>
+        <v>9601.1</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8436.200000000001</v>
+        <v>8428.5</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6037.5</v>
+        <v>6032</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5906.3</v>
+        <v>5900.9</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2540.3</v>
+        <v>2538</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>852.6</v>
+        <v>851.9</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>862</v>
+        <v>861.2</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>843.3</v>
+        <v>842.5</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>571.5</v>
+        <v>571</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -42335,76 +42335,76 @@
         <v>665342.3</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1297132.4</v>
+        <v>1296825</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1331108.1</v>
+        <v>1329880.6</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1013694.4</v>
+        <v>1012770.8</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>501306.1</v>
+        <v>500849.9</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>168031.2</v>
+        <v>167879</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67740.8</v>
+        <v>67679.7</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>46066.2</v>
+        <v>46024.3</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33587.8</v>
+        <v>33557.2</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10170.6</v>
+        <v>10161.3</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3429.2</v>
+        <v>3426.2</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3429.2</v>
+        <v>3426.2</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3429.2</v>
+        <v>3426.2</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3419.9</v>
+        <v>3416.8</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3429.2</v>
+        <v>3426.2</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1414.8</v>
+        <v>1413.5</v>
       </c>
     </row>
     <row r="17">
@@ -42521,43 +42521,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>161348.5</v>
+        <v>161226</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157624.5</v>
+        <v>157481.4</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159375.9</v>
+        <v>159231.2</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>161127.3</v>
+        <v>160981</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>161127.3</v>
+        <v>160981</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159375.9</v>
+        <v>159231.2</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159375.9</v>
+        <v>159231.2</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124754.8</v>
+        <v>124641.3</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100350.1</v>
+        <v>100258.2</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82631.10000000001</v>
+        <v>82555.10000000001</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40737.2</v>
+        <v>40699.9</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19898.4</v>
+        <v>19880.3</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6704.9</v>
+        <v>6698.8</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -42818,16 +42818,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>402072.1</v>
+        <v>401949.6</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>639255</v>
+        <v>638674.6</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>543856.7</v>
+        <v>543361.9</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149971.6</v>
+        <v>149834.1</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -43004,43 +43004,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96689.5</v>
+        <v>96616.89999999999</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94459.3</v>
+        <v>94374.5</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95508.89999999999</v>
+        <v>95423.10000000001</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96558.39999999999</v>
+        <v>96471.7</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96558.39999999999</v>
+        <v>96471.7</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95508.89999999999</v>
+        <v>95423.10000000001</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95508.89999999999</v>
+        <v>95423.10000000001</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60185.9</v>
+        <v>60132</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35781.2</v>
+        <v>35748.9</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19465.8</v>
+        <v>19448.1</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19682.1</v>
+        <v>19664.2</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19898.4</v>
+        <v>19880.3</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6704.9</v>
+        <v>6698.8</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -43391,37 +43391,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64659</v>
+        <v>64609.1</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63165.2</v>
+        <v>63106.9</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63867.1</v>
+        <v>63808.1</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64568.9</v>
+        <v>64509.3</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64568.9</v>
+        <v>64509.3</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63867.1</v>
+        <v>63808.1</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63867.1</v>
+        <v>63808.1</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64568.9</v>
+        <v>64509.3</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64568.9</v>
+        <v>64509.3</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63165.2</v>
+        <v>63106.9</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21055.1</v>
+        <v>21035.6</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -43909,367 +43909,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1354.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1351.18)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
     </row>
@@ -58117,7 +58117,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -63378,7 +63378,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -65542,7 +65542,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1975</v>
+        <v>1974.4</v>
       </c>
     </row>
     <row r="30">
@@ -65562,7 +65562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.76</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1465,55 +1465,55 @@
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1612억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)</t>
+SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)</t>
+SLS 해양 원화 1573억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1245억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1003억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
+SLS 해양 원화 1001억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2092,7 +2092,7 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4598억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4597억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2116,13 +2116,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5954억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5953억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6256억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6255억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2152,7 +2152,7 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4598억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4597억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2176,13 +2176,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5954억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5953억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6256억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6255억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3617,55 +3617,55 @@
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1612억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)
+        <t>추정: SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)
+        <t>추정: SLS 해양 원화 1573억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1245억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1003억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1001억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
@@ -4443,7 +4443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 0 — 계약 45건 중 포함 5건(marine_hedged_krw_m), 재구성 최대차 2.0 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 0 — 계약 45건 중 포함 5건(marine_hedged_krw_m), 재구성 최대차 2.1 백만원</t>
         </is>
       </c>
     </row>
@@ -7181,35 +7181,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -7300,35 +7300,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -7419,35 +7419,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -7538,35 +7538,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -7657,35 +7657,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -7776,35 +7776,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -7895,35 +7895,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8014,35 +8014,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8149,7 +8149,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>15350</v>
+        <v>14940</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -8422,7 +8422,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15226.7</v>
+        <v>15175</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9651,36 +9651,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.003381036</v>
+        <v>-0.003318006</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>0.003573479</v>
+        <v>0.015464007</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.007173291</v>
+        <v>-0.004031285</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>-0.009123622</v>
+        <v>-0.009088104</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.009403346</v>
+        <v>0.008489906</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>0.000511404</v>
+        <v>-0.001423921</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>0.000919133</v>
+        <v>0.000144219</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.006763517</v>
+        <v>0.004886256</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>-0.000516962</v>
+        <v>0.003344854</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.005319491</v>
+        <v>0.00333223</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -9779,36 +9779,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.003381036</v>
+        <v>-0.003318006</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.003573479</v>
+        <v>0.015464007</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.007173291</v>
+        <v>-0.004031285</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>-0.009123622</v>
+        <v>-0.009088104</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.009403346</v>
+        <v>0.008489906</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.000511404</v>
+        <v>-0.001423921</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>0.000919133</v>
+        <v>0.000144219</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.006763517</v>
+        <v>0.004886256</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>-0.000516962</v>
+        <v>0.003344854</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.005319491</v>
+        <v>0.00333223</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10038,33 +10038,33 @@
         <v>-0.184017988</v>
       </c>
       <c r="AD31" s="32" t="n">
-        <v>-0.28096673</v>
+        <v>-0.280911496</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="32" t="n">
-        <v>-0.398830659</v>
+        <v>-0.398689073</v>
       </c>
       <c r="AG31" s="32" t="n">
-        <v>-0.695994775</v>
+        <v>-0.695564545</v>
       </c>
       <c r="AH31" s="32" t="n">
-        <v>-1.609050999</v>
+        <v>-1.605576018</v>
       </c>
       <c r="AI31" s="32" t="n">
-        <v>2.52357948</v>
+        <v>2.532527523</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="32" t="n">
-        <v>0.735805532</v>
+        <v>0.736531253</v>
       </c>
       <c r="AL31" s="32" t="n">
-        <v>0.43219829</v>
+        <v>0.432447696</v>
       </c>
       <c r="AM31" s="32" t="n">
-        <v>0.264148466</v>
+        <v>0.264272447</v>
       </c>
       <c r="AN31" s="32" t="n">
-        <v>0.188518801</v>
+        <v>0.188587585</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10166,33 +10166,33 @@
         <v>0.130542904</v>
       </c>
       <c r="AD32" s="32" t="n">
-        <v>0.143860454</v>
+        <v>0.143832173</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="32" t="n">
-        <v>0.128366295</v>
+        <v>0.128333755</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.119348006</v>
+        <v>0.119317877</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>0.074936761</v>
+        <v>0.074910163</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>0.06659058599999999</v>
+        <v>0.066567239</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>0.064142403</v>
+        <v>0.0641202</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>0.061456318</v>
+        <v>0.061436885</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>0.050679534</v>
+        <v>0.050667804</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>0.043517807</v>
+        <v>0.043507943</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -10892,33 +10892,33 @@
         <v>2152.980811</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2152.980115</v>
+        <v>2152.974958</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2152.994168</v>
+        <v>2152.995098</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2153.008338</v>
+        <v>2153.008486</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>274.810073</v>
+        <v>274.809487</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>-0.019927</v>
+        <v>-0.020513</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>0.008338</v>
+        <v>0.008486</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>0.008338</v>
+        <v>0.008486</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>-0.01803</v>
+        <v>-0.015199</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>0.018206</v>
+        <v>0.01905</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -11038,39 +11038,39 @@
         <v>0.091372143</v>
       </c>
       <c r="AD39" s="32" t="n">
-        <v>0.100858905</v>
+        <v>0.100860741</v>
       </c>
       <c r="AE39" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF39" s="32" t="n">
-        <v>0.102752018</v>
+        <v>0.102751417</v>
       </c>
       <c r="AG39" s="32" t="n">
-        <v>0.106431777</v>
+        <v>0.106430777</v>
       </c>
       <c r="AH39" s="32" t="n">
-        <v>0.10802063</v>
+        <v>0.108021265</v>
       </c>
       <c r="AI39" s="32" t="n">
-        <v>0.109658904</v>
+        <v>0.109661451</v>
       </c>
       <c r="AJ39" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK39" s="32" t="n">
-        <v>0.112164089</v>
+        <v>0.112161754</v>
       </c>
       <c r="AL39" s="32" t="n">
-        <v>0.113495488</v>
+        <v>0.113494618</v>
       </c>
       <c r="AM39" s="32" t="n">
-        <v>0.108800475</v>
+        <v>0.108807749</v>
       </c>
       <c r="AN39" s="32" t="n">
-        <v>0.105118794</v>
+        <v>0.10511548</v>
       </c>
       <c r="AO39" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO36,"")</f>
@@ -11415,11 +11415,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>15350</v>
+        <v>14940</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,010원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,320원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -11690,7 +11690,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2199986135997462</v>
+        <v>0.2199992855596905</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05359746242032782</v>
+        <v>0.05359732499409252</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03235228149894262</v>
+        <v>0.03235095476846647</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.07870689658964482</v>
+        <v>0.0787057007461239</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38306,46 +38306,46 @@
         <v>100.274</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>115.312</v>
+        <v>115.314</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>115.478</v>
+        <v>115.48</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>122.382</v>
+        <v>122.384</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>123.837</v>
+        <v>123.839</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>124.334</v>
+        <v>124.336</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>125.21</v>
+        <v>125.212</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>124.927</v>
+        <v>124.929</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>125.515</v>
+        <v>125.517</v>
       </c>
       <c r="AI5" s="26" t="n">
-        <v>135.042</v>
+        <v>135.044</v>
       </c>
       <c r="AJ5" s="26" t="n">
-        <v>185.788</v>
+        <v>185.789</v>
       </c>
       <c r="AK5" s="26" t="n">
-        <v>220.764</v>
+        <v>220.765</v>
       </c>
       <c r="AL5" s="26" t="n">
-        <v>242.221</v>
+        <v>242.223</v>
       </c>
       <c r="AM5" s="26" t="n">
-        <v>284.657</v>
+        <v>284.659</v>
       </c>
       <c r="AN5" s="26" t="n">
-        <v>262.2</v>
+        <v>262.202</v>
       </c>
       <c r="AO5" s="26" t="n">
         <v>238.019</v>
@@ -38630,19 +38630,19 @@
         <v>245.213</v>
       </c>
       <c r="EE5" s="26" t="n">
-        <v>370.432</v>
+        <v>370.434</v>
       </c>
       <c r="EF5" s="26" t="n">
-        <v>486.031</v>
+        <v>486.039</v>
       </c>
       <c r="EG5" s="26" t="n">
-        <v>510.694</v>
+        <v>510.702</v>
       </c>
       <c r="EH5" s="26" t="n">
-        <v>933.4299999999999</v>
+        <v>933.436</v>
       </c>
       <c r="EI5" s="26" t="n">
-        <v>951.52</v>
+        <v>951.522</v>
       </c>
       <c r="EJ5" s="26" t="n">
         <v>716.011</v>
@@ -39272,46 +39272,46 @@
         <v>100.274</v>
       </c>
       <c r="AA7" s="26" t="n">
-        <v>115.312</v>
+        <v>115.314</v>
       </c>
       <c r="AB7" s="26" t="n">
-        <v>115.478</v>
+        <v>115.48</v>
       </c>
       <c r="AC7" s="26" t="n">
-        <v>122.382</v>
+        <v>122.384</v>
       </c>
       <c r="AD7" s="26" t="n">
-        <v>123.837</v>
+        <v>123.839</v>
       </c>
       <c r="AE7" s="26" t="n">
-        <v>124.334</v>
+        <v>124.336</v>
       </c>
       <c r="AF7" s="26" t="n">
-        <v>125.21</v>
+        <v>125.212</v>
       </c>
       <c r="AG7" s="26" t="n">
-        <v>124.927</v>
+        <v>124.929</v>
       </c>
       <c r="AH7" s="26" t="n">
-        <v>125.515</v>
+        <v>125.517</v>
       </c>
       <c r="AI7" s="26" t="n">
-        <v>132.36</v>
+        <v>132.362</v>
       </c>
       <c r="AJ7" s="26" t="n">
-        <v>154.297</v>
+        <v>154.299</v>
       </c>
       <c r="AK7" s="26" t="n">
-        <v>160.205</v>
+        <v>160.206</v>
       </c>
       <c r="AL7" s="26" t="n">
-        <v>169.976</v>
+        <v>169.978</v>
       </c>
       <c r="AM7" s="26" t="n">
-        <v>171.235</v>
+        <v>171.236</v>
       </c>
       <c r="AN7" s="26" t="n">
-        <v>151.243</v>
+        <v>151.245</v>
       </c>
       <c r="AO7" s="26" t="n">
         <v>125.829</v>
@@ -39596,19 +39596,19 @@
         <v>245.213</v>
       </c>
       <c r="EE7" s="26" t="n">
-        <v>370.432</v>
+        <v>370.434</v>
       </c>
       <c r="EF7" s="26" t="n">
-        <v>486.031</v>
+        <v>486.039</v>
       </c>
       <c r="EG7" s="26" t="n">
-        <v>508.012</v>
+        <v>508.02</v>
       </c>
       <c r="EH7" s="26" t="n">
-        <v>655.713</v>
+        <v>655.7190000000001</v>
       </c>
       <c r="EI7" s="26" t="n">
-        <v>501.529</v>
+        <v>501.531</v>
       </c>
       <c r="EJ7" s="26" t="n">
         <v>332.42</v>
@@ -39899,46 +39899,46 @@
         <v>100.274</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>115.312</v>
+        <v>115.314</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>115.478</v>
+        <v>115.48</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>122.382</v>
+        <v>122.384</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>123.837</v>
+        <v>123.839</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>124.334</v>
+        <v>124.336</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>125.21</v>
+        <v>125.212</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>124.927</v>
+        <v>124.929</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>125.515</v>
+        <v>125.517</v>
       </c>
       <c r="AI10" s="26" t="n">
-        <v>134.646</v>
+        <v>134.648</v>
       </c>
       <c r="AJ10" s="26" t="n">
-        <v>168.016</v>
+        <v>168.017</v>
       </c>
       <c r="AK10" s="26" t="n">
-        <v>174.076</v>
+        <v>174.078</v>
       </c>
       <c r="AL10" s="26" t="n">
-        <v>184</v>
+        <v>184.002</v>
       </c>
       <c r="AM10" s="26" t="n">
-        <v>185.258</v>
+        <v>185.26</v>
       </c>
       <c r="AN10" s="26" t="n">
-        <v>164.962</v>
+        <v>164.964</v>
       </c>
       <c r="AO10" s="26" t="n">
         <v>139.7</v>
@@ -40223,19 +40223,19 @@
         <v>245.213</v>
       </c>
       <c r="EE10" s="26" t="n">
-        <v>370.432</v>
+        <v>370.434</v>
       </c>
       <c r="EF10" s="26" t="n">
-        <v>486.031</v>
+        <v>486.039</v>
       </c>
       <c r="EG10" s="26" t="n">
-        <v>510.298</v>
+        <v>510.306</v>
       </c>
       <c r="EH10" s="26" t="n">
-        <v>711.35</v>
+        <v>711.357</v>
       </c>
       <c r="EI10" s="26" t="n">
-        <v>557.165</v>
+        <v>557.167</v>
       </c>
       <c r="EJ10" s="26" t="n">
         <v>388.211</v>
@@ -40841,7 +40841,7 @@
         <v>1206.46</v>
       </c>
       <c r="AA13" s="13" t="n">
-        <v>1220.44</v>
+        <v>1220.45</v>
       </c>
       <c r="AB13" s="13" t="n">
         <v>1221.79</v>
@@ -40859,7 +40859,7 @@
         <v>1233.83</v>
       </c>
       <c r="AG13" s="13" t="n">
-        <v>1249.2</v>
+        <v>1249.21</v>
       </c>
       <c r="AH13" s="13" t="n">
         <v>1254.23</v>
@@ -40880,7 +40880,7 @@
         <v>1391.05</v>
       </c>
       <c r="AN13" s="13" t="n">
-        <v>1404.15</v>
+        <v>1404.14</v>
       </c>
       <c r="AO13" s="13" t="n">
         <v>1421.74</v>
@@ -41264,277 +41264,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
     </row>
     <row r="15">
@@ -41651,277 +41651,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1379.09</v>
+        <v>1378.16</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1386.1</v>
+        <v>1384.54</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1398.41</v>
+        <v>1396.85</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1402.13</v>
+        <v>1400.57</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1405.82</v>
+        <v>1404.26</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1410.96</v>
+        <v>1409.4</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1415.85</v>
+        <v>1414.29</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1416.73</v>
+        <v>1415.17</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1414.9</v>
+        <v>1413.34</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1412.45</v>
+        <v>1410.89</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1415.49</v>
+        <v>1413.93</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1418.23</v>
+        <v>1416.67</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1421.74</v>
+        <v>1420.18</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1426.19</v>
+        <v>1424.63</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1426.78</v>
+        <v>1425.22</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1426.28</v>
+        <v>1424.72</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1402.48</v>
+        <v>1400.92</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1425.94</v>
+        <v>1424.38</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1429.62</v>
+        <v>1428.06</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1427.4</v>
+        <v>1425.84</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1427.4</v>
+        <v>1425.84</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1427.4</v>
+        <v>1425.84</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1415.35</v>
+        <v>1413.79</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1410.52</v>
+        <v>1408.96</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1410.52</v>
+        <v>1408.96</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1410.52</v>
+        <v>1408.96</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1410.52</v>
+        <v>1408.96</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1412.69</v>
+        <v>1411.13</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1419.31</v>
+        <v>1417.75</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1419.31</v>
+        <v>1417.75</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1421.58</v>
+        <v>1420.02</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1429.48</v>
+        <v>1427.92</v>
       </c>
     </row>
     <row r="16">
@@ -41999,316 +41999,316 @@
         <v>100004.1</v>
       </c>
       <c r="Z16" s="18" t="n">
-        <v>124200</v>
+        <v>124200.3</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>144245.2</v>
+        <v>144247.5</v>
       </c>
       <c r="AB16" s="18" t="n">
-        <v>144844</v>
+        <v>144846.3</v>
       </c>
       <c r="AC16" s="18" t="n">
-        <v>155537.7</v>
+        <v>155540</v>
       </c>
       <c r="AD16" s="18" t="n">
-        <v>156835.1</v>
+        <v>156837.5</v>
       </c>
       <c r="AE16" s="18" t="n">
-        <v>159018.5</v>
+        <v>159020.9</v>
       </c>
       <c r="AF16" s="18" t="n">
-        <v>162693.6</v>
+        <v>162696</v>
       </c>
       <c r="AG16" s="18" t="n">
-        <v>161655.2</v>
+        <v>161657.6</v>
       </c>
       <c r="AH16" s="18" t="n">
-        <v>162421.9</v>
+        <v>162424.3</v>
       </c>
       <c r="AI16" s="18" t="n">
-        <v>178571.6</v>
+        <v>178574.1</v>
       </c>
       <c r="AJ16" s="18" t="n">
-        <v>253765.6</v>
+        <v>253768</v>
       </c>
       <c r="AK16" s="18" t="n">
-        <v>312360.8</v>
+        <v>312363.2</v>
       </c>
       <c r="AL16" s="18" t="n">
-        <v>338131.1</v>
+        <v>338133.5</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392567.5</v>
+        <v>392305.1</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363434.2</v>
+        <v>363027.4</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332847.7</v>
+        <v>332476.4</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>323118.7</v>
+        <v>322759.2</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310480</v>
+        <v>310135.5</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289718.7</v>
+        <v>289398.4</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281756.6</v>
+        <v>281446.1</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>238009</v>
+        <v>237746.9</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203286.5</v>
+        <v>203062.4</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183343.6</v>
+        <v>183141.1</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129626.7</v>
+        <v>129483.9</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103557</v>
+        <v>103443</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84322.60000000001</v>
+        <v>84230.10000000001</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53203.1</v>
+        <v>53144.9</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50326.6</v>
+        <v>50271.6</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42956.9</v>
+        <v>42910</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21392.4</v>
+        <v>21368.6</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18533.6</v>
+        <v>18513.3</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17226.1</v>
+        <v>17207.3</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15960</v>
+        <v>15942.6</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15960</v>
+        <v>15942.6</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15786.5</v>
+        <v>15769.3</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10824.6</v>
+        <v>10812.6</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9706.6</v>
+        <v>9695.799999999999</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9706.6</v>
+        <v>9695.799999999999</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9495.6</v>
+        <v>9485.1</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9601.1</v>
+        <v>9590.5</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8428.5</v>
+        <v>8419.200000000001</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6032</v>
+        <v>6025.4</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5900.9</v>
+        <v>5894.4</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2538</v>
+        <v>2535.2</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>851.9</v>
+        <v>850.9</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>861.2</v>
+        <v>860.3</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>842.5</v>
+        <v>841.6</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>571</v>
+        <v>570.4</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -42326,85 +42326,85 @@
         <v>289816.6</v>
       </c>
       <c r="EE16" s="18" t="n">
-        <v>456348</v>
+        <v>456350.6</v>
       </c>
       <c r="EF16" s="18" t="n">
-        <v>616235.3</v>
+        <v>616244.7</v>
       </c>
       <c r="EG16" s="18" t="n">
-        <v>665342.3</v>
+        <v>665352</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296825</v>
+        <v>1296569.8</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1329880.6</v>
+        <v>1328398.5</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1012770.8</v>
+        <v>1011653.8</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>500849.9</v>
+        <v>500298.1</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167879</v>
+        <v>167695.1</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67679.7</v>
+        <v>67605.8</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>46024.3</v>
+        <v>45973.5</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33557.2</v>
+        <v>33520.2</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10161.3</v>
+        <v>10150.2</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3426.2</v>
+        <v>3422.4</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3426.2</v>
+        <v>3422.4</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3426.2</v>
+        <v>3422.4</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3416.8</v>
+        <v>3413.1</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3426.2</v>
+        <v>3422.4</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1413.5</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="17">
@@ -42521,43 +42521,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>161226</v>
+        <v>161120.5</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157481.4</v>
+        <v>157308.3</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159231.2</v>
+        <v>159056.2</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160981</v>
+        <v>160804</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160981</v>
+        <v>160804</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159231.2</v>
+        <v>159056.2</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159231.2</v>
+        <v>159056.2</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124641.3</v>
+        <v>124504</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100258.2</v>
+        <v>100147.1</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82555.10000000001</v>
+        <v>82463.2</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40699.9</v>
+        <v>40654.7</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19880.3</v>
+        <v>19858.4</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6698.8</v>
+        <v>6691.4</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -42818,16 +42818,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401949.6</v>
+        <v>401844.1</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>638674.6</v>
+        <v>637972.5</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>543361.9</v>
+        <v>542763.5</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149834.1</v>
+        <v>149667.7</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -43004,43 +43004,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96616.89999999999</v>
+        <v>96554.39999999999</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94374.5</v>
+        <v>94271.89999999999</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95423.10000000001</v>
+        <v>95319.39999999999</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96471.7</v>
+        <v>96366.8</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96471.7</v>
+        <v>96366.8</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95423.10000000001</v>
+        <v>95319.39999999999</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95423.10000000001</v>
+        <v>95319.39999999999</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60132</v>
+        <v>60066.8</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35748.9</v>
+        <v>35709.9</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19448.1</v>
+        <v>19426.7</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19664.2</v>
+        <v>19642.6</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19880.3</v>
+        <v>19858.4</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6698.8</v>
+        <v>6691.4</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -43391,37 +43391,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64609.1</v>
+        <v>64566.1</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63106.9</v>
+        <v>63036.4</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63808.1</v>
+        <v>63736.8</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64509.3</v>
+        <v>64437.2</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64509.3</v>
+        <v>64437.2</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63808.1</v>
+        <v>63736.8</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63808.1</v>
+        <v>63736.8</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64509.3</v>
+        <v>64437.2</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64509.3</v>
+        <v>64437.2</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63106.9</v>
+        <v>63036.4</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21035.6</v>
+        <v>21012.1</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -43909,367 +43909,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1351.18)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1348.08)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
     </row>
@@ -49557,7 +49557,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260930800251</t>
+          <t>20261007800209</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -49574,46 +49574,46 @@
         <v>2</v>
       </c>
       <c r="AA73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AB73" s="26" t="n">
-        <v>14.001</v>
+        <v>14.003</v>
       </c>
       <c r="AC73" s="26" t="n">
-        <v>14.001</v>
+        <v>14.003</v>
       </c>
       <c r="AD73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AE73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AF73" s="26" t="n">
-        <v>13.847</v>
+        <v>13.849</v>
       </c>
       <c r="AG73" s="26" t="n">
-        <v>14.001</v>
+        <v>14.003</v>
       </c>
       <c r="AH73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AI73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AJ73" s="26" t="n">
-        <v>13.847</v>
+        <v>13.849</v>
       </c>
       <c r="AK73" s="26" t="n">
-        <v>14.001</v>
+        <v>14.003</v>
       </c>
       <c r="AL73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AM73" s="26" t="n">
-        <v>14.155</v>
+        <v>14.157</v>
       </c>
       <c r="AN73" s="26" t="n">
-        <v>13.846</v>
+        <v>13.845</v>
       </c>
       <c r="FG73" s="35" t="n">
         <v>0</v>
@@ -49633,7 +49633,7 @@
         <v>1</v>
       </c>
       <c r="FM73" s="26" t="n">
-        <v>198.629</v>
+        <v>198.654</v>
       </c>
       <c r="FN73" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20260930800251</t>
+          <t>20261007800209</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -57799,7 +57799,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>20260930800251</t>
+          <t>20261007800209</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -57808,10 +57808,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>260922.379</v>
+        <v>260955.951</v>
       </c>
       <c r="E170" t="n">
-        <v>198.629</v>
+        <v>198.654</v>
       </c>
       <c r="F170" t="n">
         <v>1313.62</v>
@@ -58117,7 +58117,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -63378,7 +63378,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -65542,7 +65542,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1974.4</v>
+        <v>1974.2</v>
       </c>
     </row>
     <row r="30">
@@ -65562,7 +65562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.77</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="32">
@@ -65572,7 +65572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="33">
@@ -65582,7 +65582,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2368</v>
+        <v>0.2367</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1468,7 +1468,7 @@
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1601억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 3억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 646억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1600억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 3억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 645억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
@@ -2161,7 +2161,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4799억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4798억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2221,7 +2221,7 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4799억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4798억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3680,7 +3680,7 @@
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1601억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 3억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 646억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1600억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 3억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 645억 중 10억 제외(패널 신규수주 규모만큼, 2%)
 [sls_link]</t>
       </text>
     </comment>
@@ -4969,7 +4969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.7 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.6 백만원</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1850.6</v>
+        <v>1850.5</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.07</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="32">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="33">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14940</v>
+        <v>14310</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9166,7 +9166,7 @@
         <v>12910</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>14520</v>
+        <v>13900</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15175</v>
+        <v>14984</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10486,36 +10486,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.004368966</v>
+        <v>-0.005566257</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>0.003429686</v>
+        <v>-0.004754036</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.001748146</v>
+        <v>0.010147424</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.000626093</v>
+        <v>-0.001038769</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.001546539</v>
+        <v>0.010410553</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>0.000494766</v>
+        <v>-0.000613912</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.00105482</v>
+        <v>-0.002148235</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.005557823</v>
+        <v>0.004482581</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.006799089</v>
+        <v>0.005874669</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.000375899</v>
+        <v>0.001011393</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10614,36 +10614,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.004368966</v>
+        <v>-0.005566257</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.003429686</v>
+        <v>-0.004754036</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.001748146</v>
+        <v>0.010147424</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.000626093</v>
+        <v>-0.001038769</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.001546539</v>
+        <v>0.010410553</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.000494766</v>
+        <v>-0.000613912</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.00105482</v>
+        <v>-0.002148235</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.005557823</v>
+        <v>0.004482581</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.006799089</v>
+        <v>0.005874669</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.000375899</v>
+        <v>0.001011393</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10873,33 +10873,33 @@
         <v>-0.181163521</v>
       </c>
       <c r="AD31" s="32" t="n">
-        <v>-0.261676584</v>
+        <v>-0.261652121</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="32" t="n">
-        <v>-0.358950996</v>
+        <v>-0.35893082</v>
       </c>
       <c r="AG31" s="32" t="n">
-        <v>-0.578847396</v>
+        <v>-0.578810001</v>
       </c>
       <c r="AH31" s="32" t="n">
-        <v>-0.959561869</v>
+        <v>-0.959384011</v>
       </c>
       <c r="AI31" s="32" t="n">
-        <v>-22.588770865</v>
+        <v>-22.486404834</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="32" t="n">
-        <v>1.06825051</v>
+        <v>1.068475816</v>
       </c>
       <c r="AL31" s="32" t="n">
-        <v>0.5257774</v>
+        <v>0.525831011</v>
       </c>
       <c r="AM31" s="32" t="n">
-        <v>0.308746882</v>
+        <v>0.308767514</v>
       </c>
       <c r="AN31" s="32" t="n">
-        <v>0.217027613</v>
+        <v>0.217030185</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -11001,33 +11001,33 @@
         <v>0.128517937</v>
       </c>
       <c r="AD32" s="32" t="n">
-        <v>0.134693479</v>
+        <v>0.134680887</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="32" t="n">
-        <v>0.120222278</v>
+        <v>0.120220838</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.110943254</v>
+        <v>0.110944628</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>0.069720005</v>
+        <v>0.069718553</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>0.062043742</v>
+        <v>0.062044518</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>0.059643622</v>
+        <v>0.059644324</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>0.05729756</v>
+        <v>0.057298196</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>0.04855464</v>
+        <v>0.04855515</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>0.042599818</v>
+        <v>0.042598575</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11727,33 +11727,33 @@
         <v>2223.080436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2788.182596</v>
+        <v>2787.931739</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2773.146428</v>
+        <v>2773.134183</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2780.051506</v>
+        <v>2780.039459</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>908.748145</v>
+        <v>908.736296</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>633.918145</v>
+        <v>633.906296</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>627.041506</v>
+        <v>627.029459</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>627.041506</v>
+        <v>627.029459</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>633.923459</v>
+        <v>633.914746</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>633.957708</v>
+        <v>633.944461</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12028,39 +12028,39 @@
         <v>0.090156078</v>
       </c>
       <c r="AD40" s="32" t="n">
-        <v>0.09507547399999999</v>
+        <v>0.09507544699999999</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="32" t="n">
-        <v>0.096055928</v>
+        <v>0.09605670199999999</v>
       </c>
       <c r="AG40" s="32" t="n">
-        <v>0.097963865</v>
+        <v>0.097964647</v>
       </c>
       <c r="AH40" s="32" t="n">
-        <v>0.09878822399999999</v>
+        <v>0.098789774</v>
       </c>
       <c r="AI40" s="32" t="n">
-        <v>0.099637802</v>
+        <v>0.099639609</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="32" t="n">
-        <v>0.100934138</v>
+        <v>0.10093597</v>
       </c>
       <c r="AL40" s="32" t="n">
-        <v>0.101624286</v>
+        <v>0.101626114</v>
       </c>
       <c r="AM40" s="32" t="n">
-        <v>0.09919356</v>
+        <v>0.09919504699999999</v>
       </c>
       <c r="AN40" s="32" t="n">
-        <v>0.097285439</v>
+        <v>0.097278107</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12405,11 +12405,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>14940</v>
+        <v>14310</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,320원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,440원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2199955390469948</v>
+        <v>0.2199982702033422</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359731047190022</v>
+        <v>0.05359741940238421</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03235211495639615</v>
+        <v>0.03235274440897308</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870745062218841</v>
+        <v>0.07870774868272952</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -42482,277 +42482,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
     </row>
     <row r="15">
@@ -42869,277 +42869,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1378.16</v>
+        <v>1377.59</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1384.54</v>
+        <v>1384.51</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1396.85</v>
+        <v>1396.82</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1400.57</v>
+        <v>1400.54</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1404.26</v>
+        <v>1404.23</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1409.4</v>
+        <v>1409.38</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1414.29</v>
+        <v>1414.26</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1415.17</v>
+        <v>1415.14</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1413.34</v>
+        <v>1413.31</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1410.89</v>
+        <v>1410.87</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1413.93</v>
+        <v>1413.9</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1416.67</v>
+        <v>1416.64</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1420.18</v>
+        <v>1420.15</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1424.63</v>
+        <v>1424.6</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1425.22</v>
+        <v>1425.19</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1424.72</v>
+        <v>1424.69</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1400.92</v>
+        <v>1400.89</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1424.38</v>
+        <v>1424.35</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1428.06</v>
+        <v>1428.03</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1425.84</v>
+        <v>1425.81</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1425.84</v>
+        <v>1425.81</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1425.84</v>
+        <v>1425.81</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1413.79</v>
+        <v>1413.76</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1408.96</v>
+        <v>1408.93</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1408.96</v>
+        <v>1408.93</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1408.96</v>
+        <v>1408.93</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1408.96</v>
+        <v>1408.93</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1411.13</v>
+        <v>1411.11</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1417.75</v>
+        <v>1417.72</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1417.75</v>
+        <v>1417.72</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1420.02</v>
+        <v>1420</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1427.92</v>
+        <v>1427.89</v>
       </c>
     </row>
     <row r="16">
@@ -43256,94 +43256,94 @@
         <v>338133.5</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392305.1</v>
+        <v>392144.6</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363027.4</v>
+        <v>363020.4</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332476.4</v>
+        <v>332470</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>322759.2</v>
+        <v>322753</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310135.5</v>
+        <v>310129.5</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289398.4</v>
+        <v>289392.8</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281446.1</v>
+        <v>281440.8</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237746.9</v>
+        <v>237742.4</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203062.4</v>
+        <v>203058.5</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183141.1</v>
+        <v>183137.6</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129483.9</v>
+        <v>129481.4</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103443</v>
+        <v>103441.1</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84230.10000000001</v>
+        <v>84228.5</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53144.9</v>
+        <v>53143.9</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50271.6</v>
+        <v>50270.6</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42910</v>
+        <v>42909.1</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21368.6</v>
+        <v>21368.2</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18513.3</v>
+        <v>18512.9</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17207.3</v>
+        <v>17207</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15942.6</v>
+        <v>15942.3</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15942.6</v>
+        <v>15942.3</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15769.3</v>
+        <v>15769</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10812.6</v>
+        <v>10812.4</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9695.799999999999</v>
+        <v>9695.700000000001</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9695.799999999999</v>
+        <v>9695.700000000001</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9485.1</v>
+        <v>9484.9</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9590.5</v>
+        <v>9590.299999999999</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8419.200000000001</v>
+        <v>8419</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6025.4</v>
+        <v>6025.3</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5894.4</v>
+        <v>5894.3</v>
       </c>
       <c r="BQ16" s="18" t="n">
         <v>2535.2</v>
@@ -43553,31 +43553,31 @@
         <v>665352</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296569.8</v>
+        <v>1296409.3</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1328398.5</v>
+        <v>1328372.9</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1011653.8</v>
+        <v>1011634.5</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>500298.1</v>
+        <v>500288.6</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167695.1</v>
+        <v>167691.8</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67605.8</v>
+        <v>67604.5</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>45973.5</v>
+        <v>45972.8</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33520.2</v>
+        <v>33519.5</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10150.2</v>
+        <v>10150.1</v>
       </c>
       <c r="EQ16" s="18" t="n">
         <v>3413.1</v>
@@ -43739,43 +43739,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>161120.5</v>
+        <v>161056.5</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157308.3</v>
+        <v>157305.3</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159056.2</v>
+        <v>159053.1</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160804</v>
+        <v>160801</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160804</v>
+        <v>160801</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159056.2</v>
+        <v>159053.1</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159056.2</v>
+        <v>159053.1</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124504</v>
+        <v>124501.6</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100147.1</v>
+        <v>100145.2</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82463.2</v>
+        <v>82461.60000000001</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40654.7</v>
+        <v>40653.9</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19858.4</v>
+        <v>19858.1</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6691.4</v>
+        <v>6691.3</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44036,16 +44036,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401844.1</v>
+        <v>401780.1</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>637972.5</v>
+        <v>637960.4</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>542763.5</v>
+        <v>542753</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149667.7</v>
+        <v>149664.9</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44222,43 +44222,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96554.39999999999</v>
+        <v>96516.5</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94271.89999999999</v>
+        <v>94270.10000000001</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95319.39999999999</v>
+        <v>95317.60000000001</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96366.8</v>
+        <v>96365</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96366.8</v>
+        <v>96365</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95319.39999999999</v>
+        <v>95317.60000000001</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95319.39999999999</v>
+        <v>95317.60000000001</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60066.8</v>
+        <v>60065.7</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35709.9</v>
+        <v>35709.2</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19426.7</v>
+        <v>19426.4</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19642.6</v>
+        <v>19642.2</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19858.4</v>
+        <v>19858.1</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6691.4</v>
+        <v>6691.3</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44609,37 +44609,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64566.1</v>
+        <v>64540.1</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63036.4</v>
+        <v>63035.2</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63736.8</v>
+        <v>63735.6</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64437.2</v>
+        <v>64436</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64437.2</v>
+        <v>64436</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63736.8</v>
+        <v>63735.6</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63736.8</v>
+        <v>63735.6</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64437.2</v>
+        <v>64436</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64437.2</v>
+        <v>64436</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63036.4</v>
+        <v>63035.2</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21012.1</v>
+        <v>21011.7</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45127,367 +45127,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1348.08)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1346.2)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
     </row>
@@ -60789,7 +60789,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -66306,7 +66306,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -163,8 +163,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -843,62 +843,62 @@
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0045(r4)
+max(세전, 0) × 세율 0.5%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0045(r4)
+max(세전, 0) × 세율 0.5%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0315(r4)
+max(세전, 0) × 세율 3.1%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0584(r4)
+max(세전, 0) × 세율 5.8%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0853(r4)
+max(세전, 0) × 세율 8.5%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1123(r4)
+max(세전, 0) × 세율 11.2%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1392(r4)
+max(세전, 0) × 세율 13.9%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1661(r4)
+max(세전, 0) × 세율 16.6%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1931(r4)
+max(세전, 0) × 세율 19.3%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.22(r4)
+max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -1462,121 +1462,121 @@
     <comment ref="AC38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1050억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 6734억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 71억 중 1억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1051억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 6734억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 71억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1600억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 3억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 645억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1563억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 12억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 630억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1573억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1580억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 24억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 637억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 40억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 56억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1580억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 73억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 637억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1580억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 88억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 637억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1235억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 100억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1245억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 991억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 107억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)</t>
+SLS 해양 원화 1001억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AC40" authorId="0" shapeId="0">
@@ -2137,55 +2137,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3177억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3277억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3604억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3824억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4038억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4373억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4486억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4798억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5096억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5400억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6336억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5710억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5987억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2197,55 +2197,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3177억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3277억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3604억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3824억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4038억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4373억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4486억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4798억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5096억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5400억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6336억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5710억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5987억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2521,61 +2521,61 @@
     </comment>
     <comment ref="AC16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.5%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AD16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.5%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AF16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 3.1%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AG16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 5.8%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AH16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 8.5%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AI16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 11.2%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AK16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 13.9%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AL16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 16.6%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AM16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 19.3%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AN16" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
@@ -3674,61 +3674,61 @@
     </comment>
     <comment ref="AC36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1050억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 6734억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 71억 중 1억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1051억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 6734억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 71억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1600억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 3억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 645억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1563억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 12억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 630억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1573억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1580억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 24억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 637억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 40억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 56억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1580억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 73억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 637억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1580억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 88억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 637억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1235억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 100억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1245억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 991억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 중 패널 신규수주 규모만큼(2%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 107억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 644억 중 10억 제외(패널 신규수주 규모만큼, 2%)
+        <t>추정: SLS 해양 원화 1001억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -3744,61 +3744,61 @@
     </comment>
     <comment ref="AC37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN37" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(특수선·상선, 제외 수리)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
@@ -4349,152 +4349,152 @@
   <commentList>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="F12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="I12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 existing_only ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="F18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="I18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="M18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="N18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="O18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="P18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 conservative ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="I24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>공시 계약 원장 체결 속도 optimistic ledger_signing_rate(억원) · 폴백·저신뢰 — 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원)</t>
       </text>
     </comment>
   </commentList>
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 0.45% → 22%(terminal, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프) — 이월결손 램프(assumptions.tax_schedule): 변수 drv:법인세비용 추정 분기 셀이 분기별 세율(3절 '세율' 스칼라 연결 안 됨 — 그 값은 시작 세율) · 근거: 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
     </row>
@@ -4976,14 +4976,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 통계 흐름, 공시 계약 개별 반영 아님). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
+          <t>· 신규수주 — 공시 계약 원장 체결 속도 폴백(저신뢰) base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 공시 계약은 체결 분기별로 패널 신규수주와 상계(SLS 일정 유지)). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율, 선표 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율, 선표 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(이월결손 램프(assumptions.tax_schedule, 0.45%→22%) — 분기별 세율 드라이버 행 사용)</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(covered_scope_new_revenue, 미보정 book-value proxy, status partial; FY합 502억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 특수선·상선 (제외 수리)만 덮고 제외 부문(수리)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 3% 수준(분기 평균 110억 vs 공시 체결 3,640억 — 신규 매출 과소 가능 — 낙관 시나리오가 더 가깝다) / origin 이후 공시 수주 1건 6,790억 중 패널 신규수주 규모(체결 분기별 한도)만큼 2% 만 기존 SLS 에서 제외 — 나머지 98% 는 선표에 유지(패널이 공시 체결 속도보다 작음: 2026Q3 패널 110억 vs 공시 6,790억) — 추정 창 SLS −95억(2026 12억 · 2027 41억 · 2028 42억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 패널 base 신규수주 110억(6172%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 12억 vs 3억 · 2027 41억 vs 132억 · 2028 42억 vs 367억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 717억 vs 0억 · 2027 2,556억 vs 2,563억 · 2028 2,563억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1850.5</v>
+        <v>2365.5</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.73</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="32">
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2219</v>
+        <v>0.2837</v>
       </c>
     </row>
     <row r="34">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.47</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="35">
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20600</v>
+        <v>26300</v>
       </c>
     </row>
     <row r="36">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 세율</t>
+          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 분기별 세율(이월결손 램프, assumptions.tax_schedule)</t>
         </is>
       </c>
       <c r="E24" s="21">
@@ -9910,53 +9910,43 @@
         <f>IFERROR(subQ!AB16/subQ!AB15,"")</f>
         <v/>
       </c>
-      <c r="AC24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AD24" s="24">
-        <f>$D$52</f>
-        <v/>
+      <c r="AC24" s="31" t="n">
+        <v>0.004526838</v>
+      </c>
+      <c r="AD24" s="31" t="n">
+        <v>0.004527273</v>
       </c>
       <c r="AE24" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
-      <c r="AF24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AG24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AH24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AI24" s="24">
-        <f>$D$52</f>
-        <v/>
+      <c r="AF24" s="31" t="n">
+        <v>0.031459961</v>
+      </c>
+      <c r="AG24" s="31" t="n">
+        <v>0.058397494</v>
+      </c>
+      <c r="AH24" s="31" t="n">
+        <v>0.085331556</v>
+      </c>
+      <c r="AI24" s="31" t="n">
+        <v>0.112254498</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
-      <c r="AK24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AL24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AM24" s="24">
-        <f>$D$52</f>
-        <v/>
-      </c>
-      <c r="AN24" s="24">
-        <f>$D$52</f>
-        <v/>
+      <c r="AK24" s="31" t="n">
+        <v>0.139191074</v>
+      </c>
+      <c r="AL24" s="31" t="n">
+        <v>0.166124291</v>
+      </c>
+      <c r="AM24" s="31" t="n">
+        <v>0.193063022</v>
+      </c>
+      <c r="AN24" s="31" t="n">
+        <v>0.220002175</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10240,24 +10230,24 @@
         <f>subQ!AB19</f>
         <v/>
       </c>
-      <c r="AC26" s="31" t="n"/>
-      <c r="AD26" s="31" t="n"/>
+      <c r="AC26" s="32" t="n"/>
+      <c r="AD26" s="32" t="n"/>
       <c r="AE26" s="30">
         <f>subQ!AE19</f>
         <v/>
       </c>
-      <c r="AF26" s="31" t="n"/>
-      <c r="AG26" s="31" t="n"/>
-      <c r="AH26" s="31" t="n"/>
-      <c r="AI26" s="31" t="n"/>
+      <c r="AF26" s="32" t="n"/>
+      <c r="AG26" s="32" t="n"/>
+      <c r="AH26" s="32" t="n"/>
+      <c r="AI26" s="32" t="n"/>
       <c r="AJ26" s="30">
         <f>subQ!AJ19</f>
         <v/>
       </c>
-      <c r="AK26" s="31" t="n"/>
-      <c r="AL26" s="31" t="n"/>
-      <c r="AM26" s="31" t="n"/>
-      <c r="AN26" s="31" t="n"/>
+      <c r="AK26" s="32" t="n"/>
+      <c r="AL26" s="32" t="n"/>
+      <c r="AM26" s="32" t="n"/>
+      <c r="AN26" s="32" t="n"/>
       <c r="AO26" s="30">
         <f>subQ!AO19</f>
         <v/>
@@ -10357,36 +10347,36 @@
         <f>IFERROR(subQ!AB21/subQ!AA21-1,"")</f>
         <v/>
       </c>
-      <c r="AC27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="32" t="n">
+      <c r="AC27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AE27" s="25" t="n"/>
-      <c r="AF27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="32" t="n">
+      <c r="AF27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" s="25" t="n"/>
-      <c r="AK27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="32" t="n">
+      <c r="AK27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AO27" s="25" t="n"/>
@@ -10486,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.005566257</v>
+        <v>-0.003211096</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>-0.004754036</v>
+        <v>-0.008321265</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.010147424</v>
+        <v>0.009395171000000001</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>-0.001038769</v>
+        <v>0.001567568</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.010410553</v>
+        <v>0.000153177</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>-0.000613912</v>
+        <v>0.002046002</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.002148235</v>
+        <v>0.013380828</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.004482581</v>
+        <v>-0.002340945</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.005874669</v>
+        <v>0.007603446</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>0.001011393</v>
+        <v>-0.007123131</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10614,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.005566257</v>
+        <v>-0.003211096</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>-0.004754036</v>
+        <v>-0.008321265</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.010147424</v>
+        <v>0.009395171000000001</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>-0.001038769</v>
+        <v>0.001567568</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.010410553</v>
+        <v>0.000153177</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>-0.000613912</v>
+        <v>0.002046002</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.002148235</v>
+        <v>0.013380828</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.004482581</v>
+        <v>-0.002340945</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.005874669</v>
+        <v>0.007603446</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0.001011393</v>
+        <v>-0.007123131</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10741,36 +10731,36 @@
         <f>IFERROR(subQ!AB24/subQ!AA24-1,"")</f>
         <v/>
       </c>
-      <c r="AC30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="32" t="n">
+      <c r="AC30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AE30" s="25" t="n"/>
-      <c r="AF30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="32" t="n">
+      <c r="AF30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
-      <c r="AK30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="32" t="n">
+      <c r="AK30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AO30" s="25" t="n"/>
@@ -10869,37 +10859,37 @@
         <f>IFERROR(subQ!AB25/subQ!AA25-1,"")</f>
         <v/>
       </c>
-      <c r="AC31" s="32" t="n">
-        <v>-0.181163521</v>
-      </c>
-      <c r="AD31" s="32" t="n">
-        <v>-0.261652121</v>
+      <c r="AC31" s="31" t="n">
+        <v>-0.231261925</v>
+      </c>
+      <c r="AD31" s="31" t="n">
+        <v>-0.356667774</v>
       </c>
       <c r="AE31" s="25" t="n"/>
-      <c r="AF31" s="32" t="n">
-        <v>-0.35893082</v>
-      </c>
-      <c r="AG31" s="32" t="n">
-        <v>-0.578810001</v>
-      </c>
-      <c r="AH31" s="32" t="n">
-        <v>-0.959384011</v>
-      </c>
-      <c r="AI31" s="32" t="n">
-        <v>-22.486404834</v>
+      <c r="AF31" s="31" t="n">
+        <v>-0.556148487</v>
+      </c>
+      <c r="AG31" s="31" t="n">
+        <v>-1.316907353</v>
+      </c>
+      <c r="AH31" s="31" t="n">
+        <v>3.160679577</v>
+      </c>
+      <c r="AI31" s="31" t="n">
+        <v>0.783618243</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
-      <c r="AK31" s="32" t="n">
-        <v>1.068475816</v>
-      </c>
-      <c r="AL31" s="32" t="n">
-        <v>0.525831011</v>
-      </c>
-      <c r="AM31" s="32" t="n">
-        <v>0.308767514</v>
-      </c>
-      <c r="AN31" s="32" t="n">
-        <v>0.217030185</v>
+      <c r="AK31" s="31" t="n">
+        <v>0.478969016</v>
+      </c>
+      <c r="AL31" s="31" t="n">
+        <v>0.347905366</v>
+      </c>
+      <c r="AM31" s="31" t="n">
+        <v>0.250526756</v>
+      </c>
+      <c r="AN31" s="31" t="n">
+        <v>0.195352294</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10997,37 +10987,37 @@
         <f>IFERROR(subQ!AB26/subQ!AA26-1,"")</f>
         <v/>
       </c>
-      <c r="AC32" s="32" t="n">
-        <v>0.128517937</v>
-      </c>
-      <c r="AD32" s="32" t="n">
-        <v>0.134680887</v>
+      <c r="AC32" s="31" t="n">
+        <v>0.164057893</v>
+      </c>
+      <c r="AD32" s="31" t="n">
+        <v>0.167093931</v>
       </c>
       <c r="AE32" s="25" t="n"/>
-      <c r="AF32" s="32" t="n">
-        <v>0.120220838</v>
-      </c>
-      <c r="AG32" s="32" t="n">
-        <v>0.110944628</v>
-      </c>
-      <c r="AH32" s="32" t="n">
-        <v>0.069718553</v>
-      </c>
-      <c r="AI32" s="32" t="n">
-        <v>0.062044518</v>
+      <c r="AF32" s="31" t="n">
+        <v>0.143620707</v>
+      </c>
+      <c r="AG32" s="31" t="n">
+        <v>0.131988842</v>
+      </c>
+      <c r="AH32" s="31" t="n">
+        <v>0.088685503</v>
+      </c>
+      <c r="AI32" s="31" t="n">
+        <v>0.084030807</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
-      <c r="AK32" s="32" t="n">
-        <v>0.059644324</v>
-      </c>
-      <c r="AL32" s="32" t="n">
-        <v>0.057298196</v>
-      </c>
-      <c r="AM32" s="32" t="n">
-        <v>0.04855515</v>
-      </c>
-      <c r="AN32" s="32" t="n">
-        <v>0.042598575</v>
+      <c r="AK32" s="31" t="n">
+        <v>0.08450875400000001</v>
+      </c>
+      <c r="AL32" s="31" t="n">
+        <v>0.083710786</v>
+      </c>
+      <c r="AM32" s="31" t="n">
+        <v>0.07497568</v>
+      </c>
+      <c r="AN32" s="31" t="n">
+        <v>0.068011</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11224,36 +11214,36 @@
         <f>IFERROR(subQ!AB28/subQ!W28-1,"")</f>
         <v/>
       </c>
-      <c r="AC34" s="32" t="n">
+      <c r="AC34" s="31" t="n">
         <v>-0.332987121</v>
       </c>
-      <c r="AD34" s="32" t="n">
+      <c r="AD34" s="31" t="n">
         <v>-0.012303906</v>
       </c>
       <c r="AE34" s="25" t="n"/>
-      <c r="AF34" s="32" t="n">
+      <c r="AF34" s="31" t="n">
         <v>0.012614317</v>
       </c>
-      <c r="AG34" s="32" t="n">
+      <c r="AG34" s="31" t="n">
         <v>0.157117117</v>
       </c>
-      <c r="AH34" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="32" t="n">
+      <c r="AH34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
-      <c r="AK34" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="32" t="n">
+      <c r="AK34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AO34" s="25" t="n"/>
@@ -11451,36 +11441,36 @@
         <f>IFERROR(subQ!AB30/subQ!AA30-1,"")</f>
         <v/>
       </c>
-      <c r="AC36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="32" t="n">
+      <c r="AC36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AE36" s="25" t="n"/>
-      <c r="AF36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" s="32" t="n">
+      <c r="AF36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
-      <c r="AK36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="32" t="n">
+      <c r="AK36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AO36" s="25" t="n"/>
@@ -11597,7 +11587,7 @@
         <f>subQ!AB33</f>
         <v/>
       </c>
-      <c r="AC37" s="31" t="n"/>
+      <c r="AC37" s="32" t="n"/>
       <c r="AD37" s="29" t="n">
         <v>0</v>
       </c>
@@ -11605,9 +11595,9 @@
         <f>subQ!AE33</f>
         <v/>
       </c>
-      <c r="AF37" s="31" t="n"/>
-      <c r="AG37" s="31" t="n"/>
-      <c r="AH37" s="31" t="n"/>
+      <c r="AF37" s="32" t="n"/>
+      <c r="AG37" s="32" t="n"/>
+      <c r="AH37" s="32" t="n"/>
       <c r="AI37" s="29" t="n">
         <v>0</v>
       </c>
@@ -11615,9 +11605,9 @@
         <f>subQ!AJ33</f>
         <v/>
       </c>
-      <c r="AK37" s="31" t="n"/>
-      <c r="AL37" s="31" t="n"/>
-      <c r="AM37" s="31" t="n"/>
+      <c r="AK37" s="32" t="n"/>
+      <c r="AL37" s="32" t="n"/>
+      <c r="AM37" s="32" t="n"/>
       <c r="AN37" s="29" t="n">
         <v>0</v>
       </c>
@@ -11724,36 +11714,36 @@
         <v/>
       </c>
       <c r="AC38" s="29" t="n">
-        <v>2223.080436</v>
+        <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2787.931739</v>
+        <v>2798.391739</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2773.134183</v>
+        <v>2783.344183</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2780.039459</v>
+        <v>2790.359459</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>908.736296</v>
+        <v>919.176296</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>633.906296</v>
+        <v>644.3462960000001</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>627.029459</v>
+        <v>637.359459</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>627.029459</v>
+        <v>637.359459</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>633.914746</v>
+        <v>644.354746</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>633.944461</v>
+        <v>644.384461</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -11770,7 +11760,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>매출조선신규 (forecast_panel base 신규수주 매출, 억원 — 가정)</t>
+          <t>매출조선신규 (공시 계약 원장 체결 속도 폴백 신규수주 매출, 억원 — 가정)</t>
         </is>
       </c>
       <c r="E39" s="26">
@@ -11873,39 +11863,39 @@
         <v>0</v>
       </c>
       <c r="AD39" s="29" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AE39" s="30">
         <f>subQ!AE37</f>
         <v/>
       </c>
       <c r="AF39" s="29" t="n">
-        <v>11.75</v>
+        <v>102.88</v>
       </c>
       <c r="AG39" s="29" t="n">
-        <v>24.37</v>
+        <v>381.61</v>
       </c>
       <c r="AH39" s="29" t="n">
-        <v>39.64</v>
+        <v>791.37</v>
       </c>
       <c r="AI39" s="29" t="n">
-        <v>56.19</v>
+        <v>1287.31</v>
       </c>
       <c r="AJ39" s="30">
         <f>subQ!AJ37</f>
         <v/>
       </c>
       <c r="AK39" s="29" t="n">
-        <v>72.63</v>
+        <v>1824.59</v>
       </c>
       <c r="AL39" s="29" t="n">
-        <v>87.58</v>
+        <v>2358.38</v>
       </c>
       <c r="AM39" s="29" t="n">
-        <v>99.66</v>
+        <v>2843.84</v>
       </c>
       <c r="AN39" s="29" t="n">
-        <v>107.49</v>
+        <v>3236.14</v>
       </c>
       <c r="AO39" s="30">
         <f>subQ!AO37</f>
@@ -12024,43 +12014,43 @@
         <f>IFERROR(subQ!AB38/subQ!AB36,"")</f>
         <v/>
       </c>
-      <c r="AC40" s="32" t="n">
-        <v>0.090156078</v>
-      </c>
-      <c r="AD40" s="32" t="n">
-        <v>0.09507544699999999</v>
+      <c r="AC40" s="31" t="n">
+        <v>0.09015805</v>
+      </c>
+      <c r="AD40" s="31" t="n">
+        <v>0.095074623</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
-      <c r="AF40" s="32" t="n">
-        <v>0.09605670199999999</v>
-      </c>
-      <c r="AG40" s="32" t="n">
-        <v>0.097964647</v>
-      </c>
-      <c r="AH40" s="32" t="n">
-        <v>0.098789774</v>
-      </c>
-      <c r="AI40" s="32" t="n">
-        <v>0.099639609</v>
+      <c r="AF40" s="31" t="n">
+        <v>0.096058168</v>
+      </c>
+      <c r="AG40" s="31" t="n">
+        <v>0.09796516</v>
+      </c>
+      <c r="AH40" s="31" t="n">
+        <v>0.098788053</v>
+      </c>
+      <c r="AI40" s="31" t="n">
+        <v>0.099636655</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
-      <c r="AK40" s="32" t="n">
-        <v>0.10093597</v>
-      </c>
-      <c r="AL40" s="32" t="n">
-        <v>0.101626114</v>
-      </c>
-      <c r="AM40" s="32" t="n">
-        <v>0.09919504699999999</v>
-      </c>
-      <c r="AN40" s="32" t="n">
-        <v>0.097278107</v>
+      <c r="AK40" s="31" t="n">
+        <v>0.100936424</v>
+      </c>
+      <c r="AL40" s="31" t="n">
+        <v>0.101625512</v>
+      </c>
+      <c r="AM40" s="31" t="n">
+        <v>0.099193907</v>
+      </c>
+      <c r="AN40" s="31" t="n">
+        <v>0.09728170999999999</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12152,36 +12142,36 @@
         <f>IFERROR(subQ!AB40/subQ!W40-1,"")</f>
         <v/>
       </c>
-      <c r="AC41" s="32" t="n">
+      <c r="AC41" s="31" t="n">
         <v>0.092004263</v>
       </c>
-      <c r="AD41" s="32" t="n">
+      <c r="AD41" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AE41" s="25" t="n"/>
-      <c r="AF41" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="32" t="n">
+      <c r="AF41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="31" t="n">
         <v>-0.185882655</v>
       </c>
-      <c r="AH41" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="32" t="n">
+      <c r="AH41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
-      <c r="AK41" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" s="32" t="n">
+      <c r="AK41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" s="31" t="n">
         <v>0</v>
       </c>
       <c r="AO41" s="25" t="n"/>
@@ -12298,42 +12288,42 @@
         <f>IFERROR(subQ!AB41/subQ!AB40,"")</f>
         <v/>
       </c>
-      <c r="AC42" s="32" t="n">
+      <c r="AC42" s="31" t="n">
         <v>0.090155665</v>
       </c>
-      <c r="AD42" s="32" t="n">
+      <c r="AD42" s="31" t="n">
         <v>0.09507544800000001</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE40,"")</f>
         <v/>
       </c>
-      <c r="AF42" s="32" t="n">
+      <c r="AF42" s="31" t="n">
         <v>0.096058671</v>
       </c>
-      <c r="AG42" s="32" t="n">
+      <c r="AG42" s="31" t="n">
         <v>0.097966416</v>
       </c>
-      <c r="AH42" s="32" t="n">
+      <c r="AH42" s="31" t="n">
         <v>0.098788215</v>
       </c>
-      <c r="AI42" s="32" t="n">
+      <c r="AI42" s="31" t="n">
         <v>0.099635694</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ40,"")</f>
         <v/>
       </c>
-      <c r="AK42" s="32" t="n">
+      <c r="AK42" s="31" t="n">
         <v>0.100934429</v>
       </c>
-      <c r="AL42" s="32" t="n">
+      <c r="AL42" s="31" t="n">
         <v>0.101627821</v>
       </c>
-      <c r="AM42" s="32" t="n">
+      <c r="AM42" s="31" t="n">
         <v>0.09919544499999999</v>
       </c>
-      <c r="AN42" s="32" t="n">
+      <c r="AN42" s="31" t="n">
         <v>0.097280362</v>
       </c>
       <c r="AO42" s="25">
@@ -12484,7 +12474,7 @@
           <t>COE</t>
         </is>
       </c>
-      <c r="D47" s="32" t="n">
+      <c r="D47" s="31" t="n">
         <v>0.09</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -12640,7 +12630,7 @@
           <t>EPS_Y1가중</t>
         </is>
       </c>
-      <c r="D51" s="32" t="n">
+      <c r="D51" s="31" t="n">
         <v>0.5</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -12680,11 +12670,11 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2199982702033422</v>
+        <v>0.0045</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.22) · 최근 12분기 유효세율 -14.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.5% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>참고(연결 안 됨: 이월결손 램프(assumptions.tax_schedule, 0.45%→22%) — 분기별 세율 드라이버 행 사용) — 모델 assumptions 값(시작 0.45% → terminal 22%, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프 — 분기별 값은 2절 drv:법인세비용 행) · 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q3~2026Q2) 법인세/세전 중위 0.5%·최근 4분기 중위 0.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -12719,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359741940238421</v>
+        <v>0.05359736464701333</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12797,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03235274440897308</v>
+        <v>0.03235050807878868</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12836,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870774868272952</v>
+        <v>0.07870636507277505</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -12874,7 +12864,7 @@
           <t>배당성향</t>
         </is>
       </c>
-      <c r="D57" s="32" t="n">
+      <c r="D57" s="31" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -12950,7 +12940,7 @@
           <t>헤지비율</t>
         </is>
       </c>
-      <c r="D59" s="32" t="n">
+      <c r="D59" s="31" t="n">
         <v>0.7</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -13275,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22465,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35244,11 +35234,11 @@
       <c r="AB30" s="28" t="n">
         <v>90.289</v>
       </c>
-      <c r="AC30" s="31">
+      <c r="AC30" s="32">
         <f>IFERROR(AB30*(1+변수!AC36),"")</f>
         <v/>
       </c>
-      <c r="AD30" s="31">
+      <c r="AD30" s="32">
         <f>IFERROR(AC30*(1+변수!AD36),"")</f>
         <v/>
       </c>
@@ -35256,19 +35246,19 @@
         <f>AD30</f>
         <v/>
       </c>
-      <c r="AF30" s="31">
+      <c r="AF30" s="32">
         <f>IFERROR(AD30*(1+변수!AF36),"")</f>
         <v/>
       </c>
-      <c r="AG30" s="31">
+      <c r="AG30" s="32">
         <f>IFERROR(AF30*(1+변수!AG36),"")</f>
         <v/>
       </c>
-      <c r="AH30" s="31">
+      <c r="AH30" s="32">
         <f>IFERROR(AG30*(1+변수!AH36),"")</f>
         <v/>
       </c>
-      <c r="AI30" s="31">
+      <c r="AI30" s="32">
         <f>IFERROR(AH30*(1+변수!AI36),"")</f>
         <v/>
       </c>
@@ -35276,19 +35266,19 @@
         <f>AI30</f>
         <v/>
       </c>
-      <c r="AK30" s="31">
+      <c r="AK30" s="32">
         <f>IFERROR(AI30*(1+변수!AK36),"")</f>
         <v/>
       </c>
-      <c r="AL30" s="31">
+      <c r="AL30" s="32">
         <f>IFERROR(AK30*(1+변수!AL36),"")</f>
         <v/>
       </c>
-      <c r="AM30" s="31">
+      <c r="AM30" s="32">
         <f>IFERROR(AL30*(1+변수!AM36),"")</f>
         <v/>
       </c>
-      <c r="AN30" s="31">
+      <c r="AN30" s="32">
         <f>IFERROR(AM30*(1+변수!AN36),"")</f>
         <v/>
       </c>
@@ -36184,7 +36174,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매출 조선·해양(방산·신조선·상선·특수선) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(방산·신조선·상선·특수선) 신규수주(원장 체결 속도(폴백) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E37" s="18" t="n"/>
@@ -59216,7 +59206,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님 · ※ 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 특수선·상선 (제외 수리)만 덮고 제외 부문(수리)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 3% 수준(분기 평균 110억 vs 공시 체결 3,640억 — 신규 매출 과소 가능 — 낙관 시나리오가 더 가깝다)</t>
+          <t>출처: 공시 계약 원장(sls.contracts) 체결 분기 min/median/max × forecast_panel 역산 커널(covered_scope_new_revenue) (억원) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님 · ※ 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억)</t>
         </is>
       </c>
     </row>
@@ -60000,39 +59990,39 @@
         <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="G18" s="20">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>8.51</v>
+        <v>102.59</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>17.64</v>
+        <v>380.45</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>28.68</v>
+        <v>788.71</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>40.63</v>
+        <v>1282.51</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
-        <v>52.49</v>
+        <v>1816.96</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>63.25</v>
+        <v>2347.21</v>
       </c>
       <c r="O18" s="34" t="n">
-        <v>71.91</v>
+        <v>2828.38</v>
       </c>
       <c r="P18" s="34" t="n">
-        <v>77.45999999999999</v>
+        <v>3215.61</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -60306,39 +60296,39 @@
         <v>0</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>78.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="G24" s="20">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>290.36</v>
+        <v>110.44</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>602.01</v>
+        <v>409.59</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>979.04</v>
+        <v>849.21</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>1387.26</v>
+        <v>1381.06</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>1792.48</v>
+        <v>1956.92</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>2160.49</v>
+        <v>2528.52</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>2457.09</v>
+        <v>3047.64</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>2648.09</v>
+        <v>3466.04</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -64314,43 +64304,43 @@
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="X30" s="31">
+      <c r="X30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(X$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y30" s="31">
+      <c r="Y30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(Y$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z30" s="31">
+      <c r="Z30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(Z$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA30" s="31">
+      <c r="AA30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AA$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB30" s="31">
+      <c r="AB30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AB$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC30" s="31">
+      <c r="AC30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AC$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD30" s="31">
+      <c r="AD30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AD$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE30" s="31">
+      <c r="AE30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AE$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF30" s="31">
+      <c r="AF30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AF$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG30" s="31">
+      <c r="AG30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(AG$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -65131,7 +65121,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매출 조선·해양(방산·신조선·상선·특수선) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(방산·신조선·상선·특수선) 신규수주(원장 체결 속도(폴백) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E37" s="18">
@@ -67507,15 +67497,15 @@
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L30" s="31">
+      <c r="L30" s="32">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -67792,7 +67782,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매출 조선·해양(방산·신조선·상선·특수선) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(방산·신조선·상선·특수선) 신규수주(원장 체결 속도(폴백) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E37" s="18">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1468,55 +1468,55 @@
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1573억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1245억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1001억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2149,7 +2149,7 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4373억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4374억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2173,19 +2173,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6336억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6868억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7383억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,7 +2209,7 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4373억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4374억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2233,19 +2233,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6336억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6868억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7383억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3680,55 +3680,55 @@
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1611억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1573억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1245억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1001억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4955,7 +4955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.24% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 3.23% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.6 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.7 백만원</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 717억 vs 0억 · 2027 2,556억 vs 2,563억 · 2028 2,563억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 717억 vs 0억 · 2027 2,559억 vs 2,563억 · 2028 2,566억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2365.5</v>
+        <v>2365.9</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.05</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="32">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="33">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14310</v>
+        <v>14250</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>14984</v>
+        <v>14972</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9914,39 +9914,39 @@
         <v>0.004526838</v>
       </c>
       <c r="AD24" s="31" t="n">
-        <v>0.004527273</v>
+        <v>0.004527437</v>
       </c>
       <c r="AE24" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF24" s="31" t="n">
-        <v>0.031459961</v>
+        <v>0.031451641</v>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>0.058397494</v>
+        <v>0.058399517</v>
       </c>
       <c r="AH24" s="31" t="n">
-        <v>0.085331556</v>
+        <v>0.085323948</v>
       </c>
       <c r="AI24" s="31" t="n">
-        <v>0.112254498</v>
+        <v>0.112258494</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK24" s="31" t="n">
-        <v>0.139191074</v>
+        <v>0.139202119</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>0.166124291</v>
+        <v>0.166127055</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.193063022</v>
+        <v>0.193070703</v>
       </c>
       <c r="AN24" s="31" t="n">
-        <v>0.220002175</v>
+        <v>0.219999068</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10476,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.003211096</v>
+        <v>-0.003250629</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>-0.008321265</v>
+        <v>0.001361304</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.009395171000000001</v>
+        <v>0.008701798</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.001567568</v>
+        <v>0.001192921</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.000153177</v>
+        <v>0.001198189</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>0.002046002</v>
+        <v>-0.006061927</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>0.013380828</v>
+        <v>-0.002546604</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>-0.002340945</v>
+        <v>0.0110595</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.007603446</v>
+        <v>0.001526348</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.007123131</v>
+        <v>-0.002844643</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10604,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.003211096</v>
+        <v>-0.003250629</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>-0.008321265</v>
+        <v>0.001361304</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.009395171000000001</v>
+        <v>0.008701798</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.001567568</v>
+        <v>0.001192921</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.000153177</v>
+        <v>0.001198189</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.002046002</v>
+        <v>-0.006061927</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>0.013380828</v>
+        <v>-0.002546604</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>-0.002340945</v>
+        <v>0.0110595</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.007603446</v>
+        <v>0.001526348</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.007123131</v>
+        <v>-0.002844643</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10863,33 +10863,33 @@
         <v>-0.231261925</v>
       </c>
       <c r="AD31" s="31" t="n">
-        <v>-0.356667774</v>
+        <v>-0.356654745</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="31" t="n">
-        <v>-0.556148487</v>
+        <v>-0.556289111</v>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>-1.316907353</v>
+        <v>-1.317640347</v>
       </c>
       <c r="AH31" s="31" t="n">
-        <v>3.160679577</v>
+        <v>3.155399095</v>
       </c>
       <c r="AI31" s="31" t="n">
-        <v>0.783618243</v>
+        <v>0.783295009</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="31" t="n">
-        <v>0.478969016</v>
+        <v>0.47884511</v>
       </c>
       <c r="AL31" s="31" t="n">
-        <v>0.347905366</v>
+        <v>0.347824092</v>
       </c>
       <c r="AM31" s="31" t="n">
-        <v>0.250526756</v>
+        <v>0.250475463</v>
       </c>
       <c r="AN31" s="31" t="n">
-        <v>0.195352294</v>
+        <v>0.195309704</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10991,33 +10991,33 @@
         <v>0.164057893</v>
       </c>
       <c r="AD32" s="31" t="n">
-        <v>0.167093931</v>
+        <v>0.167087827</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="31" t="n">
-        <v>0.143620707</v>
+        <v>0.143660683</v>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>0.131988842</v>
+        <v>0.132019216</v>
       </c>
       <c r="AH32" s="31" t="n">
-        <v>0.088685503</v>
+        <v>0.088710785</v>
       </c>
       <c r="AI32" s="31" t="n">
-        <v>0.084030807</v>
+        <v>0.084051932</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="31" t="n">
-        <v>0.08450875400000001</v>
+        <v>0.084526036</v>
       </c>
       <c r="AL32" s="31" t="n">
-        <v>0.083710786</v>
+        <v>0.083721657</v>
       </c>
       <c r="AM32" s="31" t="n">
-        <v>0.07497568</v>
+        <v>0.074982308</v>
       </c>
       <c r="AN32" s="31" t="n">
-        <v>0.068011</v>
+        <v>0.068012901</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11717,33 +11717,33 @@
         <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2798.391739</v>
+        <v>2798.324508</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2783.344183</v>
+        <v>2783.993129</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2790.359459</v>
+        <v>2791.017959</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>919.176296</v>
+        <v>919.83432</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>644.3462960000001</v>
+        <v>645.00432</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>637.359459</v>
+        <v>638.017959</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>637.359459</v>
+        <v>638.017959</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>644.354746</v>
+        <v>645.016559</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>644.384461</v>
+        <v>645.046596</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12018,39 +12018,39 @@
         <v>0.09015805</v>
       </c>
       <c r="AD40" s="31" t="n">
-        <v>0.095074623</v>
+        <v>0.095076008</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="31" t="n">
-        <v>0.096058168</v>
+        <v>0.096057454</v>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>0.09796516</v>
+        <v>0.097965712</v>
       </c>
       <c r="AH40" s="31" t="n">
-        <v>0.098788053</v>
+        <v>0.09878803999999999</v>
       </c>
       <c r="AI40" s="31" t="n">
-        <v>0.099636655</v>
+        <v>0.099636168</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="31" t="n">
-        <v>0.100936424</v>
+        <v>0.10093569</v>
       </c>
       <c r="AL40" s="31" t="n">
-        <v>0.101625512</v>
+        <v>0.101627128</v>
       </c>
       <c r="AM40" s="31" t="n">
-        <v>0.099193907</v>
+        <v>0.099195134</v>
       </c>
       <c r="AN40" s="31" t="n">
-        <v>0.09728170999999999</v>
+        <v>0.09728189199999999</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>14310</v>
+        <v>14250</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,440원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,870원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359736464701333</v>
+        <v>0.05359751744267597</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03235050807878868</v>
+        <v>0.03234847773083892</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870636507277505</v>
+        <v>0.07870519551433268</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -42472,277 +42472,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
     </row>
     <row r="15">
@@ -42859,277 +42859,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1377.59</v>
+        <v>1377.46</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1384.51</v>
+        <v>1385.94</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1396.82</v>
+        <v>1398.25</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1400.54</v>
+        <v>1401.98</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1404.23</v>
+        <v>1405.66</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1409.38</v>
+        <v>1410.81</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1414.26</v>
+        <v>1415.69</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1415.14</v>
+        <v>1416.58</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1413.31</v>
+        <v>1414.74</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1410.87</v>
+        <v>1412.3</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1413.9</v>
+        <v>1415.33</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1416.64</v>
+        <v>1418.07</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1420.15</v>
+        <v>1421.58</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1424.6</v>
+        <v>1426.03</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1425.19</v>
+        <v>1426.62</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1424.69</v>
+        <v>1426.13</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1400.89</v>
+        <v>1402.32</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1424.35</v>
+        <v>1425.79</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1428.03</v>
+        <v>1429.46</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1425.81</v>
+        <v>1427.24</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1425.81</v>
+        <v>1427.24</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1425.81</v>
+        <v>1427.24</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1413.76</v>
+        <v>1415.19</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1408.93</v>
+        <v>1410.36</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1408.93</v>
+        <v>1410.36</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1408.93</v>
+        <v>1410.36</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1408.93</v>
+        <v>1410.36</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1411.11</v>
+        <v>1412.54</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1417.72</v>
+        <v>1419.15</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1417.72</v>
+        <v>1419.15</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1420</v>
+        <v>1421.43</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1427.89</v>
+        <v>1429.32</v>
       </c>
     </row>
     <row r="16">
@@ -43246,277 +43246,277 @@
         <v>338133.5</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392144.6</v>
+        <v>392105.3</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363020.4</v>
+        <v>363395.6</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332470</v>
+        <v>332810.6</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>322753</v>
+        <v>323082.7</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310129.5</v>
+        <v>310445.5</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289392.8</v>
+        <v>289686.7</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281440.8</v>
+        <v>281725.5</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237742.4</v>
+        <v>237982.8</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203058.5</v>
+        <v>203264.1</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183137.6</v>
+        <v>183323.3</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129481.4</v>
+        <v>129612.4</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103441.1</v>
+        <v>103545.6</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84228.5</v>
+        <v>84313.39999999999</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53143.9</v>
+        <v>53197.3</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50270.6</v>
+        <v>50321.1</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42909.1</v>
+        <v>42952.2</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21368.2</v>
+        <v>21390</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18512.9</v>
+        <v>18531.5</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17207</v>
+        <v>17224.3</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15942.3</v>
+        <v>15958.3</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15942.3</v>
+        <v>15958.3</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15769</v>
+        <v>15784.8</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10812.4</v>
+        <v>10823.4</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9695.700000000001</v>
+        <v>9705.5</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9695.700000000001</v>
+        <v>9705.5</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9484.9</v>
+        <v>9494.5</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9590.299999999999</v>
+        <v>9600</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8419</v>
+        <v>8427.5</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6025.3</v>
+        <v>6031.4</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5894.3</v>
+        <v>5900.2</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2535.2</v>
+        <v>2537.7</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>850.9</v>
+        <v>851.8</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>860.3</v>
+        <v>861.1</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>841.6</v>
+        <v>842.4</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>570.4</v>
+        <v>571</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -43543,76 +43543,76 @@
         <v>665352</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296409.3</v>
+        <v>1296370</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1328372.9</v>
+        <v>1329734.4</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1011634.5</v>
+        <v>1012659.1</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>500288.6</v>
+        <v>500794.7</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167691.8</v>
+        <v>167860.6</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67604.5</v>
+        <v>67672.39999999999</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>45972.8</v>
+        <v>46019.2</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33519.5</v>
+        <v>33553.4</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10150.1</v>
+        <v>10160.1</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3422.4</v>
+        <v>3425.8</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3422.4</v>
+        <v>3425.8</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3422.4</v>
+        <v>3425.8</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3413.1</v>
+        <v>3416.4</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3422.4</v>
+        <v>3425.8</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1412</v>
+        <v>1413.4</v>
       </c>
     </row>
     <row r="17">
@@ -43729,43 +43729,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>161056.5</v>
+        <v>161040.9</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157305.3</v>
+        <v>157464.1</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159053.1</v>
+        <v>159213.7</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160801</v>
+        <v>160963.3</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160801</v>
+        <v>160963.3</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159053.1</v>
+        <v>159213.7</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159053.1</v>
+        <v>159213.7</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124501.6</v>
+        <v>124627.6</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100145.2</v>
+        <v>100247.1</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82461.60000000001</v>
+        <v>82545.89999999999</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40653.9</v>
+        <v>40695.4</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19858.1</v>
+        <v>19878.1</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6691.3</v>
+        <v>6698.1</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44026,16 +44026,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401780.1</v>
+        <v>401764.5</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>637960.4</v>
+        <v>638604.4</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>542753</v>
+        <v>543302.1</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149664.9</v>
+        <v>149817.5</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44212,43 +44212,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96516.5</v>
+        <v>96507.2</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94270.10000000001</v>
+        <v>94364.2</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95317.60000000001</v>
+        <v>95412.7</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96365</v>
+        <v>96461.2</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96365</v>
+        <v>96461.2</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95317.60000000001</v>
+        <v>95412.7</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95317.60000000001</v>
+        <v>95412.7</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60065.7</v>
+        <v>60125.5</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35709.2</v>
+        <v>35745</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19426.4</v>
+        <v>19446</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19642.2</v>
+        <v>19662.1</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19858.1</v>
+        <v>19878.1</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6691.3</v>
+        <v>6698.1</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44599,37 +44599,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64540.1</v>
+        <v>64533.7</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63035.2</v>
+        <v>63099.9</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63735.6</v>
+        <v>63801</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64436</v>
+        <v>64502.1</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64436</v>
+        <v>64502.1</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63735.6</v>
+        <v>63801</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63735.6</v>
+        <v>63801</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64436</v>
+        <v>64502.1</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64436</v>
+        <v>64502.1</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63035.2</v>
+        <v>63099.9</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21011.7</v>
+        <v>21033.3</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45117,367 +45117,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1346.2)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1345.74)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1474,37 +1474,37 @@
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
@@ -2149,7 +2149,7 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4374억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4373억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2179,13 +2179,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6868억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7383억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,7 +2209,7 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4374억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4373억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2239,13 +2239,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6868억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7383억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3686,37 +3686,37 @@
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1575억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1592억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.7 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.6 백만원</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 717억 vs 0억 · 2027 2,559억 vs 2,563억 · 2028 2,566억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,558억 vs 2,563억 · 2028 2,565억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2365.9</v>
+        <v>2365.7</v>
       </c>
     </row>
     <row r="30">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9914,39 +9914,39 @@
         <v>0.004526838</v>
       </c>
       <c r="AD24" s="31" t="n">
-        <v>0.004527437</v>
+        <v>0.004527602</v>
       </c>
       <c r="AE24" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF24" s="31" t="n">
-        <v>0.031451641</v>
+        <v>0.031454969</v>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>0.058399517</v>
+        <v>0.058388922</v>
       </c>
       <c r="AH24" s="31" t="n">
-        <v>0.085323948</v>
+        <v>0.085336388</v>
       </c>
       <c r="AI24" s="31" t="n">
-        <v>0.112258494</v>
+        <v>0.112254297</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK24" s="31" t="n">
-        <v>0.139202119</v>
+        <v>0.139201673</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>0.166127055</v>
+        <v>0.166129615</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.193070703</v>
+        <v>0.193073186</v>
       </c>
       <c r="AN24" s="31" t="n">
-        <v>0.219999068</v>
+        <v>0.219997204</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10476,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.003250629</v>
+        <v>-0.002239709</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>0.001361304</v>
+        <v>-0.007732042</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.008701798</v>
+        <v>0.01938794</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.001192921</v>
+        <v>0.001789077</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.001198189</v>
+        <v>0.000648676</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>-0.006061927</v>
+        <v>0.001691458</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.002546604</v>
+        <v>-0.004143872</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.0110595</v>
+        <v>-0.0009852870000000001</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.001526348</v>
+        <v>0.007191408</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.002844643</v>
+        <v>-0.005574707</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10604,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.003250629</v>
+        <v>-0.002239709</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.001361304</v>
+        <v>-0.007732042</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.008701798</v>
+        <v>0.01938794</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.001192921</v>
+        <v>0.001789077</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.001198189</v>
+        <v>0.000648676</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>-0.006061927</v>
+        <v>0.001691458</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.002546604</v>
+        <v>-0.004143872</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.0110595</v>
+        <v>-0.0009852870000000001</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.001526348</v>
+        <v>0.007191408</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.002844643</v>
+        <v>-0.005574707</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10863,33 +10863,33 @@
         <v>-0.231261925</v>
       </c>
       <c r="AD31" s="31" t="n">
-        <v>-0.356654745</v>
+        <v>-0.356648231</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="31" t="n">
-        <v>-0.556289111</v>
+        <v>-0.556212598</v>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>-1.317640347</v>
+        <v>-1.317262937</v>
       </c>
       <c r="AH31" s="31" t="n">
-        <v>3.155399095</v>
+        <v>3.158072636</v>
       </c>
       <c r="AI31" s="31" t="n">
-        <v>0.783295009</v>
+        <v>0.783475734</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="31" t="n">
-        <v>0.47884511</v>
+        <v>0.478912303</v>
       </c>
       <c r="AL31" s="31" t="n">
-        <v>0.347824092</v>
+        <v>0.347866571</v>
       </c>
       <c r="AM31" s="31" t="n">
-        <v>0.250475463</v>
+        <v>0.250497443</v>
       </c>
       <c r="AN31" s="31" t="n">
-        <v>0.195309704</v>
+        <v>0.195330706</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10991,33 +10991,33 @@
         <v>0.164057893</v>
       </c>
       <c r="AD32" s="31" t="n">
-        <v>0.167087827</v>
+        <v>0.167084775</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="31" t="n">
-        <v>0.143660683</v>
+        <v>0.143642754</v>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>0.132019216</v>
+        <v>0.132007911</v>
       </c>
       <c r="AH32" s="31" t="n">
-        <v>0.088710785</v>
+        <v>0.088699154</v>
       </c>
       <c r="AI32" s="31" t="n">
-        <v>0.084051932</v>
+        <v>0.084044075</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="31" t="n">
-        <v>0.084526036</v>
+        <v>0.084519673</v>
       </c>
       <c r="AL32" s="31" t="n">
-        <v>0.083721657</v>
+        <v>0.083718126</v>
       </c>
       <c r="AM32" s="31" t="n">
-        <v>0.074982308</v>
+        <v>0.07497917599999999</v>
       </c>
       <c r="AN32" s="31" t="n">
-        <v>0.068012901</v>
+        <v>0.068012798</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11717,33 +11717,33 @@
         <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2798.324508</v>
+        <v>2798.235511</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2783.993129</v>
+        <v>2783.721783</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2791.017959</v>
+        <v>2790.740927</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>919.83432</v>
+        <v>919.561614</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>645.00432</v>
+        <v>644.731614</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>638.017959</v>
+        <v>637.7409270000001</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>638.017959</v>
+        <v>637.750927</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>645.016559</v>
+        <v>644.743609</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>645.046596</v>
+        <v>644.774393</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12018,39 +12018,39 @@
         <v>0.09015805</v>
       </c>
       <c r="AD40" s="31" t="n">
-        <v>0.095076008</v>
+        <v>0.09507599899999999</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="31" t="n">
-        <v>0.096057454</v>
+        <v>0.096058342</v>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>0.097965712</v>
+        <v>0.097964654</v>
       </c>
       <c r="AH40" s="31" t="n">
-        <v>0.09878803999999999</v>
+        <v>0.09878661499999999</v>
       </c>
       <c r="AI40" s="31" t="n">
-        <v>0.099636168</v>
+        <v>0.099638501</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="31" t="n">
-        <v>0.10093569</v>
+        <v>0.100934995</v>
       </c>
       <c r="AL40" s="31" t="n">
-        <v>0.101627128</v>
+        <v>0.101626387</v>
       </c>
       <c r="AM40" s="31" t="n">
-        <v>0.099195134</v>
+        <v>0.09919552</v>
       </c>
       <c r="AN40" s="31" t="n">
-        <v>0.09728189199999999</v>
+        <v>0.097282094</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359751744267597</v>
+        <v>0.0535974210343067</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03234847773083892</v>
+        <v>0.0323475708862465</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870519551433268</v>
+        <v>0.07870380316661114</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42472,277 +42472,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
     </row>
     <row r="15">
@@ -42859,277 +42859,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1377.46</v>
+        <v>1377.28</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1385.94</v>
+        <v>1385.35</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1398.25</v>
+        <v>1397.66</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1401.98</v>
+        <v>1401.38</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1405.66</v>
+        <v>1405.07</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1410.81</v>
+        <v>1410.22</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1415.69</v>
+        <v>1415.1</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1416.58</v>
+        <v>1415.98</v>
       </c>
       <c r="AU15" s="13" t="n">
+        <v>1414.15</v>
+      </c>
+      <c r="AV15" s="13" t="n">
+        <v>1411.71</v>
+      </c>
+      <c r="AW15" s="13" t="n">
         <v>1414.74</v>
       </c>
-      <c r="AV15" s="13" t="n">
-        <v>1412.3</v>
-      </c>
-      <c r="AW15" s="13" t="n">
-        <v>1415.33</v>
-      </c>
       <c r="AX15" s="13" t="n">
-        <v>1418.07</v>
+        <v>1417.48</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1421.58</v>
+        <v>1420.99</v>
       </c>
       <c r="AZ15" s="13" t="n">
+        <v>1425.44</v>
+      </c>
+      <c r="BA15" s="13" t="n">
         <v>1426.03</v>
       </c>
-      <c r="BA15" s="13" t="n">
-        <v>1426.62</v>
-      </c>
       <c r="BB15" s="13" t="n">
-        <v>1426.13</v>
+        <v>1425.53</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1402.32</v>
+        <v>1401.73</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1425.79</v>
+        <v>1425.19</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1429.46</v>
+        <v>1428.87</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1427.24</v>
+        <v>1426.65</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1427.24</v>
+        <v>1426.65</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1427.24</v>
+        <v>1426.65</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1415.19</v>
+        <v>1414.6</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1410.36</v>
+        <v>1409.77</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1410.36</v>
+        <v>1409.77</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1410.36</v>
+        <v>1409.77</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1410.36</v>
+        <v>1409.77</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1412.54</v>
+        <v>1411.95</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1419.15</v>
+        <v>1418.56</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1419.15</v>
+        <v>1418.56</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1421.43</v>
+        <v>1420.84</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1429.32</v>
+        <v>1428.73</v>
       </c>
     </row>
     <row r="16">
@@ -43246,277 +43246,277 @@
         <v>338133.5</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392105.3</v>
+        <v>392054</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363395.6</v>
+        <v>363240.6</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332810.6</v>
+        <v>332669.9</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>323082.7</v>
+        <v>322946.5</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310445.5</v>
+        <v>310315</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289686.7</v>
+        <v>289565.3</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281725.5</v>
+        <v>281607.9</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237982.8</v>
+        <v>237883.5</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203264.1</v>
+        <v>203179.2</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183323.3</v>
+        <v>183246.6</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129612.4</v>
+        <v>129558.3</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103545.6</v>
+        <v>103502.4</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84313.39999999999</v>
+        <v>84278.3</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53197.3</v>
+        <v>53175.2</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50321.1</v>
+        <v>50300.3</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42952.2</v>
+        <v>42934.4</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21390</v>
+        <v>21381</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18531.5</v>
+        <v>18523.8</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17224.3</v>
+        <v>17217.1</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15958.3</v>
+        <v>15951.7</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15958.3</v>
+        <v>15951.7</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15784.8</v>
+        <v>15778.3</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10823.4</v>
+        <v>10818.9</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9705.5</v>
+        <v>9701.4</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9705.5</v>
+        <v>9701.4</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9494.5</v>
+        <v>9490.5</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9600</v>
+        <v>9596</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8427.5</v>
+        <v>8424</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6031.4</v>
+        <v>6028.8</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5900.2</v>
+        <v>5897.8</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2537.7</v>
+        <v>2536.7</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>851.8</v>
+        <v>851.4</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>861.1</v>
+        <v>860.8</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>842.4</v>
+        <v>842.1</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>571</v>
+        <v>570.7</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -43543,76 +43543,76 @@
         <v>665352</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296370</v>
+        <v>1296318.7</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1329734.4</v>
+        <v>1329172</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1012659.1</v>
+        <v>1012235.9</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>500794.7</v>
+        <v>500585.6</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167860.6</v>
+        <v>167790.9</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67672.39999999999</v>
+        <v>67644.3</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>46019.2</v>
+        <v>46000</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33553.4</v>
+        <v>33539.3</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10160.1</v>
+        <v>10156.1</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3425.8</v>
+        <v>3424.4</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3425.8</v>
+        <v>3424.4</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3425.8</v>
+        <v>3424.4</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3416.4</v>
+        <v>3415.1</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3425.8</v>
+        <v>3424.4</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1413.4</v>
+        <v>1412.8</v>
       </c>
     </row>
     <row r="17">
@@ -43729,43 +43729,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>161040.9</v>
+        <v>161020.5</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157464.1</v>
+        <v>157398.5</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159213.7</v>
+        <v>159147.4</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160963.3</v>
+        <v>160896.3</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160963.3</v>
+        <v>160896.3</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159213.7</v>
+        <v>159147.4</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159213.7</v>
+        <v>159147.4</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124627.6</v>
+        <v>124575.6</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100247.1</v>
+        <v>100205</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82545.89999999999</v>
+        <v>82511.10000000001</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40695.4</v>
+        <v>40678.3</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19878.1</v>
+        <v>19869.8</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6698.1</v>
+        <v>6695.3</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44026,16 +44026,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401764.5</v>
+        <v>401744.1</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>638604.4</v>
+        <v>638338.5</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>543302.1</v>
+        <v>543075.4</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149817.5</v>
+        <v>149754.5</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44212,43 +44212,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96507.2</v>
+        <v>96495.10000000001</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94364.2</v>
+        <v>94325.39999999999</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95412.7</v>
+        <v>95373.39999999999</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96461.2</v>
+        <v>96421.5</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96461.2</v>
+        <v>96421.5</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95412.7</v>
+        <v>95373.39999999999</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95412.7</v>
+        <v>95373.39999999999</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60125.5</v>
+        <v>60100.8</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35745</v>
+        <v>35730.2</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19446</v>
+        <v>19437.9</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19662.1</v>
+        <v>19653.9</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19878.1</v>
+        <v>19869.8</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6698.1</v>
+        <v>6695.3</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44599,37 +44599,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64533.7</v>
+        <v>64525.4</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63099.9</v>
+        <v>63073.2</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63801</v>
+        <v>63774</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64502.1</v>
+        <v>64474.8</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64502.1</v>
+        <v>64474.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63801</v>
+        <v>63774</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63801</v>
+        <v>63774</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64502.1</v>
+        <v>64474.8</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64502.1</v>
+        <v>64474.8</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63099.9</v>
+        <v>63073.2</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21033.3</v>
+        <v>21024.4</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45117,367 +45117,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1345.74)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1345.14)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.02</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="32">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="33">
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14250</v>
+        <v>13550</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9166,7 +9166,7 @@
         <v>12910</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>13900</v>
+        <v>13400</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>14972</v>
+        <v>14735</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -12395,7 +12395,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>14250</v>
+        <v>13550</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -60779,7 +60779,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1474,49 +1474,49 @@
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1244억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2155,37 +2155,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4950억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2215,37 +2215,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4950억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3686,49 +3686,49 @@
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1244억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.23% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 3.24% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.6 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.7 백만원</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,558억 vs 2,563억 · 2028 2,565억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,553억 vs 2,563억 · 2028 2,560억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2365.7</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.73</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="32">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="33">
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2837</v>
+        <v>0.2836</v>
       </c>
     </row>
     <row r="34">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>13550</v>
+        <v>13390</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9166,7 +9166,7 @@
         <v>12910</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>13400</v>
+        <v>12630</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>14735</v>
+        <v>14540</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9914,39 +9914,39 @@
         <v>0.004526838</v>
       </c>
       <c r="AD24" s="31" t="n">
-        <v>0.004527602</v>
+        <v>0.004528014</v>
       </c>
       <c r="AE24" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF24" s="31" t="n">
-        <v>0.031454969</v>
+        <v>0.03145231</v>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>0.058388922</v>
+        <v>0.058399282</v>
       </c>
       <c r="AH24" s="31" t="n">
-        <v>0.085336388</v>
+        <v>0.085325441</v>
       </c>
       <c r="AI24" s="31" t="n">
-        <v>0.112254297</v>
+        <v>0.112259304</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK24" s="31" t="n">
-        <v>0.139201673</v>
+        <v>0.139204744</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>0.166129615</v>
+        <v>0.166129362</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.193073186</v>
+        <v>0.193064418</v>
       </c>
       <c r="AN24" s="31" t="n">
-        <v>0.219997204</v>
+        <v>0.22</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10476,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.002239709</v>
+        <v>-0.001644146</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>-0.007732042</v>
+        <v>-0.006825197</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.01938794</v>
+        <v>0.020232632</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.001789077</v>
+        <v>0.000977898</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.000648676</v>
+        <v>-0.00263598</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>0.001691458</v>
+        <v>-0.002199986</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.004143872</v>
+        <v>-0.000856358</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>-0.0009852870000000001</v>
+        <v>0.0007199869999999999</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.007191408</v>
+        <v>0.007502012</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.005574707</v>
+        <v>0.001659541</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10604,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.002239709</v>
+        <v>-0.001644146</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>-0.007732042</v>
+        <v>-0.006825197</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.01938794</v>
+        <v>0.020232632</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.001789077</v>
+        <v>0.000977898</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.000648676</v>
+        <v>-0.00263598</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.001691458</v>
+        <v>-0.002199986</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.004143872</v>
+        <v>-0.000856358</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>-0.0009852870000000001</v>
+        <v>0.0007199869999999999</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.007191408</v>
+        <v>0.007502012</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.005574707</v>
+        <v>0.001659541</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10863,33 +10863,33 @@
         <v>-0.231261925</v>
       </c>
       <c r="AD31" s="31" t="n">
-        <v>-0.356648231</v>
+        <v>-0.356615659</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="31" t="n">
-        <v>-0.556212598</v>
+        <v>-0.555921186</v>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>-1.317262937</v>
+        <v>-1.315716273</v>
       </c>
       <c r="AH31" s="31" t="n">
-        <v>3.158072636</v>
+        <v>3.169495198</v>
       </c>
       <c r="AI31" s="31" t="n">
-        <v>0.783475734</v>
+        <v>0.784151728</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="31" t="n">
-        <v>0.478912303</v>
+        <v>0.479166667</v>
       </c>
       <c r="AL31" s="31" t="n">
-        <v>0.347866571</v>
+        <v>0.348010711</v>
       </c>
       <c r="AM31" s="31" t="n">
-        <v>0.250497443</v>
+        <v>0.250604944</v>
       </c>
       <c r="AN31" s="31" t="n">
-        <v>0.195330706</v>
+        <v>0.195407669</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10991,33 +10991,33 @@
         <v>0.164057893</v>
       </c>
       <c r="AD32" s="31" t="n">
-        <v>0.167084775</v>
+        <v>0.167069516</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="31" t="n">
-        <v>0.143642754</v>
+        <v>0.143576642</v>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>0.132007911</v>
+        <v>0.131955529</v>
       </c>
       <c r="AH32" s="31" t="n">
-        <v>0.088699154</v>
+        <v>0.08865904400000001</v>
       </c>
       <c r="AI32" s="31" t="n">
-        <v>0.084044075</v>
+        <v>0.08400877299999999</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="31" t="n">
-        <v>0.084519673</v>
+        <v>0.084490937</v>
       </c>
       <c r="AL32" s="31" t="n">
-        <v>0.083718126</v>
+        <v>0.083696505</v>
       </c>
       <c r="AM32" s="31" t="n">
-        <v>0.07497917599999999</v>
+        <v>0.074970432</v>
       </c>
       <c r="AN32" s="31" t="n">
-        <v>0.068012798</v>
+        <v>0.06800887799999999</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11717,33 +11717,33 @@
         <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2798.235511</v>
+        <v>2798.030036</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2783.721783</v>
+        <v>2782.578985</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2790.740927</v>
+        <v>2789.596525</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>919.561614</v>
+        <v>918.395659</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>644.731614</v>
+        <v>643.565659</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>637.7409270000001</v>
+        <v>636.596525</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>637.750927</v>
+        <v>636.596525</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>644.743609</v>
+        <v>643.5770199999999</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>644.774393</v>
+        <v>643.604595</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12018,39 +12018,39 @@
         <v>0.09015805</v>
       </c>
       <c r="AD40" s="31" t="n">
-        <v>0.09507599899999999</v>
+        <v>0.095075598</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="31" t="n">
-        <v>0.096058342</v>
+        <v>0.09605807099999999</v>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>0.097964654</v>
+        <v>0.097963747</v>
       </c>
       <c r="AH40" s="31" t="n">
-        <v>0.09878661499999999</v>
+        <v>0.098787561</v>
       </c>
       <c r="AI40" s="31" t="n">
-        <v>0.099638501</v>
+        <v>0.099636761</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="31" t="n">
-        <v>0.100934995</v>
+        <v>0.100933424</v>
       </c>
       <c r="AL40" s="31" t="n">
-        <v>0.101626387</v>
+        <v>0.101625779</v>
       </c>
       <c r="AM40" s="31" t="n">
-        <v>0.09919552</v>
+        <v>0.099195573</v>
       </c>
       <c r="AN40" s="31" t="n">
-        <v>0.097282094</v>
+        <v>0.0972833</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>13550</v>
+        <v>13390</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,870원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,280원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0535974210343067</v>
+        <v>0.05359731723303156</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0323475708862465</v>
+        <v>0.03235025997536851</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870380316661114</v>
+        <v>0.07870489274478885</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42472,277 +42472,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="15">
@@ -42859,277 +42859,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1377.28</v>
+        <v>1376.82</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1385.35</v>
+        <v>1382.83</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1397.66</v>
+        <v>1395.14</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1401.38</v>
+        <v>1398.86</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1405.07</v>
+        <v>1402.55</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1410.22</v>
+        <v>1407.7</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1415.1</v>
+        <v>1412.58</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1415.98</v>
+        <v>1413.46</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1414.15</v>
+        <v>1411.63</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1411.71</v>
+        <v>1409.19</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1414.74</v>
+        <v>1412.22</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1417.48</v>
+        <v>1414.96</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1420.99</v>
+        <v>1418.47</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1425.44</v>
+        <v>1422.92</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1426.03</v>
+        <v>1423.51</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1425.53</v>
+        <v>1423.01</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1401.73</v>
+        <v>1399.21</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1425.19</v>
+        <v>1422.67</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1428.87</v>
+        <v>1426.35</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1426.65</v>
+        <v>1424.13</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1426.65</v>
+        <v>1424.13</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1426.65</v>
+        <v>1424.13</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1414.6</v>
+        <v>1412.08</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1409.77</v>
+        <v>1407.25</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1409.77</v>
+        <v>1407.25</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1409.77</v>
+        <v>1407.25</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1409.77</v>
+        <v>1407.25</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1411.95</v>
+        <v>1409.43</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1418.56</v>
+        <v>1416.04</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1418.56</v>
+        <v>1416.04</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1420.84</v>
+        <v>1418.32</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1428.73</v>
+        <v>1426.21</v>
       </c>
     </row>
     <row r="16">
@@ -43246,277 +43246,277 @@
         <v>338133.5</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392054</v>
+        <v>391925.1</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363240.6</v>
+        <v>362579.9</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332669.9</v>
+        <v>332070.1</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>322946.5</v>
+        <v>322365.8</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310315</v>
+        <v>309758.5</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289565.3</v>
+        <v>289047.9</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281607.9</v>
+        <v>281106.4</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237883.5</v>
+        <v>237460.1</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203179.2</v>
+        <v>202817.1</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183246.6</v>
+        <v>182919.5</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129558.3</v>
+        <v>129327.5</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103502.4</v>
+        <v>103318.4</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84278.3</v>
+        <v>84128.89999999999</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53175.2</v>
+        <v>53081.2</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50300.3</v>
+        <v>50211.4</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42934.4</v>
+        <v>42858.5</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21381</v>
+        <v>21342.6</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18523.8</v>
+        <v>18491.1</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17217.1</v>
+        <v>17186.8</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15951.7</v>
+        <v>15923.5</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15951.7</v>
+        <v>15923.5</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15778.3</v>
+        <v>15750.4</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10818.9</v>
+        <v>10799.6</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9701.4</v>
+        <v>9684.1</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9701.4</v>
+        <v>9684.1</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9490.5</v>
+        <v>9473.6</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9596</v>
+        <v>9578.799999999999</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8424</v>
+        <v>8409</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6028.8</v>
+        <v>6018.1</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5897.8</v>
+        <v>5887.3</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2536.7</v>
+        <v>2532.2</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.9</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.2</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>842.1</v>
+        <v>840.6</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>570.7</v>
+        <v>569.7</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -43543,76 +43543,76 @@
         <v>665352</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296318.7</v>
+        <v>1296189.8</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1329172</v>
+        <v>1326774.3</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1012235.9</v>
+        <v>1010431.5</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>500585.6</v>
+        <v>499694.3</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167790.9</v>
+        <v>167493.7</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67644.3</v>
+        <v>67524.89999999999</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>46000</v>
+        <v>45918.2</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33539.3</v>
+        <v>33479.5</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10156.1</v>
+        <v>10137.9</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3418.2</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3418.2</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3418.2</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3415.1</v>
+        <v>3408.9</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3418.2</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1412.8</v>
+        <v>1410.3</v>
       </c>
     </row>
     <row r="17">
@@ -43729,43 +43729,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>161020.5</v>
+        <v>160969.1</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157398.5</v>
+        <v>157118.9</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159147.4</v>
+        <v>158864.7</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160896.3</v>
+        <v>160610.4</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160896.3</v>
+        <v>160610.4</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159147.4</v>
+        <v>158864.7</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159147.4</v>
+        <v>158864.7</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124575.6</v>
+        <v>124353.8</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100205</v>
+        <v>100025.6</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82511.10000000001</v>
+        <v>82362.60000000001</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40678.3</v>
+        <v>40605.3</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19869.8</v>
+        <v>19834.5</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6695.3</v>
+        <v>6683.4</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44026,16 +44026,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401744.1</v>
+        <v>401692.7</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>638338.5</v>
+        <v>637204.4</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>543075.4</v>
+        <v>542108.8</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149754.5</v>
+        <v>149485.8</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44212,43 +44212,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96495.10000000001</v>
+        <v>96464.60000000001</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94325.39999999999</v>
+        <v>94159.60000000001</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95373.39999999999</v>
+        <v>95205.89999999999</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96421.5</v>
+        <v>96252.10000000001</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96421.5</v>
+        <v>96252.10000000001</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95373.39999999999</v>
+        <v>95205.89999999999</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95373.39999999999</v>
+        <v>95205.89999999999</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60100.8</v>
+        <v>59995.4</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35730.2</v>
+        <v>35667.2</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19437.9</v>
+        <v>19403.3</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19653.9</v>
+        <v>19618.9</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19869.8</v>
+        <v>19834.5</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6695.3</v>
+        <v>6683.4</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44599,37 +44599,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64525.4</v>
+        <v>64504.4</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63073.2</v>
+        <v>62959.3</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63774</v>
+        <v>63658.8</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64474.8</v>
+        <v>64358.4</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64474.8</v>
+        <v>64358.4</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63774</v>
+        <v>63658.8</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63774</v>
+        <v>63658.8</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64474.8</v>
+        <v>64358.4</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64474.8</v>
+        <v>64358.4</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63073.2</v>
+        <v>62959.3</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21024.4</v>
+        <v>20986.4</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45117,367 +45117,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1345.14)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.63)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
     </row>
@@ -60779,7 +60779,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1474,49 +1474,49 @@
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1244억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2155,37 +2155,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4950억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2215,37 +2215,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4950억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3686,49 +3686,49 @@
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 630억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1589억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 637억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1244억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.24% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 3.23% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.7 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.6 백만원</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,553억 vs 2,563억 · 2028 2,560억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,558억 vs 2,563억 · 2028 2,565억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2365</v>
+        <v>2365.6</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.66</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="32">
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2836</v>
+        <v>0.2837</v>
       </c>
     </row>
     <row r="34">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>13390</v>
+        <v>13410</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>14540</v>
+        <v>14411.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9921,32 +9921,32 @@
         <v/>
       </c>
       <c r="AF24" s="31" t="n">
-        <v>0.03145231</v>
+        <v>0.031454969</v>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>0.058399282</v>
+        <v>0.058388922</v>
       </c>
       <c r="AH24" s="31" t="n">
-        <v>0.085325441</v>
+        <v>0.085336388</v>
       </c>
       <c r="AI24" s="31" t="n">
-        <v>0.112259304</v>
+        <v>0.112254297</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK24" s="31" t="n">
-        <v>0.139204744</v>
+        <v>0.139201673</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>0.166129362</v>
+        <v>0.166132227</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.193064418</v>
+        <v>0.193073186</v>
       </c>
       <c r="AN24" s="31" t="n">
-        <v>0.22</v>
+        <v>0.219997204</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10476,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.001644146</v>
+        <v>-0.002075406</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>-0.006825197</v>
+        <v>-0.007476581</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.020232632</v>
+        <v>0.009488244</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.000977898</v>
+        <v>0.001637916</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>-0.00263598</v>
+        <v>0.0005523150000000001</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>-0.002199986</v>
+        <v>0.001637795</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.000856358</v>
+        <v>-0.004154874</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.0007199869999999999</v>
+        <v>0.007380463</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.007502012</v>
+        <v>-0.010869227</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>0.001659541</v>
+        <v>0.004536662</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10604,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.001644146</v>
+        <v>-0.002075406</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>-0.006825197</v>
+        <v>-0.007476581</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.020232632</v>
+        <v>0.009488244</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.000977898</v>
+        <v>0.001637916</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>-0.00263598</v>
+        <v>0.0005523150000000001</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>-0.002199986</v>
+        <v>0.001637795</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.000856358</v>
+        <v>-0.004154874</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.0007199869999999999</v>
+        <v>0.007380463</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.007502012</v>
+        <v>-0.010869227</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0.001659541</v>
+        <v>0.004536662</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10863,33 +10863,33 @@
         <v>-0.231261925</v>
       </c>
       <c r="AD31" s="31" t="n">
-        <v>-0.356615659</v>
+        <v>-0.356609145</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="31" t="n">
-        <v>-0.555921186</v>
+        <v>-0.556178808</v>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>-1.315716273</v>
+        <v>-1.31708263</v>
       </c>
       <c r="AH31" s="31" t="n">
-        <v>3.169495198</v>
+        <v>3.159435931</v>
       </c>
       <c r="AI31" s="31" t="n">
-        <v>0.784151728</v>
+        <v>0.783557047</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="31" t="n">
-        <v>0.479166667</v>
+        <v>0.478940171</v>
       </c>
       <c r="AL31" s="31" t="n">
-        <v>0.348010711</v>
+        <v>0.347873701</v>
       </c>
       <c r="AM31" s="31" t="n">
-        <v>0.250604944</v>
+        <v>0.25051084</v>
       </c>
       <c r="AN31" s="31" t="n">
-        <v>0.195407669</v>
+        <v>0.195331375</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10991,33 +10991,33 @@
         <v>0.164057893</v>
       </c>
       <c r="AD32" s="31" t="n">
-        <v>0.167069516</v>
+        <v>0.167066464</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="31" t="n">
-        <v>0.143576642</v>
+        <v>0.143645007</v>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>0.131955529</v>
+        <v>0.132009722</v>
       </c>
       <c r="AH32" s="31" t="n">
-        <v>0.08865904400000001</v>
+        <v>0.08870022900000001</v>
       </c>
       <c r="AI32" s="31" t="n">
-        <v>0.08400877299999999</v>
+        <v>0.084045011</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="31" t="n">
-        <v>0.084490937</v>
+        <v>0.084520541</v>
       </c>
       <c r="AL32" s="31" t="n">
-        <v>0.083696505</v>
+        <v>0.083717341</v>
       </c>
       <c r="AM32" s="31" t="n">
-        <v>0.074970432</v>
+        <v>0.07498139700000001</v>
       </c>
       <c r="AN32" s="31" t="n">
-        <v>0.06800887799999999</v>
+        <v>0.068011997</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11717,33 +11717,33 @@
         <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2798.030036</v>
+        <v>2797.998438</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2782.578985</v>
+        <v>2783.719674</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2789.596525</v>
+        <v>2790.738906</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>918.395659</v>
+        <v>919.559681</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>643.565659</v>
+        <v>644.719681</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>636.596525</v>
+        <v>637.738906</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>636.596525</v>
+        <v>637.738906</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>643.5770199999999</v>
+        <v>644.738625</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>643.604595</v>
+        <v>644.767394</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12018,39 +12018,39 @@
         <v>0.09015805</v>
       </c>
       <c r="AD40" s="31" t="n">
-        <v>0.095075598</v>
+        <v>0.095074961</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="31" t="n">
-        <v>0.09605807099999999</v>
+        <v>0.096055981</v>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>0.097963747</v>
+        <v>0.097964892</v>
       </c>
       <c r="AH40" s="31" t="n">
-        <v>0.098787561</v>
+        <v>0.09878698399999999</v>
       </c>
       <c r="AI40" s="31" t="n">
-        <v>0.099636761</v>
+        <v>0.099639189</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="31" t="n">
-        <v>0.100933424</v>
+        <v>0.100935291</v>
       </c>
       <c r="AL40" s="31" t="n">
-        <v>0.101625779</v>
+        <v>0.101626901</v>
       </c>
       <c r="AM40" s="31" t="n">
-        <v>0.099195573</v>
+        <v>0.099193318</v>
       </c>
       <c r="AN40" s="31" t="n">
-        <v>0.0972833</v>
+        <v>0.097282324</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>13390</v>
+        <v>13410</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,280원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,500원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359731723303156</v>
+        <v>0.05359723274754401</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03235025997536851</v>
+        <v>0.03234797457070401</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870489274478885</v>
+        <v>0.07870390338519757</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42472,277 +42472,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
     </row>
     <row r="15">
@@ -42859,277 +42859,277 @@
         <v>1395.96</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1376.82</v>
+        <v>1376.75</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1382.83</v>
+        <v>1385.34</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1395.14</v>
+        <v>1397.65</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1398.86</v>
+        <v>1401.37</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1402.55</v>
+        <v>1405.06</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1407.7</v>
+        <v>1410.2</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1412.58</v>
+        <v>1415.09</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1413.46</v>
+        <v>1415.97</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1411.63</v>
+        <v>1414.14</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1409.19</v>
+        <v>1411.7</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1412.22</v>
+        <v>1414.73</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1414.96</v>
+        <v>1417.47</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1418.47</v>
+        <v>1420.98</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1422.92</v>
+        <v>1425.43</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1423.51</v>
+        <v>1426.02</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1423.01</v>
+        <v>1425.52</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1399.21</v>
+        <v>1401.72</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1422.67</v>
+        <v>1425.18</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1426.35</v>
+        <v>1428.86</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1424.13</v>
+        <v>1426.64</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1424.13</v>
+        <v>1426.64</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1424.13</v>
+        <v>1426.64</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1412.08</v>
+        <v>1414.59</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1407.25</v>
+        <v>1409.76</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1407.25</v>
+        <v>1409.76</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1407.25</v>
+        <v>1409.76</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1407.25</v>
+        <v>1409.76</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1409.43</v>
+        <v>1411.94</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1416.04</v>
+        <v>1418.55</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1416.04</v>
+        <v>1418.55</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1418.32</v>
+        <v>1420.82</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1426.21</v>
+        <v>1428.72</v>
       </c>
     </row>
     <row r="16">
@@ -43246,277 +43246,277 @@
         <v>338133.5</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>391925.1</v>
+        <v>391904.6</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>362579.9</v>
+        <v>363237.5</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332070.1</v>
+        <v>332667.1</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>322365.8</v>
+        <v>322943.8</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>309758.5</v>
+        <v>310312.4</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289047.9</v>
+        <v>289562.9</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281106.4</v>
+        <v>281605.5</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237460.1</v>
+        <v>237881.5</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>202817.1</v>
+        <v>203177.4</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>182919.5</v>
+        <v>183245.1</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129327.5</v>
+        <v>129557.2</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103318.4</v>
+        <v>103501.5</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84128.89999999999</v>
+        <v>84277.60000000001</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53081.2</v>
+        <v>53174.8</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50211.4</v>
+        <v>50299.8</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42858.5</v>
+        <v>42934.1</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21342.6</v>
+        <v>21380.8</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18491.1</v>
+        <v>18523.7</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17186.8</v>
+        <v>17217</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15923.5</v>
+        <v>15951.5</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15923.5</v>
+        <v>15951.5</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15750.4</v>
+        <v>15778.1</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10799.6</v>
+        <v>10818.8</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9684.1</v>
+        <v>9701.4</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9684.1</v>
+        <v>9701.4</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9473.6</v>
+        <v>9490.5</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9578.799999999999</v>
+        <v>9595.9</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8409</v>
+        <v>8423.9</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6018.1</v>
+        <v>6028.8</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5887.3</v>
+        <v>5897.7</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2532.2</v>
+        <v>2536.6</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>849.9</v>
+        <v>851.4</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>859.2</v>
+        <v>860.8</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>840.6</v>
+        <v>842</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>569.7</v>
+        <v>570.7</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -43543,76 +43543,76 @@
         <v>665352</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296189.8</v>
+        <v>1296169.3</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1326774.3</v>
+        <v>1329160.8</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1010431.5</v>
+        <v>1012227.3</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>499694.3</v>
+        <v>500581.4</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167493.7</v>
+        <v>167789.5</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67524.89999999999</v>
+        <v>67643.7</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>45918.2</v>
+        <v>45999.7</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33479.5</v>
+        <v>33539.1</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10137.9</v>
+        <v>10155.9</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3418.2</v>
+        <v>3424.4</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3418.2</v>
+        <v>3424.4</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3418.2</v>
+        <v>3424.4</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3408.9</v>
+        <v>3415</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3418.2</v>
+        <v>3424.4</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1410.3</v>
+        <v>1412.7</v>
       </c>
     </row>
     <row r="17">
@@ -43729,43 +43729,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>160969.1</v>
+        <v>160960.9</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157118.9</v>
+        <v>157397.2</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>158864.7</v>
+        <v>159146</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160610.4</v>
+        <v>160894.9</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160610.4</v>
+        <v>160894.9</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>158864.7</v>
+        <v>159146</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>158864.7</v>
+        <v>159146</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124353.8</v>
+        <v>124574.5</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100025.6</v>
+        <v>100204.2</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82362.60000000001</v>
+        <v>82510.3</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40605.3</v>
+        <v>40677.9</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19834.5</v>
+        <v>19869.7</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6683.4</v>
+        <v>6695.2</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44026,16 +44026,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401692.7</v>
+        <v>401684.5</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>637204.4</v>
+        <v>638333</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>542108.8</v>
+        <v>543070.7</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149485.8</v>
+        <v>149753.1</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44212,43 +44212,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96464.60000000001</v>
+        <v>96459.8</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94159.60000000001</v>
+        <v>94324.60000000001</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95205.89999999999</v>
+        <v>95372.60000000001</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96252.10000000001</v>
+        <v>96420.7</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96252.10000000001</v>
+        <v>96420.7</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95205.89999999999</v>
+        <v>95372.60000000001</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95205.89999999999</v>
+        <v>95372.60000000001</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>59995.4</v>
+        <v>60100.3</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35667.2</v>
+        <v>35729.9</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19403.3</v>
+        <v>19437.7</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19618.9</v>
+        <v>19653.7</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19834.5</v>
+        <v>19869.7</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6683.4</v>
+        <v>6695.2</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44599,37 +44599,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64504.4</v>
+        <v>64501.1</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>62959.3</v>
+        <v>63072.6</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63658.8</v>
+        <v>63773.4</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64358.4</v>
+        <v>64474.2</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64358.4</v>
+        <v>64474.2</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63658.8</v>
+        <v>63773.4</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63658.8</v>
+        <v>63773.4</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64358.4</v>
+        <v>64474.2</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64358.4</v>
+        <v>64474.2</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>62959.3</v>
+        <v>63072.6</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>20986.4</v>
+        <v>21024.2</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45117,367 +45117,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.63)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.39)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
     </row>
@@ -60779,7 +60779,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1468,55 +1468,55 @@
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 629억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1243억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2011,121 +2011,121 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.6%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
 [divide]</t>
       </text>
     </comment>
@@ -2155,37 +2155,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 4950억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2215,37 +2215,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4951억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4950억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5390억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5843억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6337억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6867억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7382억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3680,55 +3680,55 @@
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1610억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1574억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 631억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 629억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1591억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 638억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1246억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1243억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1002억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.23% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 3.24% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.6 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 45건 중 포함 4건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.7 백만원</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,558억 vs 2,563억 · 2028 2,565억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,553억 vs 2,563억 · 2028 2,560억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2365.6</v>
+        <v>2364.9</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="32">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="33">
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2837</v>
+        <v>0.2836</v>
       </c>
     </row>
     <row r="34">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>13410</v>
+        <v>12780</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9166,7 +9166,7 @@
         <v>12910</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>12630</v>
+        <v>12160</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>14411.2</v>
+        <v>13940.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9914,39 +9914,39 @@
         <v>0.004526838</v>
       </c>
       <c r="AD24" s="31" t="n">
-        <v>0.004528014</v>
+        <v>0.00452859</v>
       </c>
       <c r="AE24" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF24" s="31" t="n">
-        <v>0.031454969</v>
+        <v>0.031455639</v>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>0.058388922</v>
+        <v>0.058396423</v>
       </c>
       <c r="AH24" s="31" t="n">
-        <v>0.085336388</v>
+        <v>0.085321885</v>
       </c>
       <c r="AI24" s="31" t="n">
-        <v>0.112254297</v>
+        <v>0.112254902</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK24" s="31" t="n">
-        <v>0.139201673</v>
+        <v>0.139199888</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>0.166132227</v>
+        <v>0.166139863</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.193073186</v>
+        <v>0.193071014</v>
       </c>
       <c r="AN24" s="31" t="n">
-        <v>0.219997204</v>
+        <v>0.220001865</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10476,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.002075406</v>
+        <v>-0.001183133</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>-0.007476581</v>
+        <v>0.00364289</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.009488244</v>
+        <v>0.010388751</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.001637916</v>
+        <v>0.000383786</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>0.0005523150000000001</v>
+        <v>-0.002127621</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>0.001637795</v>
+        <v>0.007546754</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.004154874</v>
+        <v>-0.002414994</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>0.007380463</v>
+        <v>-0.009227948999999999</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>-0.010869227</v>
+        <v>0.007691703</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>0.004536662</v>
+        <v>-0.008022186000000001</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10604,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.002075406</v>
+        <v>-0.001183133</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>-0.007476581</v>
+        <v>0.00364289</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.009488244</v>
+        <v>0.010388751</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.001637916</v>
+        <v>0.000383786</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.0005523150000000001</v>
+        <v>-0.002127621</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.001637795</v>
+        <v>0.007546754</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.004154874</v>
+        <v>-0.002414994</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>0.007380463</v>
+        <v>-0.009227948999999999</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>-0.010869227</v>
+        <v>0.007691703</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0.004536662</v>
+        <v>-0.008022186000000001</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10863,33 +10863,33 @@
         <v>-0.231261925</v>
       </c>
       <c r="AD31" s="31" t="n">
-        <v>-0.356609145</v>
+        <v>-0.356563544</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="31" t="n">
-        <v>-0.556178808</v>
+        <v>-0.555815413</v>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>-1.31708263</v>
+        <v>-1.315364803</v>
       </c>
       <c r="AH31" s="31" t="n">
-        <v>3.159435931</v>
+        <v>3.172087308</v>
       </c>
       <c r="AI31" s="31" t="n">
-        <v>0.783557047</v>
+        <v>0.784304894</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="31" t="n">
-        <v>0.478940171</v>
+        <v>0.479237663</v>
       </c>
       <c r="AL31" s="31" t="n">
-        <v>0.347873701</v>
+        <v>0.348037543</v>
       </c>
       <c r="AM31" s="31" t="n">
-        <v>0.25051084</v>
+        <v>0.250619562</v>
       </c>
       <c r="AN31" s="31" t="n">
-        <v>0.195331375</v>
+        <v>0.195424763</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10991,33 +10991,33 @@
         <v>0.164057893</v>
       </c>
       <c r="AD32" s="31" t="n">
-        <v>0.167066464</v>
+        <v>0.167045101</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="31" t="n">
-        <v>0.143645007</v>
+        <v>0.143563955</v>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>0.132009722</v>
+        <v>0.131966613</v>
       </c>
       <c r="AH32" s="31" t="n">
-        <v>0.08870022900000001</v>
+        <v>0.088663034</v>
       </c>
       <c r="AI32" s="31" t="n">
-        <v>0.084045011</v>
+        <v>0.084012188</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="31" t="n">
-        <v>0.084520541</v>
+        <v>0.084497374</v>
       </c>
       <c r="AL32" s="31" t="n">
-        <v>0.083717341</v>
+        <v>0.08370045399999999</v>
       </c>
       <c r="AM32" s="31" t="n">
-        <v>0.07498139700000001</v>
+        <v>0.074973782</v>
       </c>
       <c r="AN32" s="31" t="n">
-        <v>0.068011997</v>
+        <v>0.068014482</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11717,33 +11717,33 @@
         <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2797.998438</v>
+        <v>2797.816578</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2783.719674</v>
+        <v>2782.444298</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2790.738906</v>
+        <v>2789.454006</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>919.559681</v>
+        <v>918.255314</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>644.719681</v>
+        <v>643.425314</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>637.738906</v>
+        <v>636.454006</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>637.738906</v>
+        <v>636.464006</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>644.738625</v>
+        <v>643.4411710000001</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>644.767394</v>
+        <v>643.468869</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12018,39 +12018,39 @@
         <v>0.09015805</v>
       </c>
       <c r="AD40" s="31" t="n">
-        <v>0.095074961</v>
+        <v>0.09507279</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="31" t="n">
-        <v>0.096055981</v>
+        <v>0.096053288</v>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>0.097964892</v>
+        <v>0.097974251</v>
       </c>
       <c r="AH40" s="31" t="n">
-        <v>0.09878698399999999</v>
+        <v>0.098796389</v>
       </c>
       <c r="AI40" s="31" t="n">
-        <v>0.099639189</v>
+        <v>0.099645014</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="31" t="n">
-        <v>0.100935291</v>
+        <v>0.100943479</v>
       </c>
       <c r="AL40" s="31" t="n">
-        <v>0.101626901</v>
+        <v>0.101634277</v>
       </c>
       <c r="AM40" s="31" t="n">
-        <v>0.099193318</v>
+        <v>0.09920432999999999</v>
       </c>
       <c r="AN40" s="31" t="n">
-        <v>0.097282324</v>
+        <v>0.097290483</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12292,39 +12292,39 @@
         <v>0.090155665</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.09507544800000001</v>
+        <v>0.095071779</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE40,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.096058671</v>
+        <v>0.096051333</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.097966416</v>
+        <v>0.097973754</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.098788215</v>
+        <v>0.09879555199999999</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.099635694</v>
+        <v>0.0996467</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ40,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.100934429</v>
+        <v>0.100945435</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.101627821</v>
+        <v>0.101635158</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.09919544499999999</v>
+        <v>0.099202782</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.097280362</v>
+        <v>0.097291368</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO40,"")</f>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>13410</v>
+        <v>12780</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,530원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359723274754401</v>
+        <v>0.05359763662176677</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03234797457070401</v>
+        <v>0.03235035515380275</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870390338519757</v>
+        <v>0.07870455921391892</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39511,49 +39511,49 @@
         <v>81.759</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>100.274</v>
+        <v>100.301</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>115.314</v>
+        <v>115.507</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>115.48</v>
+        <v>115.672</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>122.384</v>
+        <v>122.576</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>123.839</v>
+        <v>124.033</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>124.336</v>
+        <v>124.53</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>125.212</v>
+        <v>125.402</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>124.929</v>
+        <v>125.12</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>125.517</v>
+        <v>125.711</v>
       </c>
       <c r="AI5" s="26" t="n">
-        <v>135.044</v>
+        <v>135.237</v>
       </c>
       <c r="AJ5" s="26" t="n">
-        <v>185.789</v>
+        <v>185.979</v>
       </c>
       <c r="AK5" s="26" t="n">
-        <v>220.765</v>
+        <v>220.957</v>
       </c>
       <c r="AL5" s="26" t="n">
-        <v>242.223</v>
+        <v>242.416</v>
       </c>
       <c r="AM5" s="26" t="n">
-        <v>284.659</v>
+        <v>284.853</v>
       </c>
       <c r="AN5" s="26" t="n">
-        <v>262.202</v>
+        <v>262.391</v>
       </c>
       <c r="AO5" s="26" t="n">
         <v>238.019</v>
@@ -39838,19 +39838,19 @@
         <v>245.213</v>
       </c>
       <c r="EE5" s="26" t="n">
-        <v>370.434</v>
+        <v>370.654</v>
       </c>
       <c r="EF5" s="26" t="n">
-        <v>486.039</v>
+        <v>486.811</v>
       </c>
       <c r="EG5" s="26" t="n">
-        <v>510.702</v>
+        <v>511.47</v>
       </c>
       <c r="EH5" s="26" t="n">
-        <v>933.436</v>
+        <v>934.205</v>
       </c>
       <c r="EI5" s="26" t="n">
-        <v>951.522</v>
+        <v>951.711</v>
       </c>
       <c r="EJ5" s="26" t="n">
         <v>716.011</v>
@@ -40477,49 +40477,49 @@
         <v>81.759</v>
       </c>
       <c r="Z7" s="26" t="n">
-        <v>100.274</v>
+        <v>100.301</v>
       </c>
       <c r="AA7" s="26" t="n">
-        <v>115.314</v>
+        <v>115.507</v>
       </c>
       <c r="AB7" s="26" t="n">
-        <v>115.48</v>
+        <v>115.672</v>
       </c>
       <c r="AC7" s="26" t="n">
-        <v>122.384</v>
+        <v>122.576</v>
       </c>
       <c r="AD7" s="26" t="n">
-        <v>123.839</v>
+        <v>124.033</v>
       </c>
       <c r="AE7" s="26" t="n">
-        <v>124.336</v>
+        <v>124.53</v>
       </c>
       <c r="AF7" s="26" t="n">
-        <v>125.212</v>
+        <v>125.402</v>
       </c>
       <c r="AG7" s="26" t="n">
-        <v>124.929</v>
+        <v>125.12</v>
       </c>
       <c r="AH7" s="26" t="n">
-        <v>125.517</v>
+        <v>125.711</v>
       </c>
       <c r="AI7" s="26" t="n">
-        <v>132.362</v>
+        <v>132.555</v>
       </c>
       <c r="AJ7" s="26" t="n">
-        <v>154.299</v>
+        <v>154.488</v>
       </c>
       <c r="AK7" s="26" t="n">
-        <v>160.206</v>
+        <v>160.398</v>
       </c>
       <c r="AL7" s="26" t="n">
-        <v>169.978</v>
+        <v>170.172</v>
       </c>
       <c r="AM7" s="26" t="n">
-        <v>171.236</v>
+        <v>171.43</v>
       </c>
       <c r="AN7" s="26" t="n">
-        <v>151.245</v>
+        <v>151.434</v>
       </c>
       <c r="AO7" s="26" t="n">
         <v>125.829</v>
@@ -40804,19 +40804,19 @@
         <v>245.213</v>
       </c>
       <c r="EE7" s="26" t="n">
-        <v>370.434</v>
+        <v>370.654</v>
       </c>
       <c r="EF7" s="26" t="n">
-        <v>486.039</v>
+        <v>486.811</v>
       </c>
       <c r="EG7" s="26" t="n">
-        <v>508.02</v>
+        <v>508.788</v>
       </c>
       <c r="EH7" s="26" t="n">
-        <v>655.7190000000001</v>
+        <v>656.4880000000001</v>
       </c>
       <c r="EI7" s="26" t="n">
-        <v>501.531</v>
+        <v>501.72</v>
       </c>
       <c r="EJ7" s="26" t="n">
         <v>332.42</v>
@@ -41104,49 +41104,49 @@
         <v>81.759</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>100.274</v>
+        <v>100.301</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>115.314</v>
+        <v>115.507</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>115.48</v>
+        <v>115.672</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>122.384</v>
+        <v>122.576</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>123.839</v>
+        <v>124.033</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>124.336</v>
+        <v>124.53</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>125.212</v>
+        <v>125.402</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>124.929</v>
+        <v>125.12</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>125.517</v>
+        <v>125.711</v>
       </c>
       <c r="AI10" s="26" t="n">
-        <v>134.648</v>
+        <v>134.842</v>
       </c>
       <c r="AJ10" s="26" t="n">
-        <v>168.017</v>
+        <v>168.207</v>
       </c>
       <c r="AK10" s="26" t="n">
-        <v>174.078</v>
+        <v>174.269</v>
       </c>
       <c r="AL10" s="26" t="n">
-        <v>184.002</v>
+        <v>184.195</v>
       </c>
       <c r="AM10" s="26" t="n">
-        <v>185.26</v>
+        <v>185.454</v>
       </c>
       <c r="AN10" s="26" t="n">
-        <v>164.964</v>
+        <v>165.153</v>
       </c>
       <c r="AO10" s="26" t="n">
         <v>139.7</v>
@@ -41431,19 +41431,19 @@
         <v>245.213</v>
       </c>
       <c r="EE10" s="26" t="n">
-        <v>370.434</v>
+        <v>370.654</v>
       </c>
       <c r="EF10" s="26" t="n">
-        <v>486.039</v>
+        <v>486.811</v>
       </c>
       <c r="EG10" s="26" t="n">
-        <v>510.306</v>
+        <v>511.075</v>
       </c>
       <c r="EH10" s="26" t="n">
-        <v>711.357</v>
+        <v>712.125</v>
       </c>
       <c r="EI10" s="26" t="n">
-        <v>557.167</v>
+        <v>557.356</v>
       </c>
       <c r="EJ10" s="26" t="n">
         <v>388.211</v>
@@ -42046,49 +42046,49 @@
         <v>1183.49</v>
       </c>
       <c r="Z13" s="13" t="n">
-        <v>1206.46</v>
+        <v>1206.49</v>
       </c>
       <c r="AA13" s="13" t="n">
-        <v>1220.45</v>
+        <v>1220.6</v>
       </c>
       <c r="AB13" s="13" t="n">
-        <v>1221.79</v>
+        <v>1221.95</v>
       </c>
       <c r="AC13" s="13" t="n">
-        <v>1227.91</v>
+        <v>1228.04</v>
       </c>
       <c r="AD13" s="13" t="n">
-        <v>1228</v>
+        <v>1228.13</v>
       </c>
       <c r="AE13" s="13" t="n">
-        <v>1228.67</v>
+        <v>1228.8</v>
       </c>
       <c r="AF13" s="13" t="n">
-        <v>1233.83</v>
+        <v>1233.95</v>
       </c>
       <c r="AG13" s="13" t="n">
-        <v>1249.21</v>
+        <v>1249.3</v>
       </c>
       <c r="AH13" s="13" t="n">
-        <v>1254.23</v>
+        <v>1254.32</v>
       </c>
       <c r="AI13" s="13" t="n">
-        <v>1267.98</v>
+        <v>1268.05</v>
       </c>
       <c r="AJ13" s="13" t="n">
-        <v>1322.94</v>
+        <v>1322.93</v>
       </c>
       <c r="AK13" s="13" t="n">
-        <v>1377.69</v>
+        <v>1377.64</v>
       </c>
       <c r="AL13" s="13" t="n">
-        <v>1386.2</v>
+        <v>1386.14</v>
       </c>
       <c r="AM13" s="13" t="n">
-        <v>1391.05</v>
+        <v>1391</v>
       </c>
       <c r="AN13" s="13" t="n">
-        <v>1404.14</v>
+        <v>1404.08</v>
       </c>
       <c r="AO13" s="13" t="n">
         <v>1421.74</v>
@@ -42472,277 +42472,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
     </row>
     <row r="15">
@@ -42820,316 +42820,316 @@
         <v>1223.15</v>
       </c>
       <c r="Z15" s="13" t="n">
-        <v>1238.61</v>
+        <v>1238.63</v>
       </c>
       <c r="AA15" s="13" t="n">
-        <v>1250.91</v>
+        <v>1251.02</v>
       </c>
       <c r="AB15" s="13" t="n">
-        <v>1254.3</v>
+        <v>1254.4</v>
       </c>
       <c r="AC15" s="13" t="n">
-        <v>1270.92</v>
+        <v>1271.01</v>
       </c>
       <c r="AD15" s="13" t="n">
-        <v>1266.46</v>
+        <v>1266.56</v>
       </c>
       <c r="AE15" s="13" t="n">
-        <v>1278.96</v>
+        <v>1279.05</v>
       </c>
       <c r="AF15" s="13" t="n">
-        <v>1299.36</v>
+        <v>1299.45</v>
       </c>
       <c r="AG15" s="13" t="n">
-        <v>1294</v>
+        <v>1294.07</v>
       </c>
       <c r="AH15" s="13" t="n">
-        <v>1294.04</v>
+        <v>1294.11</v>
       </c>
       <c r="AI15" s="13" t="n">
-        <v>1322.34</v>
+        <v>1322.39</v>
       </c>
       <c r="AJ15" s="13" t="n">
-        <v>1365.89</v>
+        <v>1365.88</v>
       </c>
       <c r="AK15" s="13" t="n">
-        <v>1414.91</v>
+        <v>1414.87</v>
       </c>
       <c r="AL15" s="13" t="n">
-        <v>1395.96</v>
+        <v>1395.92</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1376.75</v>
+        <v>1376.33</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1385.34</v>
+        <v>1382.49</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1397.65</v>
+        <v>1394.85</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1401.37</v>
+        <v>1398.57</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1405.06</v>
+        <v>1402.26</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1410.2</v>
+        <v>1407.4</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1415.09</v>
+        <v>1412.28</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1415.97</v>
+        <v>1413.17</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1414.14</v>
+        <v>1411.33</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1411.7</v>
+        <v>1408.89</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1414.73</v>
+        <v>1411.92</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1417.47</v>
+        <v>1414.67</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1420.98</v>
+        <v>1418.17</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1425.43</v>
+        <v>1422.62</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1426.02</v>
+        <v>1423.21</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1425.52</v>
+        <v>1422.72</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1401.72</v>
+        <v>1398.92</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1425.18</v>
+        <v>1422.38</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1428.86</v>
+        <v>1426.05</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1426.64</v>
+        <v>1423.83</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1426.64</v>
+        <v>1423.83</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1426.64</v>
+        <v>1423.83</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1414.59</v>
+        <v>1411.78</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1409.76</v>
+        <v>1406.95</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1409.76</v>
+        <v>1406.95</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1409.76</v>
+        <v>1406.95</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1409.76</v>
+        <v>1406.95</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1411.94</v>
+        <v>1409.13</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1418.55</v>
+        <v>1415.74</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1418.55</v>
+        <v>1415.74</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1420.82</v>
+        <v>1418.02</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1428.72</v>
+        <v>1425.91</v>
       </c>
     </row>
     <row r="16">
@@ -43207,316 +43207,316 @@
         <v>100004.1</v>
       </c>
       <c r="Z16" s="18" t="n">
-        <v>124200.3</v>
+        <v>124236.3</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>144247.5</v>
+        <v>144502.5</v>
       </c>
       <c r="AB16" s="18" t="n">
-        <v>144846.3</v>
+        <v>145099</v>
       </c>
       <c r="AC16" s="18" t="n">
-        <v>155540</v>
+        <v>155795.1</v>
       </c>
       <c r="AD16" s="18" t="n">
-        <v>156837.5</v>
+        <v>157094.5</v>
       </c>
       <c r="AE16" s="18" t="n">
-        <v>159020.9</v>
+        <v>159280.3</v>
       </c>
       <c r="AF16" s="18" t="n">
-        <v>162696</v>
+        <v>162952.9</v>
       </c>
       <c r="AG16" s="18" t="n">
-        <v>161657.6</v>
+        <v>161914.2</v>
       </c>
       <c r="AH16" s="18" t="n">
-        <v>162424.3</v>
+        <v>162683.1</v>
       </c>
       <c r="AI16" s="18" t="n">
-        <v>178574.1</v>
+        <v>178836.5</v>
       </c>
       <c r="AJ16" s="18" t="n">
-        <v>253768</v>
+        <v>254025.7</v>
       </c>
       <c r="AK16" s="18" t="n">
-        <v>312363.2</v>
+        <v>312625.8</v>
       </c>
       <c r="AL16" s="18" t="n">
-        <v>338133.5</v>
+        <v>338394.1</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>391904.6</v>
+        <v>392051.5</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>363237.5</v>
+        <v>362752</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>332667.1</v>
+        <v>331999.4</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>322943.8</v>
+        <v>322297.4</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>310312.4</v>
+        <v>309692.9</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>289562.9</v>
+        <v>288986.9</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281605.5</v>
+        <v>281047.3</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237881.5</v>
+        <v>237410.3</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>203177.4</v>
+        <v>202774.4</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>183245.1</v>
+        <v>182881</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129557.2</v>
+        <v>129300.3</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103501.5</v>
+        <v>103296.7</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84277.60000000001</v>
+        <v>84111.3</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53174.8</v>
+        <v>53070.1</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50299.8</v>
+        <v>50200.9</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42934.1</v>
+        <v>42849.6</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21380.8</v>
+        <v>21338.1</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18523.7</v>
+        <v>18487.2</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17217</v>
+        <v>17183.2</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15951.5</v>
+        <v>15920.2</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15951.5</v>
+        <v>15920.2</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15778.1</v>
+        <v>15747.1</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10818.8</v>
+        <v>10797.3</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9701.4</v>
+        <v>9682.1</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9701.4</v>
+        <v>9682.1</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9490.5</v>
+        <v>9471.6</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9595.9</v>
+        <v>9576.799999999999</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8423.9</v>
+        <v>8407.200000000001</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6028.8</v>
+        <v>6016.9</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5897.7</v>
+        <v>5886.1</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2536.6</v>
+        <v>2531.6</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>851.4</v>
+        <v>849.7</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>860.8</v>
+        <v>859.1</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>842</v>
+        <v>840.4</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>570.7</v>
+        <v>569.6</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -43534,85 +43534,85 @@
         <v>289816.6</v>
       </c>
       <c r="EE16" s="18" t="n">
-        <v>456350.6</v>
+        <v>456641.6</v>
       </c>
       <c r="EF16" s="18" t="n">
-        <v>616244.7</v>
+        <v>617268.9</v>
       </c>
       <c r="EG16" s="18" t="n">
-        <v>665352</v>
+        <v>666386.7</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1296169.3</v>
+        <v>1297097.1</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1329160.8</v>
+        <v>1326741.7</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1012227.3</v>
+        <v>1010218.9</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>500581.4</v>
+        <v>499589.3</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167789.5</v>
+        <v>167458.7</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67643.7</v>
+        <v>67510.8</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>45999.7</v>
+        <v>45908.6</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33539.1</v>
+        <v>33472.5</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10155.9</v>
+        <v>10135.9</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3417.6</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3417.6</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3417.6</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3415</v>
+        <v>3408.3</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3424.4</v>
+        <v>3417.6</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1412.7</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="17">
@@ -43729,43 +43729,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>160960.9</v>
+        <v>160917.4</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157397.2</v>
+        <v>157086</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>159146</v>
+        <v>158831.4</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160894.9</v>
+        <v>160576.7</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160894.9</v>
+        <v>160576.7</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>159146</v>
+        <v>158831.4</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>159146</v>
+        <v>158831.4</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124574.5</v>
+        <v>124327.7</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100204.2</v>
+        <v>100004.4</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82510.3</v>
+        <v>82345.10000000001</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40677.9</v>
+        <v>40596.7</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19869.7</v>
+        <v>19830.3</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6695.2</v>
+        <v>6682</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44026,16 +44026,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401684.5</v>
+        <v>401641</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>638333</v>
+        <v>637070.8</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>543070.7</v>
+        <v>541994.9</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149753.1</v>
+        <v>149454.1</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44212,43 +44212,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96459.8</v>
+        <v>96434</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94324.60000000001</v>
+        <v>94140.10000000001</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95372.60000000001</v>
+        <v>95186.10000000001</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96420.7</v>
+        <v>96232.10000000001</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96420.7</v>
+        <v>96232.10000000001</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95372.60000000001</v>
+        <v>95186.10000000001</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95372.60000000001</v>
+        <v>95186.10000000001</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>60100.3</v>
+        <v>59983</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35729.9</v>
+        <v>35659.8</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19437.7</v>
+        <v>19399.2</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19653.7</v>
+        <v>19614.8</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19869.7</v>
+        <v>19830.3</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6695.2</v>
+        <v>6682</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44599,37 +44599,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64501.1</v>
+        <v>64483.4</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>63072.6</v>
+        <v>62945.8</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63773.4</v>
+        <v>63645.2</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64474.2</v>
+        <v>64344.6</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64474.2</v>
+        <v>64344.6</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63773.4</v>
+        <v>63645.2</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63773.4</v>
+        <v>63645.2</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64474.2</v>
+        <v>64344.6</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64474.2</v>
+        <v>64344.6</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>63072.6</v>
+        <v>62945.8</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>21024.2</v>
+        <v>20981.9</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45117,367 +45117,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.39)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1342.11)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
     </row>
@@ -50765,7 +50765,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20261007800209</t>
+          <t>20261014800411</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -50779,49 +50779,49 @@
         </is>
       </c>
       <c r="Z73" s="26" t="n">
-        <v>2</v>
+        <v>2.028</v>
       </c>
       <c r="AA73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AB73" s="26" t="n">
-        <v>14.003</v>
+        <v>14.194</v>
       </c>
       <c r="AC73" s="26" t="n">
-        <v>14.003</v>
+        <v>14.194</v>
       </c>
       <c r="AD73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AE73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AF73" s="26" t="n">
-        <v>13.849</v>
+        <v>14.038</v>
       </c>
       <c r="AG73" s="26" t="n">
-        <v>14.003</v>
+        <v>14.194</v>
       </c>
       <c r="AH73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AI73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AJ73" s="26" t="n">
-        <v>13.849</v>
+        <v>14.038</v>
       </c>
       <c r="AK73" s="26" t="n">
-        <v>14.003</v>
+        <v>14.194</v>
       </c>
       <c r="AL73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AM73" s="26" t="n">
-        <v>14.157</v>
+        <v>14.35</v>
       </c>
       <c r="AN73" s="26" t="n">
-        <v>13.845</v>
+        <v>14.043</v>
       </c>
       <c r="FG73" s="35" t="n">
         <v>0</v>
@@ -50841,7 +50841,7 @@
         <v>1</v>
       </c>
       <c r="FM73" s="26" t="n">
-        <v>198.654</v>
+        <v>201.373</v>
       </c>
       <c r="FN73" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20261007800209</t>
+          <t>20261014800411</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -59007,7 +59007,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>20261007800209</t>
+          <t>20261014800411</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -59016,10 +59016,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>260955.951</v>
+        <v>264527.897</v>
       </c>
       <c r="E170" t="n">
-        <v>198.654</v>
+        <v>201.373</v>
       </c>
       <c r="F170" t="n">
         <v>1313.62</v>
@@ -59092,7 +59092,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32297억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
+          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32305억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
         </is>
       </c>
     </row>
@@ -60779,7 +60779,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/097230_model.xlsx
+++ b/argus/kship/models/097230_model.xlsx
@@ -1468,55 +1468,55 @@
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 629억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1568억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 628억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1586억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 635억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1603억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1603억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1586억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 635억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1586억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 635억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1243억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1241억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 2153.0; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 998억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
@@ -2011,121 +2011,121 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 7.4%(코호트 모드 reference_anchor; 등급 비중 24% × 코호트 10.8% + 등급없음 76% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 7.9%(코호트 모드 reference_anchor; 등급 비중 35% × 코호트 10.8% + 등급없음 65% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.0%(코호트 모드 reference_anchor; 등급 비중 37% × 코호트 10.8% + 등급없음 63% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 41% × 코호트 10.8% + 등급없음 59% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.2%(코호트 모드 reference_anchor; 등급 비중 43% × 코호트 10.8% + 등급없음 57% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 45% × 코호트 10.8% + 등급없음 55% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.4%(코호트 모드 reference_anchor; 등급 비중 48% × 코호트 10.8% + 등급없음 52% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.5%(코호트 모드 reference_anchor; 등급 비중 49% × 코호트 10.8% + 등급없음 51% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.3%(코호트 모드 reference_anchor; 등급 비중 44% × 코호트 10.8% + 등급없음 56% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%)
+        <t>추정: SLS 코호트 타겟 8.1%(코호트 모드 reference_anchor; 등급 비중 40% × 코호트 10.8% + 등급없음 60% × 최근 4분기 실측 OPM 중위 6.3%) + 회사 캘리브레이션 +1.7%p(최근 3분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%)
 [divide]</t>
       </text>
     </comment>
@@ -2161,31 +2161,31 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5388억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 5841억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6334억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6864억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7379억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2221,31 +2221,31 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5389억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5388억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 5842억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 5841억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6335억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6334억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6866억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 6864억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7380억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 7379억 × 3.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 4751억 × 7.87%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3680,55 +3680,55 @@
     </comment>
     <comment ref="AD36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1609억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 645억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1608억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 4581억) + 신규수주 매출 0억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 644억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1571억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 629억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1568억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 2428억) + 신규수주 매출 103억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 628억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1586억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 2153억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 275억) + 신규수주 매출 382억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 635억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1603억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 275억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 791억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1606억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1603억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1287억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1586억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 1825억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 635억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1588억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 636억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1586억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2358억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 635억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1243억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1241억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 2844억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN36" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 643억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 998억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 원장 수준 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 2153억/분기, 잔여 0억) + 신규수주 매출 3236억(폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate: 패널 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% → 원장 체결 분기(체결 &gt; 0 인 3분기) min/median/max(3,533/3,572/3,814억, 창 3분기 2025Q4~2026Q2)를 보수/base/낙관 신규수주로(패널 자체 N 하한), 인식은 패널 역산 커널(covered_scope_new_revenue) · 저신뢰; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억)) · origin 이후 공시 수주 SLS 642억 유지(원장 수준 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4806,7 +4806,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.24% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 3.23% / 부채 7.87% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0323, 0.0787] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.37%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 716억 vs 0억 · 2027 2,553억 vs 2,563억 · 2028 2,560억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 조선 부문 매출 음수 분기 1개 제외(부문표 누계 정정 차분 — sls.reconcile.reported_segment_rev_m; yards 레인 확인): 2022Q4 -8411억 / 2023Q2 조선 부문 매출(6762억) &gt; 연결 매출(5014억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 6.3% 채움에서만, 추정 구간 타겟 7.36%→8.08%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + ledger_signing_rate(공시 계약 원장 체결 속도 × forecast_panel 역산 커널 covered_scope_new_revenue) 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,826억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백 사슬 new_order_revenue → covered_scope_new_revenue → ledger_signing_rate(저신뢰): 패널 covered_scope 신규수주(분기 110억)가 공시 체결 속도(분기 평균 3,640억)의 3% &lt; 50% · 원장 창 3분기(2025Q4~2026Q2) → 원장 체결 분기 min/median/max 3,533/3,572/3,814억을 보수/base/낙관 분기 신규수주로, 인식 패널 역산 커널(covered_scope_new_revenue); 선형 대안(T=12분기, 원장 계약 일정 길이 중위) base FY 매출 2026 0억 · 2027 2,977억 · 2028 7,739억(공시 상계 후 — 행과 같은 축; 상계 전 2026 298억 · 2027 4,167억 · 2028 8,930억) / 신규수주 ledger_signing_rate(저신뢰): 원장은 공시 대상 대형 계약만 잡는 하한 · 표본 3분기(2025Q4 3,814억 · 2026Q1 3,533억 · 2026Q2 3,572억; 수준 통계는 체결 &gt; 0 인 3분기) — 보수~낙관 폭이 좁아 불확실성을 과소표시할 수 있음(저신뢰) / origin 이후 공시 수주 1건 6,790억은 SLS 일정으로 전부 유지, 원장 수준 신규수주에서 체결 분기별 상계(2026Q3 원장 수준 3,572억(패널 110억) − 공시 6,790억 = 0억) — 매출조선신규(원장 수준) −3,490억(2026 103억 · 2027 1,722억 · 2028 1,666억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 7건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 6,790억 vs 원장 수준 base 신규수주 3,572억(190%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 매출조선신규(원장 수준)(상계 후): 2026 715억 vs 0억 · 2027 2,549억 vs 2,563억 · 2028 2,556억 vs 10,263억 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 0.5% → 0.5% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -34/-23/+17/-50(중위 -28억) → 추정 2026Q3 -71억(차 -42억, -149%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2364.9</v>
+        <v>2364.2</v>
       </c>
     </row>
     <row r="30">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.4</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="32">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="33">
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2836</v>
+        <v>0.2835</v>
       </c>
     </row>
     <row r="34">
@@ -8016,35 +8016,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8135,35 +8135,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8254,35 +8254,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8373,35 +8373,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8492,35 +8492,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8611,35 +8611,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8730,35 +8730,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8849,35 +8849,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8984,7 +8984,7 @@
         <v>14710</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>12780</v>
+        <v>12090</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9166,7 +9166,7 @@
         <v>12910</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>12160</v>
+        <v>11970</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9257,7 +9257,7 @@
         <v>16326.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>13940.9</v>
+        <v>13466.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9911,42 +9911,42 @@
         <v/>
       </c>
       <c r="AC24" s="31" t="n">
-        <v>0.004526838</v>
+        <v>0.00452713</v>
       </c>
       <c r="AD24" s="31" t="n">
-        <v>0.00452859</v>
+        <v>0.004529826</v>
       </c>
       <c r="AE24" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF24" s="31" t="n">
-        <v>0.031455639</v>
+        <v>0.031466187</v>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>0.058396423</v>
+        <v>0.058399164</v>
       </c>
       <c r="AH24" s="31" t="n">
-        <v>0.085321885</v>
+        <v>0.085338393</v>
       </c>
       <c r="AI24" s="31" t="n">
-        <v>0.112254902</v>
+        <v>0.112264114</v>
       </c>
       <c r="AJ24" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK24" s="31" t="n">
-        <v>0.139199888</v>
+        <v>0.139198549</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>0.166139863</v>
+        <v>0.166131823</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.193071014</v>
+        <v>0.193066357</v>
       </c>
       <c r="AN24" s="31" t="n">
-        <v>0.220001865</v>
+        <v>0.220008393</v>
       </c>
       <c r="AO24" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10476,36 +10476,36 @@
         <v/>
       </c>
       <c r="AC28" s="29" t="n">
-        <v>-0.001183133</v>
+        <v>-0.001440529</v>
       </c>
       <c r="AD28" s="29" t="n">
-        <v>0.00364289</v>
+        <v>0.00305535</v>
       </c>
       <c r="AE28" s="30" t="n"/>
       <c r="AF28" s="29" t="n">
-        <v>0.010388751</v>
+        <v>-0.001777774</v>
       </c>
       <c r="AG28" s="29" t="n">
-        <v>0.000383786</v>
+        <v>-0.002813253</v>
       </c>
       <c r="AH28" s="29" t="n">
-        <v>-0.002127621</v>
+        <v>-0.007598974</v>
       </c>
       <c r="AI28" s="29" t="n">
-        <v>0.007546754</v>
+        <v>0.000501937</v>
       </c>
       <c r="AJ28" s="30" t="n"/>
       <c r="AK28" s="29" t="n">
-        <v>-0.002414994</v>
+        <v>0.000441228</v>
       </c>
       <c r="AL28" s="29" t="n">
-        <v>-0.009227948999999999</v>
+        <v>-0.00083146</v>
       </c>
       <c r="AM28" s="29" t="n">
-        <v>0.007691703</v>
+        <v>0.008486377999999999</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>-0.008022186000000001</v>
+        <v>-0.009958331000000001</v>
       </c>
       <c r="AO28" s="30" t="n"/>
     </row>
@@ -10604,36 +10604,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.001183133</v>
+        <v>-0.001440529</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.00364289</v>
+        <v>0.00305535</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.010388751</v>
+        <v>-0.001777774</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>0.000383786</v>
+        <v>-0.002813253</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>-0.002127621</v>
+        <v>-0.007598974</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.007546754</v>
+        <v>0.000501937</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.002414994</v>
+        <v>0.000441228</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>-0.009227948999999999</v>
+        <v>-0.00083146</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.007691703</v>
+        <v>0.008486377999999999</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.008022186000000001</v>
+        <v>-0.009958331000000001</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -10860,36 +10860,36 @@
         <v/>
       </c>
       <c r="AC31" s="31" t="n">
-        <v>-0.231261925</v>
+        <v>-0.231246901</v>
       </c>
       <c r="AD31" s="31" t="n">
-        <v>-0.356563544</v>
+        <v>-0.356458863</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="31" t="n">
-        <v>-0.555815413</v>
+        <v>-0.555542059</v>
       </c>
       <c r="AG31" s="31" t="n">
-        <v>-1.315364803</v>
+        <v>-1.313883575</v>
       </c>
       <c r="AH31" s="31" t="n">
-        <v>3.172087308</v>
+        <v>3.183137426</v>
       </c>
       <c r="AI31" s="31" t="n">
-        <v>0.784304894</v>
+        <v>0.784968431</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="31" t="n">
-        <v>0.479237663</v>
+        <v>0.479481474</v>
       </c>
       <c r="AL31" s="31" t="n">
-        <v>0.348037543</v>
+        <v>0.348179627</v>
       </c>
       <c r="AM31" s="31" t="n">
-        <v>0.250619562</v>
+        <v>0.250717386</v>
       </c>
       <c r="AN31" s="31" t="n">
-        <v>0.195424763</v>
+        <v>0.195496278</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -10988,36 +10988,36 @@
         <v/>
       </c>
       <c r="AC32" s="31" t="n">
-        <v>0.164057893</v>
+        <v>0.164047235</v>
       </c>
       <c r="AD32" s="31" t="n">
-        <v>0.167045101</v>
+        <v>0.167000851</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="31" t="n">
-        <v>0.143563955</v>
+        <v>0.143526255</v>
       </c>
       <c r="AG32" s="31" t="n">
-        <v>0.131966613</v>
+        <v>0.131933724</v>
       </c>
       <c r="AH32" s="31" t="n">
-        <v>0.088663034</v>
+        <v>0.08863432</v>
       </c>
       <c r="AI32" s="31" t="n">
-        <v>0.084012188</v>
+        <v>0.083988308</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="31" t="n">
-        <v>0.084497374</v>
+        <v>0.084478154</v>
       </c>
       <c r="AL32" s="31" t="n">
-        <v>0.08370045399999999</v>
+        <v>0.083688284</v>
       </c>
       <c r="AM32" s="31" t="n">
-        <v>0.074973782</v>
+        <v>0.074970281</v>
       </c>
       <c r="AN32" s="31" t="n">
-        <v>0.068014482</v>
+        <v>0.068015189</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -11717,33 +11717,33 @@
         <v>2224.230436</v>
       </c>
       <c r="AD38" s="29" t="n">
-        <v>2797.816578</v>
+        <v>2797.178302</v>
       </c>
       <c r="AE38" s="30" t="n"/>
       <c r="AF38" s="29" t="n">
-        <v>2782.444298</v>
+        <v>2781.413536</v>
       </c>
       <c r="AG38" s="29" t="n">
-        <v>2789.454006</v>
+        <v>2788.409998</v>
       </c>
       <c r="AH38" s="29" t="n">
-        <v>918.255314</v>
+        <v>917.1981050000001</v>
       </c>
       <c r="AI38" s="29" t="n">
-        <v>643.425314</v>
+        <v>642.368105</v>
       </c>
       <c r="AJ38" s="30" t="n"/>
       <c r="AK38" s="29" t="n">
-        <v>636.454006</v>
+        <v>635.409998</v>
       </c>
       <c r="AL38" s="29" t="n">
-        <v>636.464006</v>
+        <v>635.409998</v>
       </c>
       <c r="AM38" s="29" t="n">
-        <v>643.4411710000001</v>
+        <v>642.380527</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>643.468869</v>
+        <v>642.4128020000001</v>
       </c>
       <c r="AO38" s="30" t="n"/>
     </row>
@@ -12015,42 +12015,42 @@
         <v/>
       </c>
       <c r="AC40" s="31" t="n">
-        <v>0.09015805</v>
+        <v>0.090151808</v>
       </c>
       <c r="AD40" s="31" t="n">
-        <v>0.09507279</v>
+        <v>0.095072595</v>
       </c>
       <c r="AE40" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF40" s="31" t="n">
-        <v>0.096053288</v>
+        <v>0.096062173</v>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>0.097974251</v>
+        <v>0.097981968</v>
       </c>
       <c r="AH40" s="31" t="n">
-        <v>0.098796389</v>
+        <v>0.098806455</v>
       </c>
       <c r="AI40" s="31" t="n">
-        <v>0.099645014</v>
+        <v>0.099655073</v>
       </c>
       <c r="AJ40" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK40" s="31" t="n">
-        <v>0.100943479</v>
+        <v>0.100952107</v>
       </c>
       <c r="AL40" s="31" t="n">
-        <v>0.101634277</v>
+        <v>0.10164498</v>
       </c>
       <c r="AM40" s="31" t="n">
-        <v>0.09920432999999999</v>
+        <v>0.09921177</v>
       </c>
       <c r="AN40" s="31" t="n">
-        <v>0.097290483</v>
+        <v>0.097299595</v>
       </c>
       <c r="AO40" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO36,"")</f>
@@ -12289,7 +12289,7 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.090155665</v>
+        <v>0.090151996</v>
       </c>
       <c r="AD42" s="31" t="n">
         <v>0.095071779</v>
@@ -12299,32 +12299,32 @@
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.096051333</v>
+        <v>0.096062339</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.097973754</v>
+        <v>0.09798109100000001</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.09879555199999999</v>
+        <v>0.098806558</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.0996467</v>
+        <v>0.099654038</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ40,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.100945435</v>
+        <v>0.100952772</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.101635158</v>
+        <v>0.101646165</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099202782</v>
+        <v>0.099213789</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.097291368</v>
+        <v>0.097298705</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO40,"")</f>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>12780</v>
+        <v>12090</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,530원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,990원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05359763662176677</v>
+        <v>0.05359732973125074</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03235035515380275</v>
+        <v>0.03234956527776486</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07870455921391892</v>
+        <v>0.07870430894249546</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39511,46 +39511,46 @@
         <v>81.759</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>100.301</v>
+        <v>100.437</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>115.507</v>
+        <v>115.739</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>115.672</v>
+        <v>115.901</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>122.576</v>
+        <v>122.805</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>124.033</v>
+        <v>124.264</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>124.53</v>
+        <v>124.762</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>125.402</v>
+        <v>125.628</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>125.12</v>
+        <v>125.35</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>125.711</v>
+        <v>125.942</v>
       </c>
       <c r="AI5" s="26" t="n">
-        <v>135.237</v>
+        <v>135.469</v>
       </c>
       <c r="AJ5" s="26" t="n">
-        <v>185.979</v>
+        <v>186.206</v>
       </c>
       <c r="AK5" s="26" t="n">
-        <v>220.957</v>
+        <v>221.186</v>
       </c>
       <c r="AL5" s="26" t="n">
-        <v>242.416</v>
+        <v>242.648</v>
       </c>
       <c r="AM5" s="26" t="n">
-        <v>284.853</v>
+        <v>285.085</v>
       </c>
       <c r="AN5" s="26" t="n">
         <v>262.391</v>
@@ -39838,16 +39838,16 @@
         <v>245.213</v>
       </c>
       <c r="EE5" s="26" t="n">
-        <v>370.654</v>
+        <v>371.022</v>
       </c>
       <c r="EF5" s="26" t="n">
-        <v>486.811</v>
+        <v>487.732</v>
       </c>
       <c r="EG5" s="26" t="n">
-        <v>511.47</v>
+        <v>512.389</v>
       </c>
       <c r="EH5" s="26" t="n">
-        <v>934.205</v>
+        <v>935.125</v>
       </c>
       <c r="EI5" s="26" t="n">
         <v>951.711</v>
@@ -40477,46 +40477,46 @@
         <v>81.759</v>
       </c>
       <c r="Z7" s="26" t="n">
-        <v>100.301</v>
+        <v>100.437</v>
       </c>
       <c r="AA7" s="26" t="n">
-        <v>115.507</v>
+        <v>115.739</v>
       </c>
       <c r="AB7" s="26" t="n">
-        <v>115.672</v>
+        <v>115.901</v>
       </c>
       <c r="AC7" s="26" t="n">
-        <v>122.576</v>
+        <v>122.805</v>
       </c>
       <c r="AD7" s="26" t="n">
-        <v>124.033</v>
+        <v>124.264</v>
       </c>
       <c r="AE7" s="26" t="n">
-        <v>124.53</v>
+        <v>124.762</v>
       </c>
       <c r="AF7" s="26" t="n">
-        <v>125.402</v>
+        <v>125.628</v>
       </c>
       <c r="AG7" s="26" t="n">
-        <v>125.12</v>
+        <v>125.35</v>
       </c>
       <c r="AH7" s="26" t="n">
-        <v>125.711</v>
+        <v>125.942</v>
       </c>
       <c r="AI7" s="26" t="n">
-        <v>132.555</v>
+        <v>132.787</v>
       </c>
       <c r="AJ7" s="26" t="n">
-        <v>154.488</v>
+        <v>154.715</v>
       </c>
       <c r="AK7" s="26" t="n">
-        <v>160.398</v>
+        <v>160.627</v>
       </c>
       <c r="AL7" s="26" t="n">
-        <v>170.172</v>
+        <v>170.403</v>
       </c>
       <c r="AM7" s="26" t="n">
-        <v>171.43</v>
+        <v>171.662</v>
       </c>
       <c r="AN7" s="26" t="n">
         <v>151.434</v>
@@ -40804,16 +40804,16 @@
         <v>245.213</v>
       </c>
       <c r="EE7" s="26" t="n">
-        <v>370.654</v>
+        <v>371.022</v>
       </c>
       <c r="EF7" s="26" t="n">
-        <v>486.811</v>
+        <v>487.732</v>
       </c>
       <c r="EG7" s="26" t="n">
-        <v>508.788</v>
+        <v>509.707</v>
       </c>
       <c r="EH7" s="26" t="n">
-        <v>656.4880000000001</v>
+        <v>657.407</v>
       </c>
       <c r="EI7" s="26" t="n">
         <v>501.72</v>
@@ -41104,46 +41104,46 @@
         <v>81.759</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>100.301</v>
+        <v>100.437</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>115.507</v>
+        <v>115.739</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>115.672</v>
+        <v>115.901</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>122.576</v>
+        <v>122.805</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>124.033</v>
+        <v>124.264</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>124.53</v>
+        <v>124.762</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>125.402</v>
+        <v>125.628</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>125.12</v>
+        <v>125.35</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>125.711</v>
+        <v>125.942</v>
       </c>
       <c r="AI10" s="26" t="n">
-        <v>134.842</v>
+        <v>135.074</v>
       </c>
       <c r="AJ10" s="26" t="n">
-        <v>168.207</v>
+        <v>168.434</v>
       </c>
       <c r="AK10" s="26" t="n">
-        <v>174.269</v>
+        <v>174.499</v>
       </c>
       <c r="AL10" s="26" t="n">
-        <v>184.195</v>
+        <v>184.427</v>
       </c>
       <c r="AM10" s="26" t="n">
-        <v>185.454</v>
+        <v>185.686</v>
       </c>
       <c r="AN10" s="26" t="n">
         <v>165.153</v>
@@ -41431,16 +41431,16 @@
         <v>245.213</v>
       </c>
       <c r="EE10" s="26" t="n">
-        <v>370.654</v>
+        <v>371.022</v>
       </c>
       <c r="EF10" s="26" t="n">
-        <v>486.811</v>
+        <v>487.732</v>
       </c>
       <c r="EG10" s="26" t="n">
-        <v>511.075</v>
+        <v>511.994</v>
       </c>
       <c r="EH10" s="26" t="n">
-        <v>712.125</v>
+        <v>713.046</v>
       </c>
       <c r="EI10" s="26" t="n">
         <v>557.356</v>
@@ -42046,46 +42046,46 @@
         <v>1183.49</v>
       </c>
       <c r="Z13" s="13" t="n">
-        <v>1206.49</v>
+        <v>1206.64</v>
       </c>
       <c r="AA13" s="13" t="n">
-        <v>1220.6</v>
+        <v>1220.79</v>
       </c>
       <c r="AB13" s="13" t="n">
-        <v>1221.95</v>
+        <v>1222.13</v>
       </c>
       <c r="AC13" s="13" t="n">
-        <v>1228.04</v>
+        <v>1228.2</v>
       </c>
       <c r="AD13" s="13" t="n">
-        <v>1228.13</v>
+        <v>1228.29</v>
       </c>
       <c r="AE13" s="13" t="n">
-        <v>1228.8</v>
+        <v>1228.96</v>
       </c>
       <c r="AF13" s="13" t="n">
-        <v>1233.95</v>
+        <v>1234.09</v>
       </c>
       <c r="AG13" s="13" t="n">
-        <v>1249.3</v>
+        <v>1249.42</v>
       </c>
       <c r="AH13" s="13" t="n">
-        <v>1254.32</v>
+        <v>1254.43</v>
       </c>
       <c r="AI13" s="13" t="n">
-        <v>1268.05</v>
+        <v>1268.12</v>
       </c>
       <c r="AJ13" s="13" t="n">
-        <v>1322.93</v>
+        <v>1322.91</v>
       </c>
       <c r="AK13" s="13" t="n">
-        <v>1377.64</v>
+        <v>1377.57</v>
       </c>
       <c r="AL13" s="13" t="n">
-        <v>1386.14</v>
+        <v>1386.07</v>
       </c>
       <c r="AM13" s="13" t="n">
-        <v>1391</v>
+        <v>1390.93</v>
       </c>
       <c r="AN13" s="13" t="n">
         <v>1404.08</v>
@@ -42472,277 +42472,277 @@
         <v>1418.75</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BJ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BK14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BL14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BM14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BN14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BO14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BP14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BQ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BR14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BS14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BT14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BU14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BV14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BW14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BX14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BY14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BZ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CA14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CB14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CC14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CD14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CE14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CF14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CG14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CH14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CI14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CJ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CK14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CL14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CM14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CN14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CO14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CP14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CQ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CR14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CS14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CT14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CU14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CV14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CW14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CX14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CY14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="CZ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DA14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DB14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DC14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DD14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DE14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DF14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DG14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DH14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DI14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DJ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DK14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DL14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DM14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DN14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DO14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DP14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DQ14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DR14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DS14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DT14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DU14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DV14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DW14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DX14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="DY14" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
     </row>
     <row r="15">
@@ -42820,316 +42820,316 @@
         <v>1223.15</v>
       </c>
       <c r="Z15" s="13" t="n">
-        <v>1238.63</v>
+        <v>1238.73</v>
       </c>
       <c r="AA15" s="13" t="n">
-        <v>1251.02</v>
+        <v>1251.15</v>
       </c>
       <c r="AB15" s="13" t="n">
-        <v>1254.4</v>
+        <v>1254.53</v>
       </c>
       <c r="AC15" s="13" t="n">
-        <v>1271.01</v>
+        <v>1271.12</v>
       </c>
       <c r="AD15" s="13" t="n">
-        <v>1266.56</v>
+        <v>1266.67</v>
       </c>
       <c r="AE15" s="13" t="n">
-        <v>1279.05</v>
+        <v>1279.16</v>
       </c>
       <c r="AF15" s="13" t="n">
-        <v>1299.45</v>
+        <v>1299.55</v>
       </c>
       <c r="AG15" s="13" t="n">
-        <v>1294.07</v>
+        <v>1294.15</v>
       </c>
       <c r="AH15" s="13" t="n">
-        <v>1294.11</v>
+        <v>1294.18</v>
       </c>
       <c r="AI15" s="13" t="n">
-        <v>1322.39</v>
+        <v>1322.44</v>
       </c>
       <c r="AJ15" s="13" t="n">
         <v>1365.88</v>
       </c>
       <c r="AK15" s="13" t="n">
-        <v>1414.87</v>
+        <v>1414.83</v>
       </c>
       <c r="AL15" s="13" t="n">
-        <v>1395.92</v>
+        <v>1395.87</v>
       </c>
       <c r="AM15" s="13" t="n">
-        <v>1376.33</v>
+        <v>1374.9</v>
       </c>
       <c r="AN15" s="13" t="n">
-        <v>1382.49</v>
+        <v>1380.19</v>
       </c>
       <c r="AO15" s="13" t="n">
-        <v>1394.85</v>
+        <v>1392.55</v>
       </c>
       <c r="AP15" s="13" t="n">
-        <v>1398.57</v>
+        <v>1396.27</v>
       </c>
       <c r="AQ15" s="13" t="n">
-        <v>1402.26</v>
+        <v>1399.96</v>
       </c>
       <c r="AR15" s="13" t="n">
-        <v>1407.4</v>
+        <v>1405.1</v>
       </c>
       <c r="AS15" s="13" t="n">
-        <v>1412.28</v>
+        <v>1409.99</v>
       </c>
       <c r="AT15" s="13" t="n">
-        <v>1413.17</v>
+        <v>1410.87</v>
       </c>
       <c r="AU15" s="13" t="n">
-        <v>1411.33</v>
+        <v>1409.04</v>
       </c>
       <c r="AV15" s="13" t="n">
-        <v>1408.89</v>
+        <v>1406.6</v>
       </c>
       <c r="AW15" s="13" t="n">
-        <v>1411.92</v>
+        <v>1409.63</v>
       </c>
       <c r="AX15" s="13" t="n">
-        <v>1414.67</v>
+        <v>1412.37</v>
       </c>
       <c r="AY15" s="13" t="n">
-        <v>1418.17</v>
+        <v>1415.88</v>
       </c>
       <c r="AZ15" s="13" t="n">
-        <v>1422.62</v>
+        <v>1420.33</v>
       </c>
       <c r="BA15" s="13" t="n">
-        <v>1423.21</v>
+        <v>1420.92</v>
       </c>
       <c r="BB15" s="13" t="n">
-        <v>1422.72</v>
+        <v>1420.42</v>
       </c>
       <c r="BC15" s="13" t="n">
-        <v>1398.92</v>
+        <v>1396.62</v>
       </c>
       <c r="BD15" s="13" t="n">
-        <v>1422.38</v>
+        <v>1420.08</v>
       </c>
       <c r="BE15" s="13" t="n">
-        <v>1426.05</v>
+        <v>1423.76</v>
       </c>
       <c r="BF15" s="13" t="n">
-        <v>1423.83</v>
+        <v>1421.54</v>
       </c>
       <c r="BG15" s="13" t="n">
-        <v>1423.83</v>
+        <v>1421.54</v>
       </c>
       <c r="BH15" s="13" t="n">
-        <v>1423.83</v>
+        <v>1421.54</v>
       </c>
       <c r="BI15" s="13" t="n">
-        <v>1411.78</v>
+        <v>1409.49</v>
       </c>
       <c r="BJ15" s="13" t="n">
-        <v>1406.95</v>
+        <v>1404.66</v>
       </c>
       <c r="BK15" s="13" t="n">
-        <v>1406.95</v>
+        <v>1404.66</v>
       </c>
       <c r="BL15" s="13" t="n">
-        <v>1406.95</v>
+        <v>1404.66</v>
       </c>
       <c r="BM15" s="13" t="n">
-        <v>1406.95</v>
+        <v>1404.66</v>
       </c>
       <c r="BN15" s="13" t="n">
-        <v>1409.13</v>
+        <v>1406.84</v>
       </c>
       <c r="BO15" s="13" t="n">
-        <v>1415.74</v>
+        <v>1413.45</v>
       </c>
       <c r="BP15" s="13" t="n">
-        <v>1415.74</v>
+        <v>1413.45</v>
       </c>
       <c r="BQ15" s="13" t="n">
-        <v>1418.02</v>
+        <v>1415.72</v>
       </c>
       <c r="BR15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BS15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BT15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BU15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BV15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BW15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BX15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BY15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="BZ15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CA15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CB15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CC15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CD15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CE15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CF15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CG15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CH15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CI15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CJ15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CK15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CL15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CM15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CN15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CO15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CP15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CQ15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CR15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CS15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CT15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CU15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CV15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CW15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CX15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CY15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="CZ15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DA15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DB15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DC15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DD15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DE15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DF15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DG15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DH15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DI15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DJ15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DK15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DL15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DM15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DN15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DO15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DP15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DQ15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DR15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DS15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DT15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DU15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DV15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DW15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DX15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
       <c r="DY15" s="13" t="n">
-        <v>1425.91</v>
+        <v>1423.62</v>
       </c>
     </row>
     <row r="16">
@@ -43207,316 +43207,316 @@
         <v>100004.1</v>
       </c>
       <c r="Z16" s="18" t="n">
-        <v>124236.3</v>
+        <v>124415</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>144502.5</v>
+        <v>144807.6</v>
       </c>
       <c r="AB16" s="18" t="n">
-        <v>145099</v>
+        <v>145401.3</v>
       </c>
       <c r="AC16" s="18" t="n">
-        <v>155795.1</v>
+        <v>156100.2</v>
       </c>
       <c r="AD16" s="18" t="n">
-        <v>157094.5</v>
+        <v>157401.9</v>
       </c>
       <c r="AE16" s="18" t="n">
-        <v>159280.3</v>
+        <v>159590.5</v>
       </c>
       <c r="AF16" s="18" t="n">
-        <v>162952.9</v>
+        <v>163260.2</v>
       </c>
       <c r="AG16" s="18" t="n">
-        <v>161914.2</v>
+        <v>162221.2</v>
       </c>
       <c r="AH16" s="18" t="n">
-        <v>162683.1</v>
+        <v>162992.6</v>
       </c>
       <c r="AI16" s="18" t="n">
-        <v>178836.5</v>
+        <v>179150.4</v>
       </c>
       <c r="AJ16" s="18" t="n">
-        <v>254025.7</v>
+        <v>254333.9</v>
       </c>
       <c r="AK16" s="18" t="n">
-        <v>312625.8</v>
+        <v>312939.9</v>
       </c>
       <c r="AL16" s="18" t="n">
-        <v>338394.1</v>
+        <v>338705.9</v>
       </c>
       <c r="AM16" s="18" t="n">
-        <v>392051.5</v>
+        <v>391962.8</v>
       </c>
       <c r="AN16" s="18" t="n">
-        <v>362752</v>
+        <v>362149.8</v>
       </c>
       <c r="AO16" s="18" t="n">
-        <v>331999.4</v>
+        <v>331453.2</v>
       </c>
       <c r="AP16" s="18" t="n">
-        <v>322297.4</v>
+        <v>321768.5</v>
       </c>
       <c r="AQ16" s="18" t="n">
-        <v>309692.9</v>
+        <v>309186</v>
       </c>
       <c r="AR16" s="18" t="n">
-        <v>288986.9</v>
+        <v>288515.6</v>
       </c>
       <c r="AS16" s="18" t="n">
-        <v>281047.3</v>
+        <v>280590.6</v>
       </c>
       <c r="AT16" s="18" t="n">
-        <v>237410.3</v>
+        <v>237024.7</v>
       </c>
       <c r="AU16" s="18" t="n">
-        <v>202774.4</v>
+        <v>202444.7</v>
       </c>
       <c r="AV16" s="18" t="n">
-        <v>182881</v>
+        <v>182583.1</v>
       </c>
       <c r="AW16" s="18" t="n">
-        <v>129300.3</v>
+        <v>129090.2</v>
       </c>
       <c r="AX16" s="18" t="n">
-        <v>103296.7</v>
+        <v>103129.1</v>
       </c>
       <c r="AY16" s="18" t="n">
-        <v>84111.3</v>
+        <v>83975.2</v>
       </c>
       <c r="AZ16" s="18" t="n">
-        <v>53070.1</v>
+        <v>52984.5</v>
       </c>
       <c r="BA16" s="18" t="n">
-        <v>50200.9</v>
+        <v>50119.9</v>
       </c>
       <c r="BB16" s="18" t="n">
-        <v>42849.6</v>
+        <v>42780.5</v>
       </c>
       <c r="BC16" s="18" t="n">
-        <v>21338.1</v>
+        <v>21303</v>
       </c>
       <c r="BD16" s="18" t="n">
-        <v>18487.2</v>
+        <v>18457.4</v>
       </c>
       <c r="BE16" s="18" t="n">
-        <v>17183.2</v>
+        <v>17155.5</v>
       </c>
       <c r="BF16" s="18" t="n">
-        <v>15920.2</v>
+        <v>15894.5</v>
       </c>
       <c r="BG16" s="18" t="n">
-        <v>15920.2</v>
+        <v>15894.5</v>
       </c>
       <c r="BH16" s="18" t="n">
-        <v>15747.1</v>
+        <v>15721.7</v>
       </c>
       <c r="BI16" s="18" t="n">
-        <v>10797.3</v>
+        <v>10779.8</v>
       </c>
       <c r="BJ16" s="18" t="n">
-        <v>9682.1</v>
+        <v>9666.299999999999</v>
       </c>
       <c r="BK16" s="18" t="n">
-        <v>9682.1</v>
+        <v>9666.299999999999</v>
       </c>
       <c r="BL16" s="18" t="n">
-        <v>9471.6</v>
+        <v>9456.1</v>
       </c>
       <c r="BM16" s="18" t="n">
-        <v>9576.799999999999</v>
+        <v>9561.200000000001</v>
       </c>
       <c r="BN16" s="18" t="n">
-        <v>8407.200000000001</v>
+        <v>8393.5</v>
       </c>
       <c r="BO16" s="18" t="n">
-        <v>6016.9</v>
+        <v>6007.1</v>
       </c>
       <c r="BP16" s="18" t="n">
-        <v>5886.1</v>
+        <v>5876.5</v>
       </c>
       <c r="BQ16" s="18" t="n">
-        <v>2531.6</v>
+        <v>2527.5</v>
       </c>
       <c r="BR16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="BS16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="BT16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="BU16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="BV16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="BW16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="BX16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="BY16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="BZ16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CA16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CB16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="CC16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CD16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CE16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CF16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="CG16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CH16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CI16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CJ16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="CK16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CL16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CM16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CN16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CO16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CP16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CQ16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CR16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="CS16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CT16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CU16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CV16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="CW16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="CX16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CY16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="CZ16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="DA16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DB16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DC16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DD16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DE16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DF16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DG16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DH16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="DI16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DJ16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DK16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DL16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="DM16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DN16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DO16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DP16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="DQ16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DR16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DS16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DT16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DU16" s="18" t="n">
-        <v>849.7</v>
+        <v>848.4</v>
       </c>
       <c r="DV16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DW16" s="18" t="n">
-        <v>859.1</v>
+        <v>857.7</v>
       </c>
       <c r="DX16" s="18" t="n">
-        <v>840.4</v>
+        <v>839</v>
       </c>
       <c r="DY16" s="18" t="n">
-        <v>569.6</v>
+        <v>568.7</v>
       </c>
       <c r="DZ16" s="18" t="n">
         <v>16584.3</v>
@@ -43534,85 +43534,85 @@
         <v>289816.6</v>
       </c>
       <c r="EE16" s="18" t="n">
-        <v>456641.6</v>
+        <v>457125.4</v>
       </c>
       <c r="EF16" s="18" t="n">
-        <v>617268.9</v>
+        <v>618493.9</v>
       </c>
       <c r="EG16" s="18" t="n">
-        <v>666386.7</v>
+        <v>667624.4</v>
       </c>
       <c r="EH16" s="18" t="n">
-        <v>1297097.1</v>
+        <v>1297942.5</v>
       </c>
       <c r="EI16" s="18" t="n">
-        <v>1326741.7</v>
+        <v>1324557.5</v>
       </c>
       <c r="EJ16" s="18" t="n">
-        <v>1010218.9</v>
+        <v>1008575.6</v>
       </c>
       <c r="EK16" s="18" t="n">
-        <v>499589.3</v>
+        <v>498777.6</v>
       </c>
       <c r="EL16" s="18" t="n">
-        <v>167458.7</v>
+        <v>167187.9</v>
       </c>
       <c r="EM16" s="18" t="n">
-        <v>67510.8</v>
+        <v>67401.89999999999</v>
       </c>
       <c r="EN16" s="18" t="n">
-        <v>45908.6</v>
+        <v>45834.1</v>
       </c>
       <c r="EO16" s="18" t="n">
-        <v>33472.5</v>
+        <v>33417.9</v>
       </c>
       <c r="EP16" s="18" t="n">
-        <v>10135.9</v>
+        <v>10119.4</v>
       </c>
       <c r="EQ16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="ER16" s="18" t="n">
-        <v>3417.6</v>
+        <v>3412.2</v>
       </c>
       <c r="ES16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="ET16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="EU16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="EV16" s="18" t="n">
-        <v>3417.6</v>
+        <v>3412.2</v>
       </c>
       <c r="EW16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="EX16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="EY16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="EZ16" s="18" t="n">
-        <v>3417.6</v>
+        <v>3412.2</v>
       </c>
       <c r="FA16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="FB16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="FC16" s="18" t="n">
-        <v>3408.3</v>
+        <v>3402.8</v>
       </c>
       <c r="FD16" s="18" t="n">
-        <v>3417.6</v>
+        <v>3412.2</v>
       </c>
       <c r="FE16" s="18" t="n">
-        <v>1410</v>
+        <v>1407.7</v>
       </c>
     </row>
     <row r="17">
@@ -43729,43 +43729,43 @@
         <v>105104.1</v>
       </c>
       <c r="AM17" s="18" t="n">
-        <v>160917.4</v>
+        <v>160760.2</v>
       </c>
       <c r="AN17" s="18" t="n">
-        <v>157086</v>
+        <v>156831.3</v>
       </c>
       <c r="AO17" s="18" t="n">
-        <v>158831.4</v>
+        <v>158573.9</v>
       </c>
       <c r="AP17" s="18" t="n">
-        <v>160576.7</v>
+        <v>160316.4</v>
       </c>
       <c r="AQ17" s="18" t="n">
-        <v>160576.7</v>
+        <v>160316.4</v>
       </c>
       <c r="AR17" s="18" t="n">
-        <v>158831.4</v>
+        <v>158573.9</v>
       </c>
       <c r="AS17" s="18" t="n">
-        <v>158831.4</v>
+        <v>158573.9</v>
       </c>
       <c r="AT17" s="18" t="n">
-        <v>124327.7</v>
+        <v>124125.7</v>
       </c>
       <c r="AU17" s="18" t="n">
-        <v>100004.4</v>
+        <v>99841</v>
       </c>
       <c r="AV17" s="18" t="n">
-        <v>82345.10000000001</v>
+        <v>82209.89999999999</v>
       </c>
       <c r="AW17" s="18" t="n">
-        <v>40596.7</v>
+        <v>40530.3</v>
       </c>
       <c r="AX17" s="18" t="n">
-        <v>19830.3</v>
+        <v>19798.2</v>
       </c>
       <c r="AY17" s="18" t="n">
-        <v>6682</v>
+        <v>6671.1</v>
       </c>
       <c r="AZ17" s="18" t="n">
         <v>0</v>
@@ -44026,16 +44026,16 @@
         <v>3886.8</v>
       </c>
       <c r="EH17" s="18" t="n">
-        <v>401641</v>
+        <v>401483.8</v>
       </c>
       <c r="EI17" s="18" t="n">
-        <v>637070.8</v>
+        <v>636038</v>
       </c>
       <c r="EJ17" s="18" t="n">
-        <v>541994.9</v>
+        <v>541114.5</v>
       </c>
       <c r="EK17" s="18" t="n">
-        <v>149454.1</v>
+        <v>149209.5</v>
       </c>
       <c r="EL17" s="18" t="n">
         <v>0</v>
@@ -44212,43 +44212,43 @@
         <v>97979.60000000001</v>
       </c>
       <c r="AM18" s="18" t="n">
-        <v>96434</v>
+        <v>96340.8</v>
       </c>
       <c r="AN18" s="18" t="n">
-        <v>94140.10000000001</v>
+        <v>93989.2</v>
       </c>
       <c r="AO18" s="18" t="n">
-        <v>95186.10000000001</v>
+        <v>95033.5</v>
       </c>
       <c r="AP18" s="18" t="n">
-        <v>96232.10000000001</v>
+        <v>96077.8</v>
       </c>
       <c r="AQ18" s="18" t="n">
-        <v>96232.10000000001</v>
+        <v>96077.8</v>
       </c>
       <c r="AR18" s="18" t="n">
-        <v>95186.10000000001</v>
+        <v>95033.5</v>
       </c>
       <c r="AS18" s="18" t="n">
-        <v>95186.10000000001</v>
+        <v>95033.5</v>
       </c>
       <c r="AT18" s="18" t="n">
-        <v>59983</v>
+        <v>59887.1</v>
       </c>
       <c r="AU18" s="18" t="n">
-        <v>35659.8</v>
+        <v>35602.4</v>
       </c>
       <c r="AV18" s="18" t="n">
-        <v>19399.2</v>
+        <v>19367.8</v>
       </c>
       <c r="AW18" s="18" t="n">
-        <v>19614.8</v>
+        <v>19583</v>
       </c>
       <c r="AX18" s="18" t="n">
-        <v>19830.3</v>
+        <v>19798.2</v>
       </c>
       <c r="AY18" s="18" t="n">
-        <v>6682</v>
+        <v>6671.1</v>
       </c>
       <c r="AZ18" s="18" t="n">
         <v>0</v>
@@ -44599,37 +44599,37 @@
         <v>7124.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>64483.4</v>
+        <v>64419.3</v>
       </c>
       <c r="AN19" s="18" t="n">
-        <v>62945.8</v>
+        <v>62842.1</v>
       </c>
       <c r="AO19" s="18" t="n">
-        <v>63645.2</v>
+        <v>63540.4</v>
       </c>
       <c r="AP19" s="18" t="n">
-        <v>64344.6</v>
+        <v>64238.6</v>
       </c>
       <c r="AQ19" s="18" t="n">
-        <v>64344.6</v>
+        <v>64238.6</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>63645.2</v>
+        <v>63540.4</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>63645.2</v>
+        <v>63540.4</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>64344.6</v>
+        <v>64238.6</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>64344.6</v>
+        <v>64238.6</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>62945.8</v>
+        <v>62842.1</v>
       </c>
       <c r="AW19" s="18" t="n">
-        <v>20981.9</v>
+        <v>20947.4</v>
       </c>
       <c r="AX19" s="18" t="n">
         <v>0</v>
@@ -45117,367 +45117,367 @@
         <v/>
       </c>
       <c r="AM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1342.11)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1337.49)</f>
         <v/>
       </c>
       <c r="AN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BF$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BG$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BH$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BI$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BJ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BK$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BL$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BM$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BN$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BO$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BP$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BQ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BR$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BS$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BT$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BU$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BV$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BW$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BX$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BY$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BZ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CA$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CB$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CC$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CD$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CE$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CF$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CG$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CH$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CI$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CJ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CK$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CL$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CM$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CN$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CO$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CP$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CQ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CR$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CS$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CT$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CU$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CV$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CW$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CX$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CY$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="CZ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(CZ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DA25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DA$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DB25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DB$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DC25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DC$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DD25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DD$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DE25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DE$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DF25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DF$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DG25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DG$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DH25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DH$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DI25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DI$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DJ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DJ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DK25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DK$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DL25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DL$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DM25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DM$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DN25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DN$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DO25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DO$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DP25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DP$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DQ25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DQ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DR25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DR$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DS25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DS$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DT25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DT$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DU25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DU$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DV25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DV$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DW25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DW$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DX25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DX$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="DY25" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(DY$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
     </row>
@@ -50496,7 +50496,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260820800160</t>
+          <t>20260918800109</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -50506,266 +50506,269 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>500kV 신가평변환소 토건공사</t>
-        </is>
-      </c>
-      <c r="Z70" s="26" t="n">
-        <v>2.827</v>
-      </c>
-      <c r="AA70" s="26" t="n">
-        <v>4.817</v>
+          <t>울산기력 4,5,6호기 해체공사(종합심사낙찰제)</t>
+        </is>
       </c>
       <c r="AB70" s="26" t="n">
-        <v>4.764</v>
+        <v>1.268</v>
       </c>
       <c r="AC70" s="26" t="n">
-        <v>4.764</v>
+        <v>2.509</v>
       </c>
       <c r="AD70" s="26" t="n">
-        <v>4.817</v>
+        <v>2.537</v>
       </c>
       <c r="AE70" s="26" t="n">
-        <v>4.817</v>
+        <v>2.537</v>
       </c>
       <c r="AF70" s="26" t="n">
-        <v>4.712</v>
+        <v>2.481</v>
       </c>
       <c r="AG70" s="26" t="n">
-        <v>4.764</v>
+        <v>2.509</v>
       </c>
       <c r="AH70" s="26" t="n">
-        <v>4.817</v>
+        <v>2.537</v>
       </c>
       <c r="AI70" s="26" t="n">
-        <v>4.817</v>
+        <v>2.537</v>
       </c>
       <c r="AJ70" s="26" t="n">
-        <v>4.712</v>
+        <v>2.481</v>
       </c>
       <c r="AK70" s="26" t="n">
-        <v>4.764</v>
+        <v>2.509</v>
       </c>
       <c r="AL70" s="26" t="n">
-        <v>4.817</v>
+        <v>2.537</v>
       </c>
       <c r="AM70" s="26" t="n">
-        <v>4.817</v>
+        <v>2.537</v>
+      </c>
+      <c r="AN70" s="26" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="AO70" s="26" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="AP70" s="26" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="AQ70" s="26" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="AR70" s="26" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="AS70" s="26" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="AT70" s="26" t="n">
+        <v>1.1</v>
       </c>
       <c r="FG70" s="35" t="n">
         <v>0</v>
       </c>
       <c r="FH70" s="16" t="n">
-        <v>1313.62</v>
+        <v>1330.14</v>
       </c>
       <c r="FI70" s="42" t="n">
         <v>1</v>
       </c>
       <c r="FJ70" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="FK70" t="n">
         <v>1</v>
       </c>
       <c r="FM70" s="26" t="n">
-        <v>65.026</v>
+        <v>45.161</v>
       </c>
       <c r="FN70" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2028-08-09</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260918800109</t>
+          <t>20260922800008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>울산기력 4,5,6호기 해체공사(종합심사낙찰제)</t>
-        </is>
-      </c>
-      <c r="AB71" s="26" t="n">
-        <v>1.268</v>
-      </c>
-      <c r="AC71" s="26" t="n">
-        <v>2.509</v>
-      </c>
-      <c r="AD71" s="26" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="AE71" s="26" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="AF71" s="26" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="AG71" s="26" t="n">
-        <v>2.509</v>
-      </c>
-      <c r="AH71" s="26" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="AI71" s="26" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="AJ71" s="26" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="AK71" s="26" t="n">
-        <v>2.509</v>
+          <t>컨테이너선 4척 수주</t>
+        </is>
       </c>
       <c r="AL71" s="26" t="n">
-        <v>2.537</v>
+        <v>5.022</v>
       </c>
       <c r="AM71" s="26" t="n">
-        <v>2.537</v>
+        <v>46.2</v>
       </c>
       <c r="AN71" s="26" t="n">
-        <v>2.481</v>
+        <v>45.195</v>
       </c>
       <c r="AO71" s="26" t="n">
-        <v>2.509</v>
+        <v>45.697</v>
       </c>
       <c r="AP71" s="26" t="n">
-        <v>2.537</v>
+        <v>46.2</v>
       </c>
       <c r="AQ71" s="26" t="n">
-        <v>2.537</v>
+        <v>46.2</v>
       </c>
       <c r="AR71" s="26" t="n">
-        <v>2.509</v>
+        <v>45.697</v>
       </c>
       <c r="AS71" s="26" t="n">
-        <v>2.509</v>
+        <v>45.697</v>
       </c>
       <c r="AT71" s="26" t="n">
-        <v>1.1</v>
+        <v>46.2</v>
+      </c>
+      <c r="AU71" s="26" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AV71" s="26" t="n">
+        <v>45.195</v>
+      </c>
+      <c r="AW71" s="26" t="n">
+        <v>15.064</v>
       </c>
       <c r="FG71" s="35" t="n">
         <v>0</v>
       </c>
       <c r="FH71" s="16" t="n">
-        <v>1330.14</v>
+        <v>1418.75</v>
       </c>
       <c r="FI71" s="42" t="n">
         <v>1</v>
       </c>
       <c r="FJ71" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="FK71" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FL71" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
       </c>
       <c r="FM71" s="26" t="n">
-        <v>45.161</v>
+        <v>478.567</v>
       </c>
       <c r="FN71" t="inlineStr">
         <is>
-          <t>2028-08-09</t>
+          <t>2029-04-30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260922800008</t>
+          <t>20261014800411</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>4</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>컨테이너선 4척 수주</t>
-        </is>
+          <t>보령신복합 1호기 건설공사</t>
+        </is>
+      </c>
+      <c r="Z72" s="26" t="n">
+        <v>2.028</v>
+      </c>
+      <c r="AA72" s="26" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AB72" s="26" t="n">
+        <v>14.194</v>
+      </c>
+      <c r="AC72" s="26" t="n">
+        <v>14.194</v>
+      </c>
+      <c r="AD72" s="26" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AE72" s="26" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AF72" s="26" t="n">
+        <v>14.038</v>
+      </c>
+      <c r="AG72" s="26" t="n">
+        <v>14.194</v>
+      </c>
+      <c r="AH72" s="26" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AI72" s="26" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AJ72" s="26" t="n">
+        <v>14.038</v>
+      </c>
+      <c r="AK72" s="26" t="n">
+        <v>14.194</v>
       </c>
       <c r="AL72" s="26" t="n">
-        <v>5.022</v>
+        <v>14.35</v>
       </c>
       <c r="AM72" s="26" t="n">
-        <v>46.2</v>
+        <v>14.35</v>
       </c>
       <c r="AN72" s="26" t="n">
-        <v>45.195</v>
-      </c>
-      <c r="AO72" s="26" t="n">
-        <v>45.697</v>
-      </c>
-      <c r="AP72" s="26" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AQ72" s="26" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AR72" s="26" t="n">
-        <v>45.697</v>
-      </c>
-      <c r="AS72" s="26" t="n">
-        <v>45.697</v>
-      </c>
-      <c r="AT72" s="26" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AU72" s="26" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AV72" s="26" t="n">
-        <v>45.195</v>
-      </c>
-      <c r="AW72" s="26" t="n">
-        <v>15.064</v>
+        <v>14.043</v>
       </c>
       <c r="FG72" s="35" t="n">
         <v>0</v>
       </c>
       <c r="FH72" s="16" t="n">
-        <v>1418.75</v>
+        <v>1313.62</v>
       </c>
       <c r="FI72" s="42" t="n">
         <v>1</v>
       </c>
       <c r="FJ72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="FK72" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL72" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="FM72" s="26" t="n">
-        <v>478.567</v>
+        <v>201.373</v>
       </c>
       <c r="FN72" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
+          <t>2027-03-31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20261014800411</t>
+          <t>20261023800728</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -50775,53 +50778,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>보령신복합 1호기 건설공사</t>
+          <t>500kV 신가평변환소 토건공사</t>
         </is>
       </c>
       <c r="Z73" s="26" t="n">
-        <v>2.028</v>
+        <v>2.963</v>
       </c>
       <c r="AA73" s="26" t="n">
-        <v>14.35</v>
+        <v>5.049</v>
       </c>
       <c r="AB73" s="26" t="n">
-        <v>14.194</v>
+        <v>4.994</v>
       </c>
       <c r="AC73" s="26" t="n">
-        <v>14.194</v>
+        <v>4.994</v>
       </c>
       <c r="AD73" s="26" t="n">
-        <v>14.35</v>
+        <v>5.049</v>
       </c>
       <c r="AE73" s="26" t="n">
-        <v>14.35</v>
+        <v>5.049</v>
       </c>
       <c r="AF73" s="26" t="n">
-        <v>14.038</v>
+        <v>4.939</v>
       </c>
       <c r="AG73" s="26" t="n">
-        <v>14.194</v>
+        <v>4.994</v>
       </c>
       <c r="AH73" s="26" t="n">
-        <v>14.35</v>
+        <v>5.049</v>
       </c>
       <c r="AI73" s="26" t="n">
-        <v>14.35</v>
+        <v>5.049</v>
       </c>
       <c r="AJ73" s="26" t="n">
-        <v>14.038</v>
+        <v>4.939</v>
       </c>
       <c r="AK73" s="26" t="n">
-        <v>14.194</v>
+        <v>4.994</v>
       </c>
       <c r="AL73" s="26" t="n">
-        <v>14.35</v>
+        <v>5.049</v>
       </c>
       <c r="AM73" s="26" t="n">
-        <v>14.35</v>
-      </c>
-      <c r="AN73" s="26" t="n">
-        <v>14.043</v>
+        <v>5.044</v>
       </c>
       <c r="FG73" s="35" t="n">
         <v>0</v>
@@ -50834,18 +50834,18 @@
       </c>
       <c r="FJ73" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="FK73" t="n">
         <v>1</v>
       </c>
       <c r="FM73" s="26" t="n">
-        <v>201.373</v>
+        <v>68.155</v>
       </c>
       <c r="FN73" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -55336,7 +55336,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20260820800160</t>
+          <t>20260918800109</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -55346,16 +55346,8 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>500kV 신가평변환소 토건공사</t>
-        </is>
-      </c>
-      <c r="Z117" s="18">
-        <f>IFERROR(Z70*$FG70*(1+($FI70-1)*Z$26)*($D$23*$FH70+(1-$D$23)*Z$25),"")</f>
-        <v/>
-      </c>
-      <c r="AA117" s="18">
-        <f>IFERROR(AA70*$FG70*(1+($FI70-1)*AA$26)*($D$23*$FH70+(1-$D$23)*AA$25),"")</f>
-        <v/>
+          <t>울산기력 4,5,6호기 해체공사(종합심사낙찰제)</t>
+        </is>
       </c>
       <c r="AB117" s="18">
         <f>IFERROR(AB70*$FG70*(1+($FI70-1)*AB$26)*($D$23*$FH70+(1-$D$23)*AB$25),"")</f>
@@ -55403,64 +55395,55 @@
       </c>
       <c r="AM117" s="18">
         <f>IFERROR(AM70*$FG70*(1+($FI70-1)*AM$26)*($D$23*$FH70+(1-$D$23)*AM$25),"")</f>
+        <v/>
+      </c>
+      <c r="AN117" s="18">
+        <f>IFERROR(AN70*$FG70*(1+($FI70-1)*AN$26)*($D$23*$FH70+(1-$D$23)*AN$25),"")</f>
+        <v/>
+      </c>
+      <c r="AO117" s="18">
+        <f>IFERROR(AO70*$FG70*(1+($FI70-1)*AO$26)*($D$23*$FH70+(1-$D$23)*AO$25),"")</f>
+        <v/>
+      </c>
+      <c r="AP117" s="18">
+        <f>IFERROR(AP70*$FG70*(1+($FI70-1)*AP$26)*($D$23*$FH70+(1-$D$23)*AP$25),"")</f>
+        <v/>
+      </c>
+      <c r="AQ117" s="18">
+        <f>IFERROR(AQ70*$FG70*(1+($FI70-1)*AQ$26)*($D$23*$FH70+(1-$D$23)*AQ$25),"")</f>
+        <v/>
+      </c>
+      <c r="AR117" s="18">
+        <f>IFERROR(AR70*$FG70*(1+($FI70-1)*AR$26)*($D$23*$FH70+(1-$D$23)*AR$25),"")</f>
+        <v/>
+      </c>
+      <c r="AS117" s="18">
+        <f>IFERROR(AS70*$FG70*(1+($FI70-1)*AS$26)*($D$23*$FH70+(1-$D$23)*AS$25),"")</f>
+        <v/>
+      </c>
+      <c r="AT117" s="18">
+        <f>IFERROR(AT70*$FG70*(1+($FI70-1)*AT$26)*($D$23*$FH70+(1-$D$23)*AT$25),"")</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>20260918800109</t>
+          <t>20260922800008</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>4</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>울산기력 4,5,6호기 해체공사(종합심사낙찰제)</t>
-        </is>
-      </c>
-      <c r="AB118" s="18">
-        <f>IFERROR(AB71*$FG71*(1+($FI71-1)*AB$26)*($D$23*$FH71+(1-$D$23)*AB$25),"")</f>
-        <v/>
-      </c>
-      <c r="AC118" s="18">
-        <f>IFERROR(AC71*$FG71*(1+($FI71-1)*AC$26)*($D$23*$FH71+(1-$D$23)*AC$25),"")</f>
-        <v/>
-      </c>
-      <c r="AD118" s="18">
-        <f>IFERROR(AD71*$FG71*(1+($FI71-1)*AD$26)*($D$23*$FH71+(1-$D$23)*AD$25),"")</f>
-        <v/>
-      </c>
-      <c r="AE118" s="18">
-        <f>IFERROR(AE71*$FG71*(1+($FI71-1)*AE$26)*($D$23*$FH71+(1-$D$23)*AE$25),"")</f>
-        <v/>
-      </c>
-      <c r="AF118" s="18">
-        <f>IFERROR(AF71*$FG71*(1+($FI71-1)*AF$26)*($D$23*$FH71+(1-$D$23)*AF$25),"")</f>
-        <v/>
-      </c>
-      <c r="AG118" s="18">
-        <f>IFERROR(AG71*$FG71*(1+($FI71-1)*AG$26)*($D$23*$FH71+(1-$D$23)*AG$25),"")</f>
-        <v/>
-      </c>
-      <c r="AH118" s="18">
-        <f>IFERROR(AH71*$FG71*(1+($FI71-1)*AH$26)*($D$23*$FH71+(1-$D$23)*AH$25),"")</f>
-        <v/>
-      </c>
-      <c r="AI118" s="18">
-        <f>IFERROR(AI71*$FG71*(1+($FI71-1)*AI$26)*($D$23*$FH71+(1-$D$23)*AI$25),"")</f>
-        <v/>
-      </c>
-      <c r="AJ118" s="18">
-        <f>IFERROR(AJ71*$FG71*(1+($FI71-1)*AJ$26)*($D$23*$FH71+(1-$D$23)*AJ$25),"")</f>
-        <v/>
-      </c>
-      <c r="AK118" s="18">
-        <f>IFERROR(AK71*$FG71*(1+($FI71-1)*AK$26)*($D$23*$FH71+(1-$D$23)*AK$25),"")</f>
-        <v/>
+          <t>컨테이너선 4척 수주</t>
+        </is>
       </c>
       <c r="AL118" s="18">
         <f>IFERROR(AL71*$FG71*(1+($FI71-1)*AL$26)*($D$23*$FH71+(1-$D$23)*AL$25),"")</f>
@@ -55496,27 +55479,84 @@
       </c>
       <c r="AT118" s="18">
         <f>IFERROR(AT71*$FG71*(1+($FI71-1)*AT$26)*($D$23*$FH71+(1-$D$23)*AT$25),"")</f>
+        <v/>
+      </c>
+      <c r="AU118" s="18">
+        <f>IFERROR(AU71*$FG71*(1+($FI71-1)*AU$26)*($D$23*$FH71+(1-$D$23)*AU$25),"")</f>
+        <v/>
+      </c>
+      <c r="AV118" s="18">
+        <f>IFERROR(AV71*$FG71*(1+($FI71-1)*AV$26)*($D$23*$FH71+(1-$D$23)*AV$25),"")</f>
+        <v/>
+      </c>
+      <c r="AW118" s="18">
+        <f>IFERROR(AW71*$FG71*(1+($FI71-1)*AW$26)*($D$23*$FH71+(1-$D$23)*AW$25),"")</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20260922800008</t>
+          <t>20261014800411</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>4</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>컨테이너선 4척 수주</t>
-        </is>
+          <t>보령신복합 1호기 건설공사</t>
+        </is>
+      </c>
+      <c r="Z119" s="18">
+        <f>IFERROR(Z72*$FG72*(1+($FI72-1)*Z$26)*($D$23*$FH72+(1-$D$23)*Z$25),"")</f>
+        <v/>
+      </c>
+      <c r="AA119" s="18">
+        <f>IFERROR(AA72*$FG72*(1+($FI72-1)*AA$26)*($D$23*$FH72+(1-$D$23)*AA$25),"")</f>
+        <v/>
+      </c>
+      <c r="AB119" s="18">
+        <f>IFERROR(AB72*$FG72*(1+($FI72-1)*AB$26)*($D$23*$FH72+(1-$D$23)*AB$25),"")</f>
+        <v/>
+      </c>
+      <c r="AC119" s="18">
+        <f>IFERROR(AC72*$FG72*(1+($FI72-1)*AC$26)*($D$23*$FH72+(1-$D$23)*AC$25),"")</f>
+        <v/>
+      </c>
+      <c r="AD119" s="18">
+        <f>IFERROR(AD72*$FG72*(1+($FI72-1)*AD$26)*($D$23*$FH72+(1-$D$23)*AD$25),"")</f>
+        <v/>
+      </c>
+      <c r="AE119" s="18">
+        <f>IFERROR(AE72*$FG72*(1+($FI72-1)*AE$26)*($D$23*$FH72+(1-$D$23)*AE$25),"")</f>
+        <v/>
+      </c>
+      <c r="AF119" s="18">
+        <f>IFERROR(AF72*$FG72*(1+($FI72-1)*AF$26)*($D$23*$FH72+(1-$D$23)*AF$25),"")</f>
+        <v/>
+      </c>
+      <c r="AG119" s="18">
+        <f>IFERROR(AG72*$FG72*(1+($FI72-1)*AG$26)*($D$23*$FH72+(1-$D$23)*AG$25),"")</f>
+        <v/>
+      </c>
+      <c r="AH119" s="18">
+        <f>IFERROR(AH72*$FG72*(1+($FI72-1)*AH$26)*($D$23*$FH72+(1-$D$23)*AH$25),"")</f>
+        <v/>
+      </c>
+      <c r="AI119" s="18">
+        <f>IFERROR(AI72*$FG72*(1+($FI72-1)*AI$26)*($D$23*$FH72+(1-$D$23)*AI$25),"")</f>
+        <v/>
+      </c>
+      <c r="AJ119" s="18">
+        <f>IFERROR(AJ72*$FG72*(1+($FI72-1)*AJ$26)*($D$23*$FH72+(1-$D$23)*AJ$25),"")</f>
+        <v/>
+      </c>
+      <c r="AK119" s="18">
+        <f>IFERROR(AK72*$FG72*(1+($FI72-1)*AK$26)*($D$23*$FH72+(1-$D$23)*AK$25),"")</f>
+        <v/>
       </c>
       <c r="AL119" s="18">
         <f>IFERROR(AL72*$FG72*(1+($FI72-1)*AL$26)*($D$23*$FH72+(1-$D$23)*AL$25),"")</f>
@@ -55528,49 +55568,13 @@
       </c>
       <c r="AN119" s="18">
         <f>IFERROR(AN72*$FG72*(1+($FI72-1)*AN$26)*($D$23*$FH72+(1-$D$23)*AN$25),"")</f>
-        <v/>
-      </c>
-      <c r="AO119" s="18">
-        <f>IFERROR(AO72*$FG72*(1+($FI72-1)*AO$26)*($D$23*$FH72+(1-$D$23)*AO$25),"")</f>
-        <v/>
-      </c>
-      <c r="AP119" s="18">
-        <f>IFERROR(AP72*$FG72*(1+($FI72-1)*AP$26)*($D$23*$FH72+(1-$D$23)*AP$25),"")</f>
-        <v/>
-      </c>
-      <c r="AQ119" s="18">
-        <f>IFERROR(AQ72*$FG72*(1+($FI72-1)*AQ$26)*($D$23*$FH72+(1-$D$23)*AQ$25),"")</f>
-        <v/>
-      </c>
-      <c r="AR119" s="18">
-        <f>IFERROR(AR72*$FG72*(1+($FI72-1)*AR$26)*($D$23*$FH72+(1-$D$23)*AR$25),"")</f>
-        <v/>
-      </c>
-      <c r="AS119" s="18">
-        <f>IFERROR(AS72*$FG72*(1+($FI72-1)*AS$26)*($D$23*$FH72+(1-$D$23)*AS$25),"")</f>
-        <v/>
-      </c>
-      <c r="AT119" s="18">
-        <f>IFERROR(AT72*$FG72*(1+($FI72-1)*AT$26)*($D$23*$FH72+(1-$D$23)*AT$25),"")</f>
-        <v/>
-      </c>
-      <c r="AU119" s="18">
-        <f>IFERROR(AU72*$FG72*(1+($FI72-1)*AU$26)*($D$23*$FH72+(1-$D$23)*AU$25),"")</f>
-        <v/>
-      </c>
-      <c r="AV119" s="18">
-        <f>IFERROR(AV72*$FG72*(1+($FI72-1)*AV$26)*($D$23*$FH72+(1-$D$23)*AV$25),"")</f>
-        <v/>
-      </c>
-      <c r="AW119" s="18">
-        <f>IFERROR(AW72*$FG72*(1+($FI72-1)*AW$26)*($D$23*$FH72+(1-$D$23)*AW$25),"")</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20261014800411</t>
+          <t>20261023800728</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -55580,7 +55584,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>보령신복합 1호기 건설공사</t>
+          <t>500kV 신가평변환소 토건공사</t>
         </is>
       </c>
       <c r="Z120" s="18">
@@ -55637,10 +55641,6 @@
       </c>
       <c r="AM120" s="18">
         <f>IFERROR(AM73*$FG73*(1+($FI73-1)*AM$26)*($D$23*$FH73+(1-$D$23)*AM$25),"")</f>
-        <v/>
-      </c>
-      <c r="AN120" s="18">
-        <f>IFERROR(AN73*$FG73*(1+($FI73-1)*AN$26)*($D$23*$FH73+(1-$D$23)*AN$25),"")</f>
         <v/>
       </c>
     </row>
@@ -57610,7 +57610,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -58173,7 +58173,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -58844,7 +58844,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>20260820800160</t>
+          <t>20260918800109</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -58853,27 +58853,27 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>85419.25999999999</v>
+        <v>60071.111</v>
       </c>
       <c r="E167" t="n">
-        <v>65.026</v>
+        <v>45.161</v>
       </c>
       <c r="F167" t="n">
-        <v>1313.62</v>
+        <v>1330.14</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2028-08-09</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -58894,36 +58894,49 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>20260918800109</t>
+          <t>20260922800008</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>4</v>
       </c>
       <c r="D168" t="n">
-        <v>60071.111</v>
+        <v>678967.559</v>
       </c>
       <c r="E168" t="n">
-        <v>45.161</v>
+        <v>478.567</v>
       </c>
       <c r="F168" t="n">
-        <v>1330.14</v>
+        <v>1418.75</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2028-08-09</t>
+          <t>2029-04-30</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -58935,58 +58948,45 @@
         <v>1</v>
       </c>
       <c r="N168" t="b">
+        <v>0</v>
+      </c>
+      <c r="O168" t="b">
         <v>1</v>
-      </c>
-      <c r="O168" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>20260922800008</t>
+          <t>20261014800411</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>4</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D169" t="n">
-        <v>678967.559</v>
+        <v>264527.897</v>
       </c>
       <c r="E169" t="n">
-        <v>478.567</v>
+        <v>201.373</v>
       </c>
       <c r="F169" t="n">
-        <v>1418.75</v>
+        <v>1313.62</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -58998,16 +58998,16 @@
         <v>1</v>
       </c>
       <c r="N169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>20261014800411</t>
+          <t>20261023800728</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -59016,27 +59016,27 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>264527.897</v>
+        <v>89530.077</v>
       </c>
       <c r="E170" t="n">
-        <v>201.373</v>
+        <v>68.155</v>
       </c>
       <c r="F170" t="n">
         <v>1313.62</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -59078,7 +59078,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 5%, ③중마진 95%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 100%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
@@ -59092,7 +59092,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32305억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
+          <t>⚠ 비해양(OTHER: 공사·플랜트 등) 포함 원장 잔여 32311억 &gt; 정기보고서 수주표 기말잔고 19043억(전부문 커버리지 1.70) — 수주표는 조선 부문 범위(특수선·상선·수리)만 담아 비교 범위가 다르다. backlog_coverage_all_segments 는 배율로 쓰지 말 것</t>
         </is>
       </c>
     </row>
@@ -60779,7 +60779,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
